--- a/Config/Datas/FoodDatas/FoodData.xlsx
+++ b/Config/Datas/FoodDatas/FoodData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UnityProject\BBQ\Config\Datas\FoodDatas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\FoodDatas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C500893-B09E-4022-B96E-2D096A8444D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E66170A-7FBE-4A4F-B166-700658AA4BE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -546,6 +546,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -554,9 +557,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -839,31 +839,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AG22"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="4" max="4" width="15.25" customWidth="1"/>
     <col min="5" max="5" width="7.5" customWidth="1"/>
-    <col min="6" max="7" width="6.625" customWidth="1"/>
-    <col min="8" max="8" width="6.875" customWidth="1"/>
+    <col min="6" max="7" width="6.58203125" customWidth="1"/>
+    <col min="8" max="8" width="6.83203125" customWidth="1"/>
     <col min="10" max="10" width="12.75" customWidth="1"/>
     <col min="11" max="11" width="29.5" customWidth="1"/>
     <col min="12" max="12" width="15.5" customWidth="1"/>
-    <col min="13" max="13" width="5.375" style="6" customWidth="1"/>
-    <col min="14" max="14" width="21.125" style="6" customWidth="1"/>
-    <col min="15" max="15" width="9.375" style="6" customWidth="1"/>
-    <col min="16" max="16" width="13.125" style="6" customWidth="1"/>
-    <col min="17" max="17" width="9.375" style="6" customWidth="1"/>
+    <col min="13" max="13" width="5.33203125" style="6" customWidth="1"/>
+    <col min="14" max="14" width="21.08203125" style="6" customWidth="1"/>
+    <col min="15" max="15" width="9.33203125" style="6" customWidth="1"/>
+    <col min="16" max="16" width="13.08203125" style="6" customWidth="1"/>
+    <col min="17" max="17" width="9.33203125" style="6" customWidth="1"/>
     <col min="18" max="18" width="21.75" style="6" customWidth="1"/>
     <col min="19" max="19" width="21" style="6" customWidth="1"/>
     <col min="20" max="20" width="23" style="6" customWidth="1"/>
     <col min="21" max="21" width="24.25" customWidth="1"/>
     <col min="22" max="22" width="20.5" customWidth="1"/>
     <col min="23" max="23" width="11.75" customWidth="1"/>
-    <col min="27" max="27" width="13.625" customWidth="1"/>
+    <col min="27" max="27" width="13.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -897,34 +897,34 @@
       <c r="K1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="L1" s="11" t="s">
+      <c r="L1" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="M1" s="11"/>
-      <c r="N1" s="11"/>
-      <c r="O1" s="11"/>
-      <c r="P1" s="11"/>
-      <c r="Q1" s="11"/>
-      <c r="R1" s="11"/>
-      <c r="S1" s="11"/>
-      <c r="T1" s="11"/>
-      <c r="U1" s="11"/>
-      <c r="V1" s="10" t="s">
+      <c r="M1" s="12"/>
+      <c r="N1" s="12"/>
+      <c r="O1" s="12"/>
+      <c r="P1" s="12"/>
+      <c r="Q1" s="12"/>
+      <c r="R1" s="12"/>
+      <c r="S1" s="12"/>
+      <c r="T1" s="12"/>
+      <c r="U1" s="12"/>
+      <c r="V1" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="W1" s="10"/>
-      <c r="X1" s="10"/>
-      <c r="Y1" s="10"/>
-      <c r="Z1" s="10"/>
-      <c r="AA1" s="10"/>
-      <c r="AB1" s="10"/>
-      <c r="AC1" s="10"/>
-      <c r="AD1" s="10"/>
-      <c r="AE1" s="10"/>
-      <c r="AF1" s="10"/>
-      <c r="AG1" s="10"/>
-    </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="W1" s="11"/>
+      <c r="X1" s="11"/>
+      <c r="Y1" s="11"/>
+      <c r="Z1" s="11"/>
+      <c r="AA1" s="11"/>
+      <c r="AB1" s="11"/>
+      <c r="AC1" s="11"/>
+      <c r="AD1" s="11"/>
+      <c r="AE1" s="11"/>
+      <c r="AF1" s="11"/>
+      <c r="AG1" s="11"/>
+    </row>
+    <row r="2" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -958,34 +958,34 @@
       <c r="K2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="L2" s="10" t="s">
+      <c r="L2" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M2" s="10"/>
-      <c r="N2" s="10"/>
-      <c r="O2" s="10"/>
-      <c r="P2" s="10"/>
-      <c r="Q2" s="10"/>
-      <c r="R2" s="10"/>
-      <c r="S2" s="10"/>
-      <c r="T2" s="10"/>
-      <c r="U2" s="10"/>
-      <c r="V2" s="11" t="s">
+      <c r="M2" s="11"/>
+      <c r="N2" s="11"/>
+      <c r="O2" s="11"/>
+      <c r="P2" s="11"/>
+      <c r="Q2" s="11"/>
+      <c r="R2" s="11"/>
+      <c r="S2" s="11"/>
+      <c r="T2" s="11"/>
+      <c r="U2" s="11"/>
+      <c r="V2" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="W2" s="11"/>
-      <c r="X2" s="11"/>
-      <c r="Y2" s="11"/>
-      <c r="Z2" s="11"/>
-      <c r="AA2" s="11"/>
-      <c r="AB2" s="11"/>
-      <c r="AC2" s="11"/>
-      <c r="AD2" s="11"/>
-      <c r="AE2" s="11"/>
-      <c r="AF2" s="11"/>
-      <c r="AG2" s="11"/>
-    </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="W2" s="12"/>
+      <c r="X2" s="12"/>
+      <c r="Y2" s="12"/>
+      <c r="Z2" s="12"/>
+      <c r="AA2" s="12"/>
+      <c r="AB2" s="12"/>
+      <c r="AC2" s="12"/>
+      <c r="AD2" s="12"/>
+      <c r="AE2" s="12"/>
+      <c r="AF2" s="12"/>
+      <c r="AG2" s="12"/>
+    </row>
+    <row r="3" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -1030,7 +1030,7 @@
       <c r="AC3" s="1"/>
       <c r="AD3" s="1"/>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1047,39 +1047,39 @@
       <c r="L4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="M4" s="10" t="s">
+      <c r="M4" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="N4" s="10"/>
-      <c r="O4" s="10"/>
-      <c r="P4" s="10"/>
-      <c r="Q4" s="10"/>
-      <c r="R4" s="10"/>
-      <c r="S4" s="10"/>
-      <c r="T4" s="10"/>
-      <c r="U4" s="10"/>
+      <c r="N4" s="11"/>
+      <c r="O4" s="11"/>
+      <c r="P4" s="11"/>
+      <c r="Q4" s="11"/>
+      <c r="R4" s="11"/>
+      <c r="S4" s="11"/>
+      <c r="T4" s="11"/>
+      <c r="U4" s="11"/>
       <c r="V4" t="s">
         <v>36</v>
       </c>
       <c r="W4" t="s">
         <v>73</v>
       </c>
-      <c r="X4" s="13" t="s">
+      <c r="X4" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="Y4" s="13"/>
-      <c r="Z4" s="13"/>
-      <c r="AA4" s="13"/>
-      <c r="AB4" s="13"/>
-      <c r="AC4" s="13"/>
-      <c r="AD4" s="13"/>
-      <c r="AE4" s="11" t="s">
+      <c r="Y4" s="10"/>
+      <c r="Z4" s="10"/>
+      <c r="AA4" s="10"/>
+      <c r="AB4" s="10"/>
+      <c r="AC4" s="10"/>
+      <c r="AD4" s="10"/>
+      <c r="AE4" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="AF4" s="11"/>
-      <c r="AG4" s="11"/>
-    </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AF4" s="12"/>
+      <c r="AG4" s="12"/>
+    </row>
+    <row r="5" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1097,33 +1097,33 @@
       <c r="M5" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="N5" s="10" t="s">
+      <c r="N5" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="O5" s="10"/>
-      <c r="P5" s="10"/>
-      <c r="Q5" s="10"/>
-      <c r="R5" s="13" t="s">
+      <c r="O5" s="11"/>
+      <c r="P5" s="11"/>
+      <c r="Q5" s="11"/>
+      <c r="R5" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="S5" s="13"/>
-      <c r="T5" s="13"/>
-      <c r="U5" s="13"/>
+      <c r="S5" s="10"/>
+      <c r="T5" s="10"/>
+      <c r="U5" s="10"/>
       <c r="X5" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="Y5" s="13" t="s">
+      <c r="Y5" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="Z5" s="13"/>
-      <c r="AA5" s="13" t="s">
+      <c r="Z5" s="10"/>
+      <c r="AA5" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="AB5" s="13"/>
-      <c r="AC5" s="13"/>
-      <c r="AD5" s="13"/>
-    </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AB5" s="10"/>
+      <c r="AC5" s="10"/>
+      <c r="AD5" s="10"/>
+    </row>
+    <row r="6" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -1141,20 +1141,20 @@
       <c r="M6" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="N6" s="10" t="s">
+      <c r="N6" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="O6" s="10"/>
-      <c r="P6" s="10"/>
-      <c r="Q6" s="10"/>
-      <c r="R6" s="13" t="s">
+      <c r="O6" s="11"/>
+      <c r="P6" s="11"/>
+      <c r="Q6" s="11"/>
+      <c r="R6" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="S6" s="13"/>
-      <c r="T6" s="13"/>
-      <c r="U6" s="13"/>
-    </row>
-    <row r="7" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="S6" s="10"/>
+      <c r="T6" s="10"/>
+      <c r="U6" s="10"/>
+    </row>
+    <row r="7" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>3</v>
       </c>
@@ -1163,21 +1163,21 @@
       <c r="N7" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="O7" s="12" t="s">
+      <c r="O7" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="P7" s="12"/>
-      <c r="Q7" s="12"/>
+      <c r="P7" s="13"/>
+      <c r="Q7" s="13"/>
       <c r="R7" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="S7" s="12" t="s">
+      <c r="S7" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="T7" s="12"/>
-      <c r="U7" s="12"/>
-    </row>
-    <row r="8" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="T7" s="13"/>
+      <c r="U7" s="13"/>
+    </row>
+    <row r="8" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
         <v>96</v>
       </c>
@@ -1221,7 +1221,7 @@
       <c r="W8" s="2"/>
       <c r="AA8" s="2"/>
     </row>
-    <row r="9" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
@@ -1247,7 +1247,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="10" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B10" s="7" t="s">
         <v>95</v>
       </c>
@@ -1276,8 +1276,8 @@
       <c r="K10" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="L10" s="7" t="s">
-        <v>62</v>
+      <c r="L10" s="2" t="s">
+        <v>98</v>
       </c>
       <c r="M10" s="7">
         <v>1</v>
@@ -1304,13 +1304,13 @@
         <v>52</v>
       </c>
     </row>
-    <row r="11" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
       <c r="J11" s="2"/>
     </row>
-    <row r="12" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B12" s="7" t="s">
         <v>94</v>
       </c>
@@ -1339,8 +1339,8 @@
       <c r="K12" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="L12" s="7" t="s">
-        <v>62</v>
+      <c r="L12" s="2" t="s">
+        <v>98</v>
       </c>
       <c r="M12" s="7">
         <v>1</v>
@@ -1364,8 +1364,8 @@
         <v>58</v>
       </c>
     </row>
-    <row r="13" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="14" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B14" s="7" t="s">
         <v>93</v>
       </c>
@@ -1412,8 +1412,8 @@
         <v>67</v>
       </c>
     </row>
-    <row r="15" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="16" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
         <v>17</v>
       </c>
@@ -1442,8 +1442,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="17" spans="1:30" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="18" spans="1:30" s="7" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:30" s="7" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="18" spans="1:30" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B18" s="7" t="s">
         <v>91</v>
       </c>
@@ -1490,7 +1490,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="19" spans="1:30" s="7" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:30" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="X19" s="7">
         <v>2</v>
       </c>
@@ -1507,7 +1507,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="20" spans="1:30" s="7" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:30" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B20" s="7" t="s">
         <v>90</v>
       </c>
@@ -1551,7 +1551,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="22" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>17</v>
       </c>
@@ -1594,12 +1594,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="Y5:Z5"/>
-    <mergeCell ref="AA5:AD5"/>
-    <mergeCell ref="V1:AG1"/>
-    <mergeCell ref="V2:AG2"/>
-    <mergeCell ref="X4:AD4"/>
-    <mergeCell ref="AE4:AG4"/>
     <mergeCell ref="L2:U2"/>
     <mergeCell ref="L1:U1"/>
     <mergeCell ref="N6:Q6"/>
@@ -1609,6 +1603,12 @@
     <mergeCell ref="R6:U6"/>
     <mergeCell ref="R5:U5"/>
     <mergeCell ref="M4:U4"/>
+    <mergeCell ref="Y5:Z5"/>
+    <mergeCell ref="AA5:AD5"/>
+    <mergeCell ref="V1:AG1"/>
+    <mergeCell ref="V2:AG2"/>
+    <mergeCell ref="X4:AD4"/>
+    <mergeCell ref="AE4:AG4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/Datas/FoodDatas/FoodData.xlsx
+++ b/Config/Datas/FoodDatas/FoodData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\FoodDatas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E66170A-7FBE-4A4F-B166-700658AA4BE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA7290A8-4162-4903-89CF-34345CA67B69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -546,9 +546,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -557,6 +554,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -839,31 +839,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AG22"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="4" max="4" width="15.25" customWidth="1"/>
     <col min="5" max="5" width="7.5" customWidth="1"/>
-    <col min="6" max="7" width="6.58203125" customWidth="1"/>
-    <col min="8" max="8" width="6.83203125" customWidth="1"/>
+    <col min="6" max="7" width="6.625" customWidth="1"/>
+    <col min="8" max="8" width="6.875" customWidth="1"/>
     <col min="10" max="10" width="12.75" customWidth="1"/>
     <col min="11" max="11" width="29.5" customWidth="1"/>
     <col min="12" max="12" width="15.5" customWidth="1"/>
-    <col min="13" max="13" width="5.33203125" style="6" customWidth="1"/>
-    <col min="14" max="14" width="21.08203125" style="6" customWidth="1"/>
-    <col min="15" max="15" width="9.33203125" style="6" customWidth="1"/>
-    <col min="16" max="16" width="13.08203125" style="6" customWidth="1"/>
-    <col min="17" max="17" width="9.33203125" style="6" customWidth="1"/>
+    <col min="13" max="13" width="5.375" style="6" customWidth="1"/>
+    <col min="14" max="14" width="21.125" style="6" customWidth="1"/>
+    <col min="15" max="15" width="9.375" style="6" customWidth="1"/>
+    <col min="16" max="16" width="13.125" style="6" customWidth="1"/>
+    <col min="17" max="17" width="9.375" style="6" customWidth="1"/>
     <col min="18" max="18" width="21.75" style="6" customWidth="1"/>
     <col min="19" max="19" width="21" style="6" customWidth="1"/>
     <col min="20" max="20" width="23" style="6" customWidth="1"/>
     <col min="21" max="21" width="24.25" customWidth="1"/>
-    <col min="22" max="22" width="20.5" customWidth="1"/>
+    <col min="22" max="22" width="11.5" customWidth="1"/>
     <col min="23" max="23" width="11.75" customWidth="1"/>
-    <col min="27" max="27" width="13.58203125" customWidth="1"/>
+    <col min="27" max="27" width="13.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -897,34 +897,34 @@
       <c r="K1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="L1" s="12" t="s">
+      <c r="L1" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="M1" s="12"/>
-      <c r="N1" s="12"/>
-      <c r="O1" s="12"/>
-      <c r="P1" s="12"/>
-      <c r="Q1" s="12"/>
-      <c r="R1" s="12"/>
-      <c r="S1" s="12"/>
-      <c r="T1" s="12"/>
-      <c r="U1" s="12"/>
-      <c r="V1" s="11" t="s">
+      <c r="M1" s="11"/>
+      <c r="N1" s="11"/>
+      <c r="O1" s="11"/>
+      <c r="P1" s="11"/>
+      <c r="Q1" s="11"/>
+      <c r="R1" s="11"/>
+      <c r="S1" s="11"/>
+      <c r="T1" s="11"/>
+      <c r="U1" s="11"/>
+      <c r="V1" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="W1" s="11"/>
-      <c r="X1" s="11"/>
-      <c r="Y1" s="11"/>
-      <c r="Z1" s="11"/>
-      <c r="AA1" s="11"/>
-      <c r="AB1" s="11"/>
-      <c r="AC1" s="11"/>
-      <c r="AD1" s="11"/>
-      <c r="AE1" s="11"/>
-      <c r="AF1" s="11"/>
-      <c r="AG1" s="11"/>
-    </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="W1" s="10"/>
+      <c r="X1" s="10"/>
+      <c r="Y1" s="10"/>
+      <c r="Z1" s="10"/>
+      <c r="AA1" s="10"/>
+      <c r="AB1" s="10"/>
+      <c r="AC1" s="10"/>
+      <c r="AD1" s="10"/>
+      <c r="AE1" s="10"/>
+      <c r="AF1" s="10"/>
+      <c r="AG1" s="10"/>
+    </row>
+    <row r="2" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -958,34 +958,34 @@
       <c r="K2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="L2" s="11" t="s">
+      <c r="L2" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="M2" s="11"/>
-      <c r="N2" s="11"/>
-      <c r="O2" s="11"/>
-      <c r="P2" s="11"/>
-      <c r="Q2" s="11"/>
-      <c r="R2" s="11"/>
-      <c r="S2" s="11"/>
-      <c r="T2" s="11"/>
-      <c r="U2" s="11"/>
-      <c r="V2" s="12" t="s">
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="10"/>
+      <c r="Q2" s="10"/>
+      <c r="R2" s="10"/>
+      <c r="S2" s="10"/>
+      <c r="T2" s="10"/>
+      <c r="U2" s="10"/>
+      <c r="V2" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="W2" s="12"/>
-      <c r="X2" s="12"/>
-      <c r="Y2" s="12"/>
-      <c r="Z2" s="12"/>
-      <c r="AA2" s="12"/>
-      <c r="AB2" s="12"/>
-      <c r="AC2" s="12"/>
-      <c r="AD2" s="12"/>
-      <c r="AE2" s="12"/>
-      <c r="AF2" s="12"/>
-      <c r="AG2" s="12"/>
-    </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="W2" s="11"/>
+      <c r="X2" s="11"/>
+      <c r="Y2" s="11"/>
+      <c r="Z2" s="11"/>
+      <c r="AA2" s="11"/>
+      <c r="AB2" s="11"/>
+      <c r="AC2" s="11"/>
+      <c r="AD2" s="11"/>
+      <c r="AE2" s="11"/>
+      <c r="AF2" s="11"/>
+      <c r="AG2" s="11"/>
+    </row>
+    <row r="3" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -1030,7 +1030,7 @@
       <c r="AC3" s="1"/>
       <c r="AD3" s="1"/>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1047,39 +1047,39 @@
       <c r="L4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="M4" s="11" t="s">
+      <c r="M4" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="N4" s="11"/>
-      <c r="O4" s="11"/>
-      <c r="P4" s="11"/>
-      <c r="Q4" s="11"/>
-      <c r="R4" s="11"/>
-      <c r="S4" s="11"/>
-      <c r="T4" s="11"/>
-      <c r="U4" s="11"/>
+      <c r="N4" s="10"/>
+      <c r="O4" s="10"/>
+      <c r="P4" s="10"/>
+      <c r="Q4" s="10"/>
+      <c r="R4" s="10"/>
+      <c r="S4" s="10"/>
+      <c r="T4" s="10"/>
+      <c r="U4" s="10"/>
       <c r="V4" t="s">
         <v>36</v>
       </c>
       <c r="W4" t="s">
         <v>73</v>
       </c>
-      <c r="X4" s="10" t="s">
+      <c r="X4" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="Y4" s="10"/>
-      <c r="Z4" s="10"/>
-      <c r="AA4" s="10"/>
-      <c r="AB4" s="10"/>
-      <c r="AC4" s="10"/>
-      <c r="AD4" s="10"/>
-      <c r="AE4" s="12" t="s">
+      <c r="Y4" s="13"/>
+      <c r="Z4" s="13"/>
+      <c r="AA4" s="13"/>
+      <c r="AB4" s="13"/>
+      <c r="AC4" s="13"/>
+      <c r="AD4" s="13"/>
+      <c r="AE4" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="AF4" s="12"/>
-      <c r="AG4" s="12"/>
-    </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AF4" s="11"/>
+      <c r="AG4" s="11"/>
+    </row>
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1097,33 +1097,33 @@
       <c r="M5" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="N5" s="11" t="s">
+      <c r="N5" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="O5" s="11"/>
-      <c r="P5" s="11"/>
-      <c r="Q5" s="11"/>
-      <c r="R5" s="10" t="s">
+      <c r="O5" s="10"/>
+      <c r="P5" s="10"/>
+      <c r="Q5" s="10"/>
+      <c r="R5" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="S5" s="10"/>
-      <c r="T5" s="10"/>
-      <c r="U5" s="10"/>
+      <c r="S5" s="13"/>
+      <c r="T5" s="13"/>
+      <c r="U5" s="13"/>
       <c r="X5" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="Y5" s="10" t="s">
+      <c r="Y5" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="Z5" s="10"/>
-      <c r="AA5" s="10" t="s">
+      <c r="Z5" s="13"/>
+      <c r="AA5" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="AB5" s="10"/>
-      <c r="AC5" s="10"/>
-      <c r="AD5" s="10"/>
-    </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AB5" s="13"/>
+      <c r="AC5" s="13"/>
+      <c r="AD5" s="13"/>
+    </row>
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -1141,20 +1141,20 @@
       <c r="M6" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="N6" s="11" t="s">
+      <c r="N6" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="O6" s="11"/>
-      <c r="P6" s="11"/>
-      <c r="Q6" s="11"/>
-      <c r="R6" s="10" t="s">
+      <c r="O6" s="10"/>
+      <c r="P6" s="10"/>
+      <c r="Q6" s="10"/>
+      <c r="R6" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="S6" s="10"/>
-      <c r="T6" s="10"/>
-      <c r="U6" s="10"/>
-    </row>
-    <row r="7" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="S6" s="13"/>
+      <c r="T6" s="13"/>
+      <c r="U6" s="13"/>
+    </row>
+    <row r="7" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
         <v>3</v>
       </c>
@@ -1163,21 +1163,21 @@
       <c r="N7" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="O7" s="13" t="s">
+      <c r="O7" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="P7" s="13"/>
-      <c r="Q7" s="13"/>
+      <c r="P7" s="12"/>
+      <c r="Q7" s="12"/>
       <c r="R7" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="S7" s="13" t="s">
+      <c r="S7" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="T7" s="13"/>
-      <c r="U7" s="13"/>
-    </row>
-    <row r="8" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="T7" s="12"/>
+      <c r="U7" s="12"/>
+    </row>
+    <row r="8" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B8" s="7" t="s">
         <v>96</v>
       </c>
@@ -1221,7 +1221,7 @@
       <c r="W8" s="2"/>
       <c r="AA8" s="2"/>
     </row>
-    <row r="9" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
@@ -1247,7 +1247,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="10" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B10" s="7" t="s">
         <v>95</v>
       </c>
@@ -1304,13 +1304,13 @@
         <v>52</v>
       </c>
     </row>
-    <row r="11" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
       <c r="J11" s="2"/>
     </row>
-    <row r="12" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B12" s="7" t="s">
         <v>94</v>
       </c>
@@ -1364,8 +1364,8 @@
         <v>58</v>
       </c>
     </row>
-    <row r="13" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="14" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B14" s="7" t="s">
         <v>93</v>
       </c>
@@ -1412,8 +1412,8 @@
         <v>67</v>
       </c>
     </row>
-    <row r="15" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="16" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="16" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A16" s="7" t="s">
         <v>17</v>
       </c>
@@ -1442,8 +1442,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="17" spans="1:30" s="7" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="18" spans="1:30" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:30" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="18" spans="1:30" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B18" s="7" t="s">
         <v>91</v>
       </c>
@@ -1490,7 +1490,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="19" spans="1:30" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:30" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="X19" s="7">
         <v>2</v>
       </c>
@@ -1507,7 +1507,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="20" spans="1:30" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:30" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B20" s="7" t="s">
         <v>90</v>
       </c>
@@ -1551,7 +1551,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="22" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>17</v>
       </c>
@@ -1594,6 +1594,12 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="Y5:Z5"/>
+    <mergeCell ref="AA5:AD5"/>
+    <mergeCell ref="V1:AG1"/>
+    <mergeCell ref="V2:AG2"/>
+    <mergeCell ref="X4:AD4"/>
+    <mergeCell ref="AE4:AG4"/>
     <mergeCell ref="L2:U2"/>
     <mergeCell ref="L1:U1"/>
     <mergeCell ref="N6:Q6"/>
@@ -1603,12 +1609,6 @@
     <mergeCell ref="R6:U6"/>
     <mergeCell ref="R5:U5"/>
     <mergeCell ref="M4:U4"/>
-    <mergeCell ref="Y5:Z5"/>
-    <mergeCell ref="AA5:AD5"/>
-    <mergeCell ref="V1:AG1"/>
-    <mergeCell ref="V2:AG2"/>
-    <mergeCell ref="X4:AD4"/>
-    <mergeCell ref="AE4:AG4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/Datas/FoodDatas/FoodData.xlsx
+++ b/Config/Datas/FoodDatas/FoodData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\FoodDatas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA7290A8-4162-4903-89CF-34345CA67B69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDCDFE0E-E211-42D6-AFCD-24DE5C4CCB56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -546,6 +546,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -554,9 +557,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -897,32 +897,32 @@
       <c r="K1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="L1" s="11" t="s">
+      <c r="L1" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="M1" s="11"/>
-      <c r="N1" s="11"/>
-      <c r="O1" s="11"/>
-      <c r="P1" s="11"/>
-      <c r="Q1" s="11"/>
-      <c r="R1" s="11"/>
-      <c r="S1" s="11"/>
-      <c r="T1" s="11"/>
-      <c r="U1" s="11"/>
-      <c r="V1" s="10" t="s">
+      <c r="M1" s="12"/>
+      <c r="N1" s="12"/>
+      <c r="O1" s="12"/>
+      <c r="P1" s="12"/>
+      <c r="Q1" s="12"/>
+      <c r="R1" s="12"/>
+      <c r="S1" s="12"/>
+      <c r="T1" s="12"/>
+      <c r="U1" s="12"/>
+      <c r="V1" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="W1" s="10"/>
-      <c r="X1" s="10"/>
-      <c r="Y1" s="10"/>
-      <c r="Z1" s="10"/>
-      <c r="AA1" s="10"/>
-      <c r="AB1" s="10"/>
-      <c r="AC1" s="10"/>
-      <c r="AD1" s="10"/>
-      <c r="AE1" s="10"/>
-      <c r="AF1" s="10"/>
-      <c r="AG1" s="10"/>
+      <c r="W1" s="11"/>
+      <c r="X1" s="11"/>
+      <c r="Y1" s="11"/>
+      <c r="Z1" s="11"/>
+      <c r="AA1" s="11"/>
+      <c r="AB1" s="11"/>
+      <c r="AC1" s="11"/>
+      <c r="AD1" s="11"/>
+      <c r="AE1" s="11"/>
+      <c r="AF1" s="11"/>
+      <c r="AG1" s="11"/>
     </row>
     <row r="2" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
@@ -958,32 +958,32 @@
       <c r="K2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="L2" s="10" t="s">
+      <c r="L2" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M2" s="10"/>
-      <c r="N2" s="10"/>
-      <c r="O2" s="10"/>
-      <c r="P2" s="10"/>
-      <c r="Q2" s="10"/>
-      <c r="R2" s="10"/>
-      <c r="S2" s="10"/>
-      <c r="T2" s="10"/>
-      <c r="U2" s="10"/>
-      <c r="V2" s="11" t="s">
+      <c r="M2" s="11"/>
+      <c r="N2" s="11"/>
+      <c r="O2" s="11"/>
+      <c r="P2" s="11"/>
+      <c r="Q2" s="11"/>
+      <c r="R2" s="11"/>
+      <c r="S2" s="11"/>
+      <c r="T2" s="11"/>
+      <c r="U2" s="11"/>
+      <c r="V2" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="W2" s="11"/>
-      <c r="X2" s="11"/>
-      <c r="Y2" s="11"/>
-      <c r="Z2" s="11"/>
-      <c r="AA2" s="11"/>
-      <c r="AB2" s="11"/>
-      <c r="AC2" s="11"/>
-      <c r="AD2" s="11"/>
-      <c r="AE2" s="11"/>
-      <c r="AF2" s="11"/>
-      <c r="AG2" s="11"/>
+      <c r="W2" s="12"/>
+      <c r="X2" s="12"/>
+      <c r="Y2" s="12"/>
+      <c r="Z2" s="12"/>
+      <c r="AA2" s="12"/>
+      <c r="AB2" s="12"/>
+      <c r="AC2" s="12"/>
+      <c r="AD2" s="12"/>
+      <c r="AE2" s="12"/>
+      <c r="AF2" s="12"/>
+      <c r="AG2" s="12"/>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
@@ -1047,37 +1047,37 @@
       <c r="L4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="M4" s="10" t="s">
+      <c r="M4" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="N4" s="10"/>
-      <c r="O4" s="10"/>
-      <c r="P4" s="10"/>
-      <c r="Q4" s="10"/>
-      <c r="R4" s="10"/>
-      <c r="S4" s="10"/>
-      <c r="T4" s="10"/>
-      <c r="U4" s="10"/>
+      <c r="N4" s="11"/>
+      <c r="O4" s="11"/>
+      <c r="P4" s="11"/>
+      <c r="Q4" s="11"/>
+      <c r="R4" s="11"/>
+      <c r="S4" s="11"/>
+      <c r="T4" s="11"/>
+      <c r="U4" s="11"/>
       <c r="V4" t="s">
         <v>36</v>
       </c>
       <c r="W4" t="s">
         <v>73</v>
       </c>
-      <c r="X4" s="13" t="s">
+      <c r="X4" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="Y4" s="13"/>
-      <c r="Z4" s="13"/>
-      <c r="AA4" s="13"/>
-      <c r="AB4" s="13"/>
-      <c r="AC4" s="13"/>
-      <c r="AD4" s="13"/>
-      <c r="AE4" s="11" t="s">
+      <c r="Y4" s="10"/>
+      <c r="Z4" s="10"/>
+      <c r="AA4" s="10"/>
+      <c r="AB4" s="10"/>
+      <c r="AC4" s="10"/>
+      <c r="AD4" s="10"/>
+      <c r="AE4" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="AF4" s="11"/>
-      <c r="AG4" s="11"/>
+      <c r="AF4" s="12"/>
+      <c r="AG4" s="12"/>
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
@@ -1097,31 +1097,31 @@
       <c r="M5" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="N5" s="10" t="s">
+      <c r="N5" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="O5" s="10"/>
-      <c r="P5" s="10"/>
-      <c r="Q5" s="10"/>
-      <c r="R5" s="13" t="s">
+      <c r="O5" s="11"/>
+      <c r="P5" s="11"/>
+      <c r="Q5" s="11"/>
+      <c r="R5" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="S5" s="13"/>
-      <c r="T5" s="13"/>
-      <c r="U5" s="13"/>
+      <c r="S5" s="10"/>
+      <c r="T5" s="10"/>
+      <c r="U5" s="10"/>
       <c r="X5" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="Y5" s="13" t="s">
+      <c r="Y5" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="Z5" s="13"/>
-      <c r="AA5" s="13" t="s">
+      <c r="Z5" s="10"/>
+      <c r="AA5" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="AB5" s="13"/>
-      <c r="AC5" s="13"/>
-      <c r="AD5" s="13"/>
+      <c r="AB5" s="10"/>
+      <c r="AC5" s="10"/>
+      <c r="AD5" s="10"/>
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
@@ -1141,18 +1141,18 @@
       <c r="M6" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="N6" s="10" t="s">
+      <c r="N6" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="O6" s="10"/>
-      <c r="P6" s="10"/>
-      <c r="Q6" s="10"/>
-      <c r="R6" s="13" t="s">
+      <c r="O6" s="11"/>
+      <c r="P6" s="11"/>
+      <c r="Q6" s="11"/>
+      <c r="R6" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="S6" s="13"/>
-      <c r="T6" s="13"/>
-      <c r="U6" s="13"/>
+      <c r="S6" s="10"/>
+      <c r="T6" s="10"/>
+      <c r="U6" s="10"/>
     </row>
     <row r="7" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
@@ -1163,19 +1163,19 @@
       <c r="N7" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="O7" s="12" t="s">
+      <c r="O7" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="P7" s="12"/>
-      <c r="Q7" s="12"/>
+      <c r="P7" s="13"/>
+      <c r="Q7" s="13"/>
       <c r="R7" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="S7" s="12" t="s">
+      <c r="S7" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="T7" s="12"/>
-      <c r="U7" s="12"/>
+      <c r="T7" s="13"/>
+      <c r="U7" s="13"/>
     </row>
     <row r="8" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B8" s="7" t="s">
@@ -1285,11 +1285,11 @@
       <c r="N10" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="O10" s="7" t="s">
+      <c r="O10" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="P10" s="7" t="s">
         <v>48</v>
-      </c>
-      <c r="P10" s="9" t="s">
-        <v>51</v>
       </c>
       <c r="Q10" s="7" t="s">
         <v>52</v>
@@ -1594,12 +1594,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="Y5:Z5"/>
-    <mergeCell ref="AA5:AD5"/>
-    <mergeCell ref="V1:AG1"/>
-    <mergeCell ref="V2:AG2"/>
-    <mergeCell ref="X4:AD4"/>
-    <mergeCell ref="AE4:AG4"/>
     <mergeCell ref="L2:U2"/>
     <mergeCell ref="L1:U1"/>
     <mergeCell ref="N6:Q6"/>
@@ -1609,6 +1603,12 @@
     <mergeCell ref="R6:U6"/>
     <mergeCell ref="R5:U5"/>
     <mergeCell ref="M4:U4"/>
+    <mergeCell ref="Y5:Z5"/>
+    <mergeCell ref="AA5:AD5"/>
+    <mergeCell ref="V1:AG1"/>
+    <mergeCell ref="V2:AG2"/>
+    <mergeCell ref="X4:AD4"/>
+    <mergeCell ref="AE4:AG4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/Datas/FoodDatas/FoodData.xlsx
+++ b/Config/Datas/FoodDatas/FoodData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\FoodDatas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDCDFE0E-E211-42D6-AFCD-24DE5C4CCB56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07D32490-3A6C-4247-A053-83029EB6BBCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -546,9 +546,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -557,6 +554,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -897,32 +897,32 @@
       <c r="K1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="L1" s="12" t="s">
+      <c r="L1" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="M1" s="12"/>
-      <c r="N1" s="12"/>
-      <c r="O1" s="12"/>
-      <c r="P1" s="12"/>
-      <c r="Q1" s="12"/>
-      <c r="R1" s="12"/>
-      <c r="S1" s="12"/>
-      <c r="T1" s="12"/>
-      <c r="U1" s="12"/>
-      <c r="V1" s="11" t="s">
+      <c r="M1" s="11"/>
+      <c r="N1" s="11"/>
+      <c r="O1" s="11"/>
+      <c r="P1" s="11"/>
+      <c r="Q1" s="11"/>
+      <c r="R1" s="11"/>
+      <c r="S1" s="11"/>
+      <c r="T1" s="11"/>
+      <c r="U1" s="11"/>
+      <c r="V1" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="W1" s="11"/>
-      <c r="X1" s="11"/>
-      <c r="Y1" s="11"/>
-      <c r="Z1" s="11"/>
-      <c r="AA1" s="11"/>
-      <c r="AB1" s="11"/>
-      <c r="AC1" s="11"/>
-      <c r="AD1" s="11"/>
-      <c r="AE1" s="11"/>
-      <c r="AF1" s="11"/>
-      <c r="AG1" s="11"/>
+      <c r="W1" s="10"/>
+      <c r="X1" s="10"/>
+      <c r="Y1" s="10"/>
+      <c r="Z1" s="10"/>
+      <c r="AA1" s="10"/>
+      <c r="AB1" s="10"/>
+      <c r="AC1" s="10"/>
+      <c r="AD1" s="10"/>
+      <c r="AE1" s="10"/>
+      <c r="AF1" s="10"/>
+      <c r="AG1" s="10"/>
     </row>
     <row r="2" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
@@ -958,32 +958,32 @@
       <c r="K2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="L2" s="11" t="s">
+      <c r="L2" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="M2" s="11"/>
-      <c r="N2" s="11"/>
-      <c r="O2" s="11"/>
-      <c r="P2" s="11"/>
-      <c r="Q2" s="11"/>
-      <c r="R2" s="11"/>
-      <c r="S2" s="11"/>
-      <c r="T2" s="11"/>
-      <c r="U2" s="11"/>
-      <c r="V2" s="12" t="s">
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="10"/>
+      <c r="Q2" s="10"/>
+      <c r="R2" s="10"/>
+      <c r="S2" s="10"/>
+      <c r="T2" s="10"/>
+      <c r="U2" s="10"/>
+      <c r="V2" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="W2" s="12"/>
-      <c r="X2" s="12"/>
-      <c r="Y2" s="12"/>
-      <c r="Z2" s="12"/>
-      <c r="AA2" s="12"/>
-      <c r="AB2" s="12"/>
-      <c r="AC2" s="12"/>
-      <c r="AD2" s="12"/>
-      <c r="AE2" s="12"/>
-      <c r="AF2" s="12"/>
-      <c r="AG2" s="12"/>
+      <c r="W2" s="11"/>
+      <c r="X2" s="11"/>
+      <c r="Y2" s="11"/>
+      <c r="Z2" s="11"/>
+      <c r="AA2" s="11"/>
+      <c r="AB2" s="11"/>
+      <c r="AC2" s="11"/>
+      <c r="AD2" s="11"/>
+      <c r="AE2" s="11"/>
+      <c r="AF2" s="11"/>
+      <c r="AG2" s="11"/>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
@@ -1047,37 +1047,37 @@
       <c r="L4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="M4" s="11" t="s">
+      <c r="M4" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="N4" s="11"/>
-      <c r="O4" s="11"/>
-      <c r="P4" s="11"/>
-      <c r="Q4" s="11"/>
-      <c r="R4" s="11"/>
-      <c r="S4" s="11"/>
-      <c r="T4" s="11"/>
-      <c r="U4" s="11"/>
+      <c r="N4" s="10"/>
+      <c r="O4" s="10"/>
+      <c r="P4" s="10"/>
+      <c r="Q4" s="10"/>
+      <c r="R4" s="10"/>
+      <c r="S4" s="10"/>
+      <c r="T4" s="10"/>
+      <c r="U4" s="10"/>
       <c r="V4" t="s">
         <v>36</v>
       </c>
       <c r="W4" t="s">
         <v>73</v>
       </c>
-      <c r="X4" s="10" t="s">
+      <c r="X4" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="Y4" s="10"/>
-      <c r="Z4" s="10"/>
-      <c r="AA4" s="10"/>
-      <c r="AB4" s="10"/>
-      <c r="AC4" s="10"/>
-      <c r="AD4" s="10"/>
-      <c r="AE4" s="12" t="s">
+      <c r="Y4" s="13"/>
+      <c r="Z4" s="13"/>
+      <c r="AA4" s="13"/>
+      <c r="AB4" s="13"/>
+      <c r="AC4" s="13"/>
+      <c r="AD4" s="13"/>
+      <c r="AE4" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="AF4" s="12"/>
-      <c r="AG4" s="12"/>
+      <c r="AF4" s="11"/>
+      <c r="AG4" s="11"/>
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
@@ -1097,31 +1097,31 @@
       <c r="M5" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="N5" s="11" t="s">
+      <c r="N5" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="O5" s="11"/>
-      <c r="P5" s="11"/>
-      <c r="Q5" s="11"/>
-      <c r="R5" s="10" t="s">
+      <c r="O5" s="10"/>
+      <c r="P5" s="10"/>
+      <c r="Q5" s="10"/>
+      <c r="R5" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="S5" s="10"/>
-      <c r="T5" s="10"/>
-      <c r="U5" s="10"/>
+      <c r="S5" s="13"/>
+      <c r="T5" s="13"/>
+      <c r="U5" s="13"/>
       <c r="X5" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="Y5" s="10" t="s">
+      <c r="Y5" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="Z5" s="10"/>
-      <c r="AA5" s="10" t="s">
+      <c r="Z5" s="13"/>
+      <c r="AA5" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="AB5" s="10"/>
-      <c r="AC5" s="10"/>
-      <c r="AD5" s="10"/>
+      <c r="AB5" s="13"/>
+      <c r="AC5" s="13"/>
+      <c r="AD5" s="13"/>
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
@@ -1141,18 +1141,18 @@
       <c r="M6" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="N6" s="11" t="s">
+      <c r="N6" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="O6" s="11"/>
-      <c r="P6" s="11"/>
-      <c r="Q6" s="11"/>
-      <c r="R6" s="10" t="s">
+      <c r="O6" s="10"/>
+      <c r="P6" s="10"/>
+      <c r="Q6" s="10"/>
+      <c r="R6" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="S6" s="10"/>
-      <c r="T6" s="10"/>
-      <c r="U6" s="10"/>
+      <c r="S6" s="13"/>
+      <c r="T6" s="13"/>
+      <c r="U6" s="13"/>
     </row>
     <row r="7" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
@@ -1163,19 +1163,19 @@
       <c r="N7" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="O7" s="13" t="s">
+      <c r="O7" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="P7" s="13"/>
-      <c r="Q7" s="13"/>
+      <c r="P7" s="12"/>
+      <c r="Q7" s="12"/>
       <c r="R7" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="S7" s="13" t="s">
+      <c r="S7" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="T7" s="13"/>
-      <c r="U7" s="13"/>
+      <c r="T7" s="12"/>
+      <c r="U7" s="12"/>
     </row>
     <row r="8" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B8" s="7" t="s">
@@ -1594,6 +1594,12 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="Y5:Z5"/>
+    <mergeCell ref="AA5:AD5"/>
+    <mergeCell ref="V1:AG1"/>
+    <mergeCell ref="V2:AG2"/>
+    <mergeCell ref="X4:AD4"/>
+    <mergeCell ref="AE4:AG4"/>
     <mergeCell ref="L2:U2"/>
     <mergeCell ref="L1:U1"/>
     <mergeCell ref="N6:Q6"/>
@@ -1603,12 +1609,6 @@
     <mergeCell ref="R6:U6"/>
     <mergeCell ref="R5:U5"/>
     <mergeCell ref="M4:U4"/>
-    <mergeCell ref="Y5:Z5"/>
-    <mergeCell ref="AA5:AD5"/>
-    <mergeCell ref="V1:AG1"/>
-    <mergeCell ref="V2:AG2"/>
-    <mergeCell ref="X4:AD4"/>
-    <mergeCell ref="AE4:AG4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/Datas/FoodDatas/FoodData.xlsx
+++ b/Config/Datas/FoodDatas/FoodData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\FoodDatas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07D32490-3A6C-4247-A053-83029EB6BBCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08BBE797-446E-46B7-81C8-315F2A8EA6A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="97">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -115,18 +115,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>鸡肉</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>肉类</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>一只鸡！</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>sprite</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -303,18 +291,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>面包</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>一片面包！</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bread</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>SE_监听事件</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -395,14 +371,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>bread</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>chicken</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>beer</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -423,35 +391,27 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>fish</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>小鱼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>很滑很活泼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Fish</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>被选中时\n每与另一个樱桃相邻，则烧烤属性+2/+2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>完成烤串后\n小鱼会选择一个方向冲到底\n增加自身等同于移动格数的属性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>完成烤串后\n小虾会选择一个方向移动\n并增加属性+1/+1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>周围空位,TRUE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>零食</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>曲奇饼干</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cookie</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -546,6 +506,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -554,9 +517,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -838,7 +798,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AG22"/>
+  <dimension ref="A1:AG18"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="9" customWidth="1"/>
@@ -880,10 +840,10 @@
         <v>6</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>7</v>
@@ -892,37 +852,37 @@
         <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="L1" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="M1" s="11"/>
-      <c r="N1" s="11"/>
-      <c r="O1" s="11"/>
-      <c r="P1" s="11"/>
-      <c r="Q1" s="11"/>
-      <c r="R1" s="11"/>
-      <c r="S1" s="11"/>
-      <c r="T1" s="11"/>
-      <c r="U1" s="11"/>
-      <c r="V1" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="W1" s="10"/>
-      <c r="X1" s="10"/>
-      <c r="Y1" s="10"/>
-      <c r="Z1" s="10"/>
-      <c r="AA1" s="10"/>
-      <c r="AB1" s="10"/>
-      <c r="AC1" s="10"/>
-      <c r="AD1" s="10"/>
-      <c r="AE1" s="10"/>
-      <c r="AF1" s="10"/>
-      <c r="AG1" s="10"/>
+        <v>30</v>
+      </c>
+      <c r="L1" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="M1" s="12"/>
+      <c r="N1" s="12"/>
+      <c r="O1" s="12"/>
+      <c r="P1" s="12"/>
+      <c r="Q1" s="12"/>
+      <c r="R1" s="12"/>
+      <c r="S1" s="12"/>
+      <c r="T1" s="12"/>
+      <c r="U1" s="12"/>
+      <c r="V1" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="W1" s="11"/>
+      <c r="X1" s="11"/>
+      <c r="Y1" s="11"/>
+      <c r="Z1" s="11"/>
+      <c r="AA1" s="11"/>
+      <c r="AB1" s="11"/>
+      <c r="AC1" s="11"/>
+      <c r="AD1" s="11"/>
+      <c r="AE1" s="11"/>
+      <c r="AF1" s="11"/>
+      <c r="AG1" s="11"/>
     </row>
     <row r="2" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
@@ -941,10 +901,10 @@
         <v>9</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>10</v>
@@ -958,32 +918,32 @@
       <c r="K2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="L2" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="M2" s="10"/>
-      <c r="N2" s="10"/>
-      <c r="O2" s="10"/>
-      <c r="P2" s="10"/>
-      <c r="Q2" s="10"/>
-      <c r="R2" s="10"/>
-      <c r="S2" s="10"/>
-      <c r="T2" s="10"/>
-      <c r="U2" s="10"/>
-      <c r="V2" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="W2" s="11"/>
-      <c r="X2" s="11"/>
-      <c r="Y2" s="11"/>
-      <c r="Z2" s="11"/>
-      <c r="AA2" s="11"/>
-      <c r="AB2" s="11"/>
-      <c r="AC2" s="11"/>
-      <c r="AD2" s="11"/>
-      <c r="AE2" s="11"/>
-      <c r="AF2" s="11"/>
-      <c r="AG2" s="11"/>
+      <c r="L2" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="M2" s="11"/>
+      <c r="N2" s="11"/>
+      <c r="O2" s="11"/>
+      <c r="P2" s="11"/>
+      <c r="Q2" s="11"/>
+      <c r="R2" s="11"/>
+      <c r="S2" s="11"/>
+      <c r="T2" s="11"/>
+      <c r="U2" s="11"/>
+      <c r="V2" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="W2" s="12"/>
+      <c r="X2" s="12"/>
+      <c r="Y2" s="12"/>
+      <c r="Z2" s="12"/>
+      <c r="AA2" s="12"/>
+      <c r="AB2" s="12"/>
+      <c r="AC2" s="12"/>
+      <c r="AD2" s="12"/>
+      <c r="AE2" s="12"/>
+      <c r="AF2" s="12"/>
+      <c r="AG2" s="12"/>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
@@ -1002,7 +962,7 @@
         <v>14</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="1" t="s">
@@ -1012,10 +972,10 @@
         <v>16</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="L3" s="1"/>
       <c r="M3" s="5"/>
@@ -1047,37 +1007,37 @@
       <c r="L4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="M4" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="N4" s="10"/>
-      <c r="O4" s="10"/>
-      <c r="P4" s="10"/>
-      <c r="Q4" s="10"/>
-      <c r="R4" s="10"/>
-      <c r="S4" s="10"/>
-      <c r="T4" s="10"/>
-      <c r="U4" s="10"/>
+      <c r="M4" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="N4" s="11"/>
+      <c r="O4" s="11"/>
+      <c r="P4" s="11"/>
+      <c r="Q4" s="11"/>
+      <c r="R4" s="11"/>
+      <c r="S4" s="11"/>
+      <c r="T4" s="11"/>
+      <c r="U4" s="11"/>
       <c r="V4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="W4" t="s">
-        <v>73</v>
-      </c>
-      <c r="X4" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="Y4" s="13"/>
-      <c r="Z4" s="13"/>
-      <c r="AA4" s="13"/>
-      <c r="AB4" s="13"/>
-      <c r="AC4" s="13"/>
-      <c r="AD4" s="13"/>
-      <c r="AE4" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="AF4" s="11"/>
-      <c r="AG4" s="11"/>
+        <v>67</v>
+      </c>
+      <c r="X4" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y4" s="10"/>
+      <c r="Z4" s="10"/>
+      <c r="AA4" s="10"/>
+      <c r="AB4" s="10"/>
+      <c r="AC4" s="10"/>
+      <c r="AD4" s="10"/>
+      <c r="AE4" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="AF4" s="12"/>
+      <c r="AG4" s="12"/>
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
@@ -1097,31 +1057,31 @@
       <c r="M5" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="N5" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="O5" s="10"/>
-      <c r="P5" s="10"/>
-      <c r="Q5" s="10"/>
-      <c r="R5" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="S5" s="13"/>
-      <c r="T5" s="13"/>
-      <c r="U5" s="13"/>
+      <c r="N5" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="O5" s="11"/>
+      <c r="P5" s="11"/>
+      <c r="Q5" s="11"/>
+      <c r="R5" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="S5" s="10"/>
+      <c r="T5" s="10"/>
+      <c r="U5" s="10"/>
       <c r="X5" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="Y5" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="Z5" s="13"/>
-      <c r="AA5" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="AB5" s="13"/>
-      <c r="AC5" s="13"/>
-      <c r="AD5" s="13"/>
+      <c r="Y5" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z5" s="10"/>
+      <c r="AA5" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="AB5" s="10"/>
+      <c r="AC5" s="10"/>
+      <c r="AD5" s="10"/>
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
@@ -1141,18 +1101,18 @@
       <c r="M6" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="N6" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="O6" s="10"/>
-      <c r="P6" s="10"/>
-      <c r="Q6" s="10"/>
-      <c r="R6" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="S6" s="13"/>
-      <c r="T6" s="13"/>
-      <c r="U6" s="13"/>
+      <c r="N6" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="O6" s="11"/>
+      <c r="P6" s="11"/>
+      <c r="Q6" s="11"/>
+      <c r="R6" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="S6" s="10"/>
+      <c r="T6" s="10"/>
+      <c r="U6" s="10"/>
     </row>
     <row r="7" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
@@ -1161,25 +1121,25 @@
       <c r="K7" s="8"/>
       <c r="L7" s="8"/>
       <c r="N7" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="O7" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="P7" s="12"/>
-      <c r="Q7" s="12"/>
+        <v>33</v>
+      </c>
+      <c r="O7" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="P7" s="13"/>
+      <c r="Q7" s="13"/>
       <c r="R7" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="S7" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="T7" s="12"/>
-      <c r="U7" s="12"/>
+        <v>33</v>
+      </c>
+      <c r="S7" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="T7" s="13"/>
+      <c r="U7" s="13"/>
     </row>
     <row r="8" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B8" s="7" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>18</v>
@@ -1201,22 +1161,22 @@
         <v>2</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="M8" s="7">
         <v>1</v>
       </c>
       <c r="R8" s="9" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="S8" s="7" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="W8" s="2"/>
       <c r="AA8" s="2"/>
@@ -1229,33 +1189,33 @@
       <c r="I9" s="8"/>
       <c r="J9" s="2"/>
       <c r="L9" s="7" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="M9" s="7">
         <v>1</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="S9" s="7" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="T9" s="7" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="U9" s="7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B10" s="7" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>21</v>
@@ -1271,37 +1231,37 @@
         <v>1</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="M10" s="7">
         <v>1</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="O10" s="9" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="P10" s="7" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="Q10" s="7" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="S10" s="7" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="T10" s="7" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.2">
@@ -1312,13 +1272,13 @@
     </row>
     <row r="12" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B12" s="7" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>21</v>
@@ -1334,52 +1294,52 @@
         <v>2</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="M12" s="7">
         <v>1</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="O12" s="7" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="P12" s="7">
         <v>2</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="S12" s="7" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="T12" s="7" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="14" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B14" s="7" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>22</v>
+        <v>95</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>24</v>
+        <v>95</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>23</v>
+        <v>94</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G14" s="2">
         <v>1</v>
@@ -1391,215 +1351,138 @@
         <v>2</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="M14" s="7">
         <v>1</v>
       </c>
       <c r="R14" s="7" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="S14" s="7" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="16" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="7" t="s">
-        <v>17</v>
-      </c>
       <c r="B16" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G16" s="7">
+        <v>1</v>
+      </c>
+      <c r="H16" s="7">
+        <v>1</v>
+      </c>
+      <c r="I16" s="7">
+        <v>1</v>
+      </c>
+      <c r="J16" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="K16" t="s">
         <v>92</v>
       </c>
-      <c r="C16" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G16" s="7">
-        <v>1</v>
-      </c>
-      <c r="H16" s="7">
-        <v>1</v>
-      </c>
-      <c r="I16" s="7">
-        <v>1</v>
-      </c>
-      <c r="J16" s="7" t="s">
+      <c r="V16" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="W16" s="2" t="s">
         <v>71</v>
       </c>
+      <c r="X16" s="7">
+        <v>1</v>
+      </c>
+      <c r="AA16" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="AB16" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AC16" s="7" t="s">
+        <v>93</v>
+      </c>
     </row>
-    <row r="17" spans="1:30" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="18" spans="1:30" s="7" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:30" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="X17" s="7">
+        <v>2</v>
+      </c>
+      <c r="AA17" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="AB17" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="AC17" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="AD17" s="7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="18" spans="2:30" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B18" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G18" s="7">
+        <v>2</v>
+      </c>
+      <c r="H18" s="7">
+        <v>2</v>
+      </c>
+      <c r="I18" s="7">
+        <v>2</v>
+      </c>
+      <c r="J18" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="K18" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="C18" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="G18" s="7">
-        <v>1</v>
-      </c>
-      <c r="H18" s="7">
-        <v>1</v>
-      </c>
-      <c r="I18" s="7">
-        <v>1</v>
-      </c>
-      <c r="J18" s="7" t="s">
+      <c r="L18" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="M18" s="7">
+        <v>1</v>
+      </c>
+      <c r="R18" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="S18" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="T18" s="2" t="s">
         <v>83</v>
-      </c>
-      <c r="K18" t="s">
-        <v>105</v>
-      </c>
-      <c r="V18" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="W18" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="X18" s="7">
-        <v>1</v>
-      </c>
-      <c r="AA18" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="AB18" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="AC18" s="7" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="19" spans="1:30" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="X19" s="7">
-        <v>2</v>
-      </c>
-      <c r="AA19" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="AB19" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="AC19" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="AD19" s="7" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="20" spans="1:30" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G20" s="7">
-        <v>2</v>
-      </c>
-      <c r="H20" s="7">
-        <v>2</v>
-      </c>
-      <c r="I20" s="7">
-        <v>2</v>
-      </c>
-      <c r="J20" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="K20" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="L20" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="M20" s="7">
-        <v>1</v>
-      </c>
-      <c r="R20" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="S20" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="T20" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="22" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>17</v>
-      </c>
-      <c r="B22" t="s">
-        <v>99</v>
-      </c>
-      <c r="C22" t="s">
-        <v>100</v>
-      </c>
-      <c r="D22" t="s">
-        <v>101</v>
-      </c>
-      <c r="E22" t="s">
-        <v>82</v>
-      </c>
-      <c r="G22">
-        <v>2</v>
-      </c>
-      <c r="H22">
-        <v>1</v>
-      </c>
-      <c r="I22">
-        <v>1</v>
-      </c>
-      <c r="J22" t="s">
-        <v>102</v>
-      </c>
-      <c r="K22" t="s">
-        <v>104</v>
-      </c>
-      <c r="V22" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="W22" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="X22" s="7">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="Y5:Z5"/>
-    <mergeCell ref="AA5:AD5"/>
-    <mergeCell ref="V1:AG1"/>
-    <mergeCell ref="V2:AG2"/>
-    <mergeCell ref="X4:AD4"/>
-    <mergeCell ref="AE4:AG4"/>
     <mergeCell ref="L2:U2"/>
     <mergeCell ref="L1:U1"/>
     <mergeCell ref="N6:Q6"/>
@@ -1609,6 +1492,12 @@
     <mergeCell ref="R6:U6"/>
     <mergeCell ref="R5:U5"/>
     <mergeCell ref="M4:U4"/>
+    <mergeCell ref="Y5:Z5"/>
+    <mergeCell ref="AA5:AD5"/>
+    <mergeCell ref="V1:AG1"/>
+    <mergeCell ref="V2:AG2"/>
+    <mergeCell ref="X4:AD4"/>
+    <mergeCell ref="AE4:AG4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/Datas/FoodDatas/FoodData.xlsx
+++ b/Config/Datas/FoodDatas/FoodData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\FoodDatas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08BBE797-446E-46B7-81C8-315F2A8EA6A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAB12E69-04EF-4FB4-A739-D1D455D06F79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1155,10 +1155,10 @@
         <v>1</v>
       </c>
       <c r="H8" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I8" s="8">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -1224,11 +1224,11 @@
       <c r="G10" s="2">
         <v>1</v>
       </c>
-      <c r="H10" s="7">
-        <v>2</v>
-      </c>
-      <c r="I10" s="7">
-        <v>1</v>
+      <c r="H10" s="2">
+        <v>5</v>
+      </c>
+      <c r="I10" s="8">
+        <v>5</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>25</v>
@@ -1287,11 +1287,11 @@
       <c r="G12" s="2">
         <v>1</v>
       </c>
-      <c r="H12" s="7">
-        <v>2</v>
-      </c>
-      <c r="I12" s="7">
-        <v>2</v>
+      <c r="H12" s="2">
+        <v>5</v>
+      </c>
+      <c r="I12" s="8">
+        <v>5</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>26</v>
@@ -1344,11 +1344,11 @@
       <c r="G14" s="2">
         <v>1</v>
       </c>
-      <c r="H14" s="7">
-        <v>1</v>
-      </c>
-      <c r="I14" s="7">
-        <v>2</v>
+      <c r="H14" s="2">
+        <v>5</v>
+      </c>
+      <c r="I14" s="8">
+        <v>5</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>27</v>
@@ -1389,11 +1389,11 @@
       <c r="G16" s="7">
         <v>1</v>
       </c>
-      <c r="H16" s="7">
-        <v>1</v>
-      </c>
-      <c r="I16" s="7">
-        <v>1</v>
+      <c r="H16" s="2">
+        <v>5</v>
+      </c>
+      <c r="I16" s="8">
+        <v>5</v>
       </c>
       <c r="J16" s="7" t="s">
         <v>77</v>
@@ -1453,11 +1453,11 @@
       <c r="G18" s="7">
         <v>2</v>
       </c>
-      <c r="H18" s="7">
-        <v>2</v>
-      </c>
-      <c r="I18" s="7">
-        <v>2</v>
+      <c r="H18" s="2">
+        <v>5</v>
+      </c>
+      <c r="I18" s="8">
+        <v>5</v>
       </c>
       <c r="J18" s="7" t="s">
         <v>81</v>

--- a/Config/Datas/FoodDatas/FoodData.xlsx
+++ b/Config/Datas/FoodDatas/FoodData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\FoodDatas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAB12E69-04EF-4FB4-A739-D1D455D06F79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{778422D3-20D5-4F11-8407-23D1326E438F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Config/Datas/FoodDatas/FoodData.xlsx
+++ b/Config/Datas/FoodDatas/FoodData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\FoodDatas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{778422D3-20D5-4F11-8407-23D1326E438F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{828F4FA2-3BD7-4E07-B44C-A143A7C340D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Config/Datas/FoodDatas/FoodData.xlsx
+++ b/Config/Datas/FoodDatas/FoodData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\FoodDatas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{828F4FA2-3BD7-4E07-B44C-A143A7C340D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E936F4DB-CD58-4D72-835E-6C26E1CD657F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="104">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -412,6 +412,34 @@
   </si>
   <si>
     <t>cookie</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>orio</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>奥利奥</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>夹心饼干</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bread</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>烤串构建后</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Condition_位于首尾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DV_值,5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -506,9 +534,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -517,6 +542,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -798,7 +826,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AG18"/>
+  <dimension ref="A1:AG20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="9" customWidth="1"/>
@@ -857,32 +885,32 @@
       <c r="K1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="L1" s="12" t="s">
+      <c r="L1" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="M1" s="12"/>
-      <c r="N1" s="12"/>
-      <c r="O1" s="12"/>
-      <c r="P1" s="12"/>
-      <c r="Q1" s="12"/>
-      <c r="R1" s="12"/>
-      <c r="S1" s="12"/>
-      <c r="T1" s="12"/>
-      <c r="U1" s="12"/>
-      <c r="V1" s="11" t="s">
+      <c r="M1" s="11"/>
+      <c r="N1" s="11"/>
+      <c r="O1" s="11"/>
+      <c r="P1" s="11"/>
+      <c r="Q1" s="11"/>
+      <c r="R1" s="11"/>
+      <c r="S1" s="11"/>
+      <c r="T1" s="11"/>
+      <c r="U1" s="11"/>
+      <c r="V1" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="W1" s="11"/>
-      <c r="X1" s="11"/>
-      <c r="Y1" s="11"/>
-      <c r="Z1" s="11"/>
-      <c r="AA1" s="11"/>
-      <c r="AB1" s="11"/>
-      <c r="AC1" s="11"/>
-      <c r="AD1" s="11"/>
-      <c r="AE1" s="11"/>
-      <c r="AF1" s="11"/>
-      <c r="AG1" s="11"/>
+      <c r="W1" s="10"/>
+      <c r="X1" s="10"/>
+      <c r="Y1" s="10"/>
+      <c r="Z1" s="10"/>
+      <c r="AA1" s="10"/>
+      <c r="AB1" s="10"/>
+      <c r="AC1" s="10"/>
+      <c r="AD1" s="10"/>
+      <c r="AE1" s="10"/>
+      <c r="AF1" s="10"/>
+      <c r="AG1" s="10"/>
     </row>
     <row r="2" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
@@ -918,32 +946,32 @@
       <c r="K2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="L2" s="11" t="s">
+      <c r="L2" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="M2" s="11"/>
-      <c r="N2" s="11"/>
-      <c r="O2" s="11"/>
-      <c r="P2" s="11"/>
-      <c r="Q2" s="11"/>
-      <c r="R2" s="11"/>
-      <c r="S2" s="11"/>
-      <c r="T2" s="11"/>
-      <c r="U2" s="11"/>
-      <c r="V2" s="12" t="s">
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="10"/>
+      <c r="Q2" s="10"/>
+      <c r="R2" s="10"/>
+      <c r="S2" s="10"/>
+      <c r="T2" s="10"/>
+      <c r="U2" s="10"/>
+      <c r="V2" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="W2" s="12"/>
-      <c r="X2" s="12"/>
-      <c r="Y2" s="12"/>
-      <c r="Z2" s="12"/>
-      <c r="AA2" s="12"/>
-      <c r="AB2" s="12"/>
-      <c r="AC2" s="12"/>
-      <c r="AD2" s="12"/>
-      <c r="AE2" s="12"/>
-      <c r="AF2" s="12"/>
-      <c r="AG2" s="12"/>
+      <c r="W2" s="11"/>
+      <c r="X2" s="11"/>
+      <c r="Y2" s="11"/>
+      <c r="Z2" s="11"/>
+      <c r="AA2" s="11"/>
+      <c r="AB2" s="11"/>
+      <c r="AC2" s="11"/>
+      <c r="AD2" s="11"/>
+      <c r="AE2" s="11"/>
+      <c r="AF2" s="11"/>
+      <c r="AG2" s="11"/>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
@@ -1007,37 +1035,37 @@
       <c r="L4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="M4" s="11" t="s">
+      <c r="M4" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="N4" s="11"/>
-      <c r="O4" s="11"/>
-      <c r="P4" s="11"/>
-      <c r="Q4" s="11"/>
-      <c r="R4" s="11"/>
-      <c r="S4" s="11"/>
-      <c r="T4" s="11"/>
-      <c r="U4" s="11"/>
+      <c r="N4" s="10"/>
+      <c r="O4" s="10"/>
+      <c r="P4" s="10"/>
+      <c r="Q4" s="10"/>
+      <c r="R4" s="10"/>
+      <c r="S4" s="10"/>
+      <c r="T4" s="10"/>
+      <c r="U4" s="10"/>
       <c r="V4" t="s">
         <v>33</v>
       </c>
       <c r="W4" t="s">
         <v>67</v>
       </c>
-      <c r="X4" s="10" t="s">
+      <c r="X4" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="Y4" s="10"/>
-      <c r="Z4" s="10"/>
-      <c r="AA4" s="10"/>
-      <c r="AB4" s="10"/>
-      <c r="AC4" s="10"/>
-      <c r="AD4" s="10"/>
-      <c r="AE4" s="12" t="s">
+      <c r="Y4" s="13"/>
+      <c r="Z4" s="13"/>
+      <c r="AA4" s="13"/>
+      <c r="AB4" s="13"/>
+      <c r="AC4" s="13"/>
+      <c r="AD4" s="13"/>
+      <c r="AE4" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="AF4" s="12"/>
-      <c r="AG4" s="12"/>
+      <c r="AF4" s="11"/>
+      <c r="AG4" s="11"/>
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
@@ -1057,31 +1085,31 @@
       <c r="M5" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="N5" s="11" t="s">
+      <c r="N5" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="O5" s="11"/>
-      <c r="P5" s="11"/>
-      <c r="Q5" s="11"/>
-      <c r="R5" s="10" t="s">
+      <c r="O5" s="10"/>
+      <c r="P5" s="10"/>
+      <c r="Q5" s="10"/>
+      <c r="R5" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="S5" s="10"/>
-      <c r="T5" s="10"/>
-      <c r="U5" s="10"/>
+      <c r="S5" s="13"/>
+      <c r="T5" s="13"/>
+      <c r="U5" s="13"/>
       <c r="X5" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="Y5" s="10" t="s">
+      <c r="Y5" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="Z5" s="10"/>
-      <c r="AA5" s="10" t="s">
+      <c r="Z5" s="13"/>
+      <c r="AA5" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="AB5" s="10"/>
-      <c r="AC5" s="10"/>
-      <c r="AD5" s="10"/>
+      <c r="AB5" s="13"/>
+      <c r="AC5" s="13"/>
+      <c r="AD5" s="13"/>
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
@@ -1101,18 +1129,18 @@
       <c r="M6" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="N6" s="11" t="s">
+      <c r="N6" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="O6" s="11"/>
-      <c r="P6" s="11"/>
-      <c r="Q6" s="11"/>
-      <c r="R6" s="10" t="s">
+      <c r="O6" s="10"/>
+      <c r="P6" s="10"/>
+      <c r="Q6" s="10"/>
+      <c r="R6" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="S6" s="10"/>
-      <c r="T6" s="10"/>
-      <c r="U6" s="10"/>
+      <c r="S6" s="13"/>
+      <c r="T6" s="13"/>
+      <c r="U6" s="13"/>
     </row>
     <row r="7" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
@@ -1123,19 +1151,19 @@
       <c r="N7" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="O7" s="13" t="s">
+      <c r="O7" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="P7" s="13"/>
-      <c r="Q7" s="13"/>
+      <c r="P7" s="12"/>
+      <c r="Q7" s="12"/>
       <c r="R7" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="S7" s="13" t="s">
+      <c r="S7" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="T7" s="13"/>
-      <c r="U7" s="13"/>
+      <c r="T7" s="12"/>
+      <c r="U7" s="12"/>
     </row>
     <row r="8" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B8" s="7" t="s">
@@ -1481,8 +1509,61 @@
         <v>83</v>
       </c>
     </row>
+    <row r="20" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="B20" t="s">
+        <v>97</v>
+      </c>
+      <c r="C20" t="s">
+        <v>98</v>
+      </c>
+      <c r="D20" t="s">
+        <v>99</v>
+      </c>
+      <c r="E20" t="s">
+        <v>94</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+      <c r="H20">
+        <v>5</v>
+      </c>
+      <c r="I20">
+        <v>5</v>
+      </c>
+      <c r="J20" t="s">
+        <v>100</v>
+      </c>
+      <c r="L20" t="s">
+        <v>101</v>
+      </c>
+      <c r="M20" s="6">
+        <v>1</v>
+      </c>
+      <c r="N20" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="O20" s="6">
+        <v>0</v>
+      </c>
+      <c r="R20" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="S20" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="T20" s="7" t="s">
+        <v>103</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="Y5:Z5"/>
+    <mergeCell ref="AA5:AD5"/>
+    <mergeCell ref="V1:AG1"/>
+    <mergeCell ref="V2:AG2"/>
+    <mergeCell ref="X4:AD4"/>
+    <mergeCell ref="AE4:AG4"/>
     <mergeCell ref="L2:U2"/>
     <mergeCell ref="L1:U1"/>
     <mergeCell ref="N6:Q6"/>
@@ -1492,12 +1573,6 @@
     <mergeCell ref="R6:U6"/>
     <mergeCell ref="R5:U5"/>
     <mergeCell ref="M4:U4"/>
-    <mergeCell ref="Y5:Z5"/>
-    <mergeCell ref="AA5:AD5"/>
-    <mergeCell ref="V1:AG1"/>
-    <mergeCell ref="V2:AG2"/>
-    <mergeCell ref="X4:AD4"/>
-    <mergeCell ref="AE4:AG4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/Datas/FoodDatas/FoodData.xlsx
+++ b/Config/Datas/FoodDatas/FoodData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\FoodDatas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E936F4DB-CD58-4D72-835E-6C26E1CD657F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39D32103-5B38-41E2-9A8A-121A51956B7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="115">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -440,6 +440,50 @@
   </si>
   <si>
     <t>DV_值,5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chocolate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>巧克力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>德芙，纵享丝滑~</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>添加到烤串上时，获得一层【丝滑】</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GA_获得Buff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>softness</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sushi</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>spicy_strip</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>辣条</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PotatoRed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>周围随机,DV_值~-1,棋盘上</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -534,6 +578,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -542,9 +589,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -826,32 +870,32 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AG20"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:AG25"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="4" max="4" width="15.25" customWidth="1"/>
     <col min="5" max="5" width="7.5" customWidth="1"/>
-    <col min="6" max="7" width="6.625" customWidth="1"/>
-    <col min="8" max="8" width="6.875" customWidth="1"/>
+    <col min="6" max="7" width="6.58203125" customWidth="1"/>
+    <col min="8" max="8" width="6.83203125" customWidth="1"/>
     <col min="10" max="10" width="12.75" customWidth="1"/>
     <col min="11" max="11" width="29.5" customWidth="1"/>
     <col min="12" max="12" width="15.5" customWidth="1"/>
-    <col min="13" max="13" width="5.375" style="6" customWidth="1"/>
-    <col min="14" max="14" width="21.125" style="6" customWidth="1"/>
-    <col min="15" max="15" width="9.375" style="6" customWidth="1"/>
-    <col min="16" max="16" width="13.125" style="6" customWidth="1"/>
-    <col min="17" max="17" width="9.375" style="6" customWidth="1"/>
+    <col min="13" max="13" width="5.33203125" style="6" customWidth="1"/>
+    <col min="14" max="14" width="21.08203125" style="6" customWidth="1"/>
+    <col min="15" max="15" width="9.33203125" style="6" customWidth="1"/>
+    <col min="16" max="16" width="13.08203125" style="6" customWidth="1"/>
+    <col min="17" max="17" width="9.33203125" style="6" customWidth="1"/>
     <col min="18" max="18" width="21.75" style="6" customWidth="1"/>
     <col min="19" max="19" width="21" style="6" customWidth="1"/>
     <col min="20" max="20" width="23" style="6" customWidth="1"/>
     <col min="21" max="21" width="24.25" customWidth="1"/>
     <col min="22" max="22" width="11.5" customWidth="1"/>
     <col min="23" max="23" width="11.75" customWidth="1"/>
-    <col min="27" max="27" width="13.625" customWidth="1"/>
+    <col min="27" max="27" width="15.4140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -885,34 +929,34 @@
       <c r="K1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="L1" s="11" t="s">
+      <c r="L1" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="M1" s="11"/>
-      <c r="N1" s="11"/>
-      <c r="O1" s="11"/>
-      <c r="P1" s="11"/>
-      <c r="Q1" s="11"/>
-      <c r="R1" s="11"/>
-      <c r="S1" s="11"/>
-      <c r="T1" s="11"/>
-      <c r="U1" s="11"/>
-      <c r="V1" s="10" t="s">
+      <c r="M1" s="12"/>
+      <c r="N1" s="12"/>
+      <c r="O1" s="12"/>
+      <c r="P1" s="12"/>
+      <c r="Q1" s="12"/>
+      <c r="R1" s="12"/>
+      <c r="S1" s="12"/>
+      <c r="T1" s="12"/>
+      <c r="U1" s="12"/>
+      <c r="V1" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="W1" s="10"/>
-      <c r="X1" s="10"/>
-      <c r="Y1" s="10"/>
-      <c r="Z1" s="10"/>
-      <c r="AA1" s="10"/>
-      <c r="AB1" s="10"/>
-      <c r="AC1" s="10"/>
-      <c r="AD1" s="10"/>
-      <c r="AE1" s="10"/>
-      <c r="AF1" s="10"/>
-      <c r="AG1" s="10"/>
-    </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="W1" s="11"/>
+      <c r="X1" s="11"/>
+      <c r="Y1" s="11"/>
+      <c r="Z1" s="11"/>
+      <c r="AA1" s="11"/>
+      <c r="AB1" s="11"/>
+      <c r="AC1" s="11"/>
+      <c r="AD1" s="11"/>
+      <c r="AE1" s="11"/>
+      <c r="AF1" s="11"/>
+      <c r="AG1" s="11"/>
+    </row>
+    <row r="2" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -946,34 +990,34 @@
       <c r="K2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="L2" s="10" t="s">
+      <c r="L2" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="M2" s="10"/>
-      <c r="N2" s="10"/>
-      <c r="O2" s="10"/>
-      <c r="P2" s="10"/>
-      <c r="Q2" s="10"/>
-      <c r="R2" s="10"/>
-      <c r="S2" s="10"/>
-      <c r="T2" s="10"/>
-      <c r="U2" s="10"/>
-      <c r="V2" s="11" t="s">
+      <c r="M2" s="11"/>
+      <c r="N2" s="11"/>
+      <c r="O2" s="11"/>
+      <c r="P2" s="11"/>
+      <c r="Q2" s="11"/>
+      <c r="R2" s="11"/>
+      <c r="S2" s="11"/>
+      <c r="T2" s="11"/>
+      <c r="U2" s="11"/>
+      <c r="V2" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="W2" s="11"/>
-      <c r="X2" s="11"/>
-      <c r="Y2" s="11"/>
-      <c r="Z2" s="11"/>
-      <c r="AA2" s="11"/>
-      <c r="AB2" s="11"/>
-      <c r="AC2" s="11"/>
-      <c r="AD2" s="11"/>
-      <c r="AE2" s="11"/>
-      <c r="AF2" s="11"/>
-      <c r="AG2" s="11"/>
-    </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="W2" s="12"/>
+      <c r="X2" s="12"/>
+      <c r="Y2" s="12"/>
+      <c r="Z2" s="12"/>
+      <c r="AA2" s="12"/>
+      <c r="AB2" s="12"/>
+      <c r="AC2" s="12"/>
+      <c r="AD2" s="12"/>
+      <c r="AE2" s="12"/>
+      <c r="AF2" s="12"/>
+      <c r="AG2" s="12"/>
+    </row>
+    <row r="3" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -1018,7 +1062,7 @@
       <c r="AC3" s="1"/>
       <c r="AD3" s="1"/>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1035,39 +1079,39 @@
       <c r="L4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="M4" s="10" t="s">
+      <c r="M4" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="N4" s="10"/>
-      <c r="O4" s="10"/>
-      <c r="P4" s="10"/>
-      <c r="Q4" s="10"/>
-      <c r="R4" s="10"/>
-      <c r="S4" s="10"/>
-      <c r="T4" s="10"/>
-      <c r="U4" s="10"/>
+      <c r="N4" s="11"/>
+      <c r="O4" s="11"/>
+      <c r="P4" s="11"/>
+      <c r="Q4" s="11"/>
+      <c r="R4" s="11"/>
+      <c r="S4" s="11"/>
+      <c r="T4" s="11"/>
+      <c r="U4" s="11"/>
       <c r="V4" t="s">
         <v>33</v>
       </c>
       <c r="W4" t="s">
         <v>67</v>
       </c>
-      <c r="X4" s="13" t="s">
+      <c r="X4" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="Y4" s="13"/>
-      <c r="Z4" s="13"/>
-      <c r="AA4" s="13"/>
-      <c r="AB4" s="13"/>
-      <c r="AC4" s="13"/>
-      <c r="AD4" s="13"/>
-      <c r="AE4" s="11" t="s">
+      <c r="Y4" s="10"/>
+      <c r="Z4" s="10"/>
+      <c r="AA4" s="10"/>
+      <c r="AB4" s="10"/>
+      <c r="AC4" s="10"/>
+      <c r="AD4" s="10"/>
+      <c r="AE4" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="AF4" s="11"/>
-      <c r="AG4" s="11"/>
-    </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AF4" s="12"/>
+      <c r="AG4" s="12"/>
+    </row>
+    <row r="5" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1085,33 +1129,33 @@
       <c r="M5" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="N5" s="10" t="s">
+      <c r="N5" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="O5" s="10"/>
-      <c r="P5" s="10"/>
-      <c r="Q5" s="10"/>
-      <c r="R5" s="13" t="s">
+      <c r="O5" s="11"/>
+      <c r="P5" s="11"/>
+      <c r="Q5" s="11"/>
+      <c r="R5" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="S5" s="13"/>
-      <c r="T5" s="13"/>
-      <c r="U5" s="13"/>
+      <c r="S5" s="10"/>
+      <c r="T5" s="10"/>
+      <c r="U5" s="10"/>
       <c r="X5" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="Y5" s="13" t="s">
+      <c r="Y5" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="Z5" s="13"/>
-      <c r="AA5" s="13" t="s">
+      <c r="Z5" s="10"/>
+      <c r="AA5" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="AB5" s="13"/>
-      <c r="AC5" s="13"/>
-      <c r="AD5" s="13"/>
-    </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AB5" s="10"/>
+      <c r="AC5" s="10"/>
+      <c r="AD5" s="10"/>
+    </row>
+    <row r="6" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -1129,20 +1173,20 @@
       <c r="M6" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="N6" s="10" t="s">
+      <c r="N6" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="O6" s="10"/>
-      <c r="P6" s="10"/>
-      <c r="Q6" s="10"/>
-      <c r="R6" s="13" t="s">
+      <c r="O6" s="11"/>
+      <c r="P6" s="11"/>
+      <c r="Q6" s="11"/>
+      <c r="R6" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="S6" s="13"/>
-      <c r="T6" s="13"/>
-      <c r="U6" s="13"/>
-    </row>
-    <row r="7" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="S6" s="10"/>
+      <c r="T6" s="10"/>
+      <c r="U6" s="10"/>
+    </row>
+    <row r="7" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>3</v>
       </c>
@@ -1151,21 +1195,21 @@
       <c r="N7" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="O7" s="12" t="s">
+      <c r="O7" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="P7" s="12"/>
-      <c r="Q7" s="12"/>
+      <c r="P7" s="13"/>
+      <c r="Q7" s="13"/>
       <c r="R7" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="S7" s="12" t="s">
+      <c r="S7" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="T7" s="12"/>
-      <c r="U7" s="12"/>
-    </row>
-    <row r="8" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="T7" s="13"/>
+      <c r="U7" s="13"/>
+    </row>
+    <row r="8" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
         <v>88</v>
       </c>
@@ -1209,7 +1253,7 @@
       <c r="W8" s="2"/>
       <c r="AA8" s="2"/>
     </row>
-    <row r="9" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
@@ -1235,7 +1279,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="10" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B10" s="7" t="s">
         <v>87</v>
       </c>
@@ -1292,13 +1336,13 @@
         <v>49</v>
       </c>
     </row>
-    <row r="11" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
       <c r="J11" s="2"/>
     </row>
-    <row r="12" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B12" s="7" t="s">
         <v>86</v>
       </c>
@@ -1352,8 +1396,8 @@
         <v>55</v>
       </c>
     </row>
-    <row r="13" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="14" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B14" s="7" t="s">
         <v>96</v>
       </c>
@@ -1400,8 +1444,8 @@
         <v>64</v>
       </c>
     </row>
-    <row r="15" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="16" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B16" s="7" t="s">
         <v>85</v>
       </c>
@@ -1448,7 +1492,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="17" spans="2:30" s="7" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:31" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="X17" s="7">
         <v>2</v>
       </c>
@@ -1465,7 +1509,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="18" spans="2:30" s="7" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:31" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B18" s="7" t="s">
         <v>84</v>
       </c>
@@ -1509,7 +1553,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="20" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:31" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>97</v>
       </c>
@@ -1556,14 +1600,111 @@
         <v>103</v>
       </c>
     </row>
+    <row r="22" spans="2:31" x14ac:dyDescent="0.3">
+      <c r="B22" t="s">
+        <v>104</v>
+      </c>
+      <c r="C22" t="s">
+        <v>105</v>
+      </c>
+      <c r="D22" t="s">
+        <v>106</v>
+      </c>
+      <c r="E22" t="s">
+        <v>94</v>
+      </c>
+      <c r="G22">
+        <v>2</v>
+      </c>
+      <c r="H22">
+        <v>4</v>
+      </c>
+      <c r="I22">
+        <v>4</v>
+      </c>
+      <c r="J22" t="s">
+        <v>110</v>
+      </c>
+      <c r="K22" t="s">
+        <v>107</v>
+      </c>
+      <c r="L22" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="M22" s="6">
+        <v>1</v>
+      </c>
+      <c r="R22" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="S22" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="T22" s="6" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="24" spans="2:31" x14ac:dyDescent="0.3">
+      <c r="B24" t="s">
+        <v>111</v>
+      </c>
+      <c r="C24" t="s">
+        <v>112</v>
+      </c>
+      <c r="E24" t="s">
+        <v>94</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+      <c r="H24">
+        <v>5</v>
+      </c>
+      <c r="I24">
+        <v>5</v>
+      </c>
+      <c r="J24" t="s">
+        <v>113</v>
+      </c>
+      <c r="V24" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="W24" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="X24" s="7">
+        <v>1</v>
+      </c>
+      <c r="Y24" s="7"/>
+      <c r="Z24" s="7"/>
+      <c r="AA24" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="AB24" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC24" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="AD24" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="AE24" s="7"/>
+    </row>
+    <row r="25" spans="2:31" x14ac:dyDescent="0.3">
+      <c r="V25" s="7"/>
+      <c r="W25" s="7"/>
+      <c r="X25" s="7"/>
+      <c r="Y25" s="7"/>
+      <c r="Z25" s="7"/>
+      <c r="AA25" s="2"/>
+      <c r="AB25" s="7"/>
+      <c r="AC25" s="7"/>
+      <c r="AD25" s="7"/>
+      <c r="AE25" s="7"/>
+    </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="Y5:Z5"/>
-    <mergeCell ref="AA5:AD5"/>
-    <mergeCell ref="V1:AG1"/>
-    <mergeCell ref="V2:AG2"/>
-    <mergeCell ref="X4:AD4"/>
-    <mergeCell ref="AE4:AG4"/>
     <mergeCell ref="L2:U2"/>
     <mergeCell ref="L1:U1"/>
     <mergeCell ref="N6:Q6"/>
@@ -1573,6 +1714,12 @@
     <mergeCell ref="R6:U6"/>
     <mergeCell ref="R5:U5"/>
     <mergeCell ref="M4:U4"/>
+    <mergeCell ref="Y5:Z5"/>
+    <mergeCell ref="AA5:AD5"/>
+    <mergeCell ref="V1:AG1"/>
+    <mergeCell ref="V2:AG2"/>
+    <mergeCell ref="X4:AD4"/>
+    <mergeCell ref="AE4:AG4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/Datas/FoodDatas/FoodData.xlsx
+++ b/Config/Datas/FoodDatas/FoodData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\FoodDatas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39D32103-5B38-41E2-9A8A-121A51956B7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F9EBCD7-99CA-446A-9F2B-7B97D4EFDD0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="118">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -484,6 +484,18 @@
   </si>
   <si>
     <t>周围随机,DV_值~-1,棋盘上</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>timeCost</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>时间消耗</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -557,9 +569,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -578,9 +587,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -588,6 +594,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -870,32 +882,35 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AG25"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:AH25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="4" max="4" width="15.25" customWidth="1"/>
     <col min="5" max="5" width="7.5" customWidth="1"/>
-    <col min="6" max="7" width="6.58203125" customWidth="1"/>
-    <col min="8" max="8" width="6.83203125" customWidth="1"/>
-    <col min="10" max="10" width="12.75" customWidth="1"/>
-    <col min="11" max="11" width="29.5" customWidth="1"/>
-    <col min="12" max="12" width="15.5" customWidth="1"/>
-    <col min="13" max="13" width="5.33203125" style="6" customWidth="1"/>
-    <col min="14" max="14" width="21.08203125" style="6" customWidth="1"/>
-    <col min="15" max="15" width="9.33203125" style="6" customWidth="1"/>
-    <col min="16" max="16" width="13.08203125" style="6" customWidth="1"/>
-    <col min="17" max="17" width="9.33203125" style="6" customWidth="1"/>
-    <col min="18" max="18" width="21.75" style="6" customWidth="1"/>
-    <col min="19" max="19" width="21" style="6" customWidth="1"/>
-    <col min="20" max="20" width="23" style="6" customWidth="1"/>
-    <col min="21" max="21" width="24.25" customWidth="1"/>
-    <col min="22" max="22" width="11.5" customWidth="1"/>
-    <col min="23" max="23" width="11.75" customWidth="1"/>
-    <col min="27" max="27" width="15.4140625" customWidth="1"/>
+    <col min="6" max="6" width="6.625" customWidth="1"/>
+    <col min="7" max="7" width="6" style="6" customWidth="1"/>
+    <col min="8" max="8" width="4.5" style="6" customWidth="1"/>
+    <col min="9" max="9" width="4.875" style="6" customWidth="1"/>
+    <col min="10" max="10" width="4.75" style="6" customWidth="1"/>
+    <col min="11" max="11" width="12.75" customWidth="1"/>
+    <col min="12" max="12" width="29.5" customWidth="1"/>
+    <col min="13" max="13" width="15.5" customWidth="1"/>
+    <col min="14" max="14" width="5.375" style="5" customWidth="1"/>
+    <col min="15" max="15" width="21.125" style="5" customWidth="1"/>
+    <col min="16" max="16" width="9.375" style="5" customWidth="1"/>
+    <col min="17" max="17" width="13.125" style="5" customWidth="1"/>
+    <col min="18" max="18" width="9.375" style="5" customWidth="1"/>
+    <col min="19" max="19" width="21.75" style="5" customWidth="1"/>
+    <col min="20" max="20" width="21" style="5" customWidth="1"/>
+    <col min="21" max="21" width="23" style="5" customWidth="1"/>
+    <col min="22" max="22" width="24.25" customWidth="1"/>
+    <col min="23" max="23" width="11.5" customWidth="1"/>
+    <col min="24" max="24" width="11.75" customWidth="1"/>
+    <col min="28" max="28" width="15.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -914,49 +929,52 @@
       <c r="F1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="I1" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>22</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="L1" s="12" t="s">
+      <c r="M1" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="M1" s="12"/>
-      <c r="N1" s="12"/>
-      <c r="O1" s="12"/>
-      <c r="P1" s="12"/>
-      <c r="Q1" s="12"/>
-      <c r="R1" s="12"/>
-      <c r="S1" s="12"/>
-      <c r="T1" s="12"/>
-      <c r="U1" s="12"/>
-      <c r="V1" s="11" t="s">
+      <c r="N1" s="10"/>
+      <c r="O1" s="10"/>
+      <c r="P1" s="10"/>
+      <c r="Q1" s="10"/>
+      <c r="R1" s="10"/>
+      <c r="S1" s="10"/>
+      <c r="T1" s="10"/>
+      <c r="U1" s="10"/>
+      <c r="V1" s="10"/>
+      <c r="W1" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="W1" s="11"/>
-      <c r="X1" s="11"/>
-      <c r="Y1" s="11"/>
-      <c r="Z1" s="11"/>
-      <c r="AA1" s="11"/>
-      <c r="AB1" s="11"/>
-      <c r="AC1" s="11"/>
-      <c r="AD1" s="11"/>
-      <c r="AE1" s="11"/>
-      <c r="AF1" s="11"/>
-      <c r="AG1" s="11"/>
-    </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="X1" s="9"/>
+      <c r="Y1" s="9"/>
+      <c r="Z1" s="9"/>
+      <c r="AA1" s="9"/>
+      <c r="AB1" s="9"/>
+      <c r="AC1" s="9"/>
+      <c r="AD1" s="9"/>
+      <c r="AE1" s="9"/>
+      <c r="AF1" s="9"/>
+      <c r="AG1" s="9"/>
+      <c r="AH1" s="9"/>
+    </row>
+    <row r="2" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -975,49 +993,52 @@
       <c r="F2" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="2" t="s">
         <v>74</v>
       </c>
       <c r="H2" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="J2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="2" t="s">
-        <v>1</v>
-      </c>
       <c r="K2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="L2" s="11" t="s">
+      <c r="L2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="M2" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="M2" s="11"/>
-      <c r="N2" s="11"/>
-      <c r="O2" s="11"/>
-      <c r="P2" s="11"/>
-      <c r="Q2" s="11"/>
-      <c r="R2" s="11"/>
-      <c r="S2" s="11"/>
-      <c r="T2" s="11"/>
-      <c r="U2" s="11"/>
-      <c r="V2" s="12" t="s">
+      <c r="N2" s="9"/>
+      <c r="O2" s="9"/>
+      <c r="P2" s="9"/>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="9"/>
+      <c r="S2" s="9"/>
+      <c r="T2" s="9"/>
+      <c r="U2" s="9"/>
+      <c r="V2" s="9"/>
+      <c r="W2" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="W2" s="12"/>
-      <c r="X2" s="12"/>
-      <c r="Y2" s="12"/>
-      <c r="Z2" s="12"/>
-      <c r="AA2" s="12"/>
-      <c r="AB2" s="12"/>
-      <c r="AC2" s="12"/>
-      <c r="AD2" s="12"/>
-      <c r="AE2" s="12"/>
-      <c r="AF2" s="12"/>
-      <c r="AG2" s="12"/>
-    </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="X2" s="10"/>
+      <c r="Y2" s="10"/>
+      <c r="Z2" s="10"/>
+      <c r="AA2" s="10"/>
+      <c r="AB2" s="10"/>
+      <c r="AC2" s="10"/>
+      <c r="AD2" s="10"/>
+      <c r="AE2" s="10"/>
+      <c r="AF2" s="10"/>
+      <c r="AG2" s="10"/>
+      <c r="AH2" s="10"/>
+    </row>
+    <row r="3" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -1036,33 +1057,36 @@
       <c r="F3" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1" t="s">
+      <c r="G3" s="2"/>
+      <c r="H3" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="J3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="L3" s="1"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="5"/>
-      <c r="V3" s="1"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4"/>
       <c r="W3" s="1"/>
-      <c r="X3" s="2"/>
-      <c r="Y3" s="1"/>
+      <c r="X3" s="1"/>
+      <c r="Y3" s="2"/>
       <c r="Z3" s="1"/>
       <c r="AA3" s="1"/>
       <c r="AB3" s="1"/>
       <c r="AC3" s="1"/>
       <c r="AD3" s="1"/>
-    </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AE3" s="1"/>
+    </row>
+    <row r="4" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1071,47 +1095,48 @@
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
       <c r="K4" s="1"/>
-      <c r="L4" s="1" t="s">
+      <c r="L4" s="1"/>
+      <c r="M4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="M4" s="11" t="s">
+      <c r="N4" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="N4" s="11"/>
-      <c r="O4" s="11"/>
-      <c r="P4" s="11"/>
-      <c r="Q4" s="11"/>
-      <c r="R4" s="11"/>
-      <c r="S4" s="11"/>
-      <c r="T4" s="11"/>
-      <c r="U4" s="11"/>
-      <c r="V4" t="s">
+      <c r="O4" s="9"/>
+      <c r="P4" s="9"/>
+      <c r="Q4" s="9"/>
+      <c r="R4" s="9"/>
+      <c r="S4" s="9"/>
+      <c r="T4" s="9"/>
+      <c r="U4" s="9"/>
+      <c r="V4" s="9"/>
+      <c r="W4" t="s">
         <v>33</v>
       </c>
-      <c r="W4" t="s">
+      <c r="X4" t="s">
         <v>67</v>
       </c>
-      <c r="X4" s="10" t="s">
+      <c r="Y4" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="Y4" s="10"/>
-      <c r="Z4" s="10"/>
-      <c r="AA4" s="10"/>
-      <c r="AB4" s="10"/>
-      <c r="AC4" s="10"/>
-      <c r="AD4" s="10"/>
-      <c r="AE4" s="12" t="s">
+      <c r="Z4" s="12"/>
+      <c r="AA4" s="12"/>
+      <c r="AB4" s="12"/>
+      <c r="AC4" s="12"/>
+      <c r="AD4" s="12"/>
+      <c r="AE4" s="12"/>
+      <c r="AF4" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="AF4" s="12"/>
-      <c r="AG4" s="12"/>
-    </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AG4" s="10"/>
+      <c r="AH4" s="10"/>
+    </row>
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1120,42 +1145,43 @@
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
-      <c r="M5" s="5" t="s">
+      <c r="M5" s="1"/>
+      <c r="N5" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="N5" s="11" t="s">
+      <c r="O5" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="O5" s="11"/>
-      <c r="P5" s="11"/>
-      <c r="Q5" s="11"/>
-      <c r="R5" s="10" t="s">
+      <c r="P5" s="9"/>
+      <c r="Q5" s="9"/>
+      <c r="R5" s="9"/>
+      <c r="S5" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="S5" s="10"/>
-      <c r="T5" s="10"/>
-      <c r="U5" s="10"/>
-      <c r="X5" s="7" t="s">
+      <c r="T5" s="12"/>
+      <c r="U5" s="12"/>
+      <c r="V5" s="12"/>
+      <c r="Y5" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="Y5" s="10" t="s">
+      <c r="Z5" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="Z5" s="10"/>
-      <c r="AA5" s="10" t="s">
+      <c r="AA5" s="12"/>
+      <c r="AB5" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="AB5" s="10"/>
-      <c r="AC5" s="10"/>
-      <c r="AD5" s="10"/>
-    </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AC5" s="12"/>
+      <c r="AD5" s="12"/>
+      <c r="AE5" s="12"/>
+    </row>
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -1164,59 +1190,60 @@
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
-      <c r="M6" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="N6" s="11" t="s">
+      <c r="M6" s="1"/>
+      <c r="N6" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="O6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="O6" s="11"/>
-      <c r="P6" s="11"/>
-      <c r="Q6" s="11"/>
-      <c r="R6" s="10" t="s">
+      <c r="P6" s="9"/>
+      <c r="Q6" s="9"/>
+      <c r="R6" s="9"/>
+      <c r="S6" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="S6" s="10"/>
-      <c r="T6" s="10"/>
-      <c r="U6" s="10"/>
-    </row>
-    <row r="7" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="7" t="s">
+      <c r="T6" s="12"/>
+      <c r="U6" s="12"/>
+      <c r="V6" s="12"/>
+    </row>
+    <row r="7" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
-      <c r="N7" s="8" t="s">
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+      <c r="O7" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="O7" s="13" t="s">
+      <c r="P7" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="P7" s="13"/>
-      <c r="Q7" s="13"/>
-      <c r="R7" s="8" t="s">
+      <c r="Q7" s="11"/>
+      <c r="R7" s="11"/>
+      <c r="S7" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="S7" s="13" t="s">
+      <c r="T7" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="T7" s="13"/>
-      <c r="U7" s="13"/>
-    </row>
-    <row r="8" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="7" t="s">
+      <c r="U7" s="11"/>
+      <c r="V7" s="11"/>
+    </row>
+    <row r="8" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="6" t="s">
         <v>20</v>
       </c>
       <c r="E8" s="2" t="s">
@@ -1227,66 +1254,70 @@
         <v>1</v>
       </c>
       <c r="H8" s="2">
+        <v>1</v>
+      </c>
+      <c r="I8" s="2">
         <v>5</v>
       </c>
-      <c r="I8" s="8">
+      <c r="J8" s="7">
         <v>5</v>
       </c>
-      <c r="J8" s="2" t="s">
+      <c r="K8" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K8" s="7" t="s">
+      <c r="L8" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="L8" s="7" t="s">
+      <c r="M8" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="M8" s="7">
-        <v>1</v>
-      </c>
-      <c r="R8" s="9" t="s">
+      <c r="N8" s="6">
+        <v>1</v>
+      </c>
+      <c r="S8" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="S8" s="7" t="s">
+      <c r="T8" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="W8" s="2"/>
-      <c r="AA8" s="2"/>
-    </row>
-    <row r="9" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="X8" s="2"/>
+      <c r="AB8" s="2"/>
+    </row>
+    <row r="9" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="2"/>
-      <c r="L9" s="7" t="s">
+      <c r="I9" s="2"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="2"/>
+      <c r="M9" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="M9" s="7">
-        <v>1</v>
-      </c>
-      <c r="R9" s="2" t="s">
+      <c r="N9" s="6">
+        <v>1</v>
+      </c>
+      <c r="S9" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="S9" s="7" t="s">
+      <c r="T9" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="T9" s="7" t="s">
+      <c r="U9" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="U9" s="7" t="s">
+      <c r="V9" s="6" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="10" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="7" t="s">
+    <row r="10" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="6" t="s">
         <v>41</v>
       </c>
       <c r="E10" s="2" t="s">
@@ -1297,59 +1328,63 @@
         <v>1</v>
       </c>
       <c r="H10" s="2">
+        <v>1</v>
+      </c>
+      <c r="I10" s="2">
         <v>5</v>
       </c>
-      <c r="I10" s="8">
+      <c r="J10" s="7">
         <v>5</v>
       </c>
-      <c r="J10" s="2" t="s">
+      <c r="K10" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="K10" s="7" t="s">
+      <c r="L10" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="L10" s="2" t="s">
+      <c r="M10" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="M10" s="7">
-        <v>1</v>
-      </c>
-      <c r="N10" s="2" t="s">
+      <c r="N10" s="6">
+        <v>1</v>
+      </c>
+      <c r="O10" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="O10" s="9" t="s">
+      <c r="P10" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="P10" s="7" t="s">
+      <c r="Q10" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="Q10" s="7" t="s">
+      <c r="R10" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="R10" s="2" t="s">
+      <c r="S10" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="S10" s="7" t="s">
+      <c r="T10" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="T10" s="7" t="s">
+      <c r="U10" s="6" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="11" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
-      <c r="J11" s="2"/>
-    </row>
-    <row r="12" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="7" t="s">
+      <c r="H11" s="2"/>
+      <c r="K11" s="2"/>
+    </row>
+    <row r="12" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="6" t="s">
         <v>40</v>
       </c>
       <c r="E12" s="2" t="s">
@@ -1360,51 +1395,54 @@
         <v>1</v>
       </c>
       <c r="H12" s="2">
+        <v>1</v>
+      </c>
+      <c r="I12" s="2">
         <v>5</v>
       </c>
-      <c r="I12" s="8">
+      <c r="J12" s="7">
         <v>5</v>
       </c>
-      <c r="J12" s="2" t="s">
+      <c r="K12" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K12" s="7" t="s">
+      <c r="L12" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="L12" s="2" t="s">
+      <c r="M12" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="M12" s="7">
-        <v>1</v>
-      </c>
-      <c r="N12" s="2" t="s">
+      <c r="N12" s="6">
+        <v>1</v>
+      </c>
+      <c r="O12" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="O12" s="7" t="s">
+      <c r="P12" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="P12" s="7">
+      <c r="Q12" s="6">
         <v>2</v>
       </c>
-      <c r="R12" s="2" t="s">
+      <c r="S12" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="S12" s="7" t="s">
+      <c r="T12" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="T12" s="7" t="s">
+      <c r="U12" s="6" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="13" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="7" t="s">
+    <row r="13" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="14" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="6" t="s">
         <v>95</v>
       </c>
       <c r="E14" s="2" t="s">
@@ -1417,143 +1455,152 @@
         <v>1</v>
       </c>
       <c r="H14" s="2">
+        <v>1</v>
+      </c>
+      <c r="I14" s="2">
         <v>5</v>
       </c>
-      <c r="I14" s="8">
+      <c r="J14" s="7">
         <v>5</v>
       </c>
-      <c r="J14" s="2" t="s">
+      <c r="K14" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="K14" s="7" t="s">
+      <c r="L14" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="L14" s="7" t="s">
+      <c r="M14" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="M14" s="7">
-        <v>1</v>
-      </c>
-      <c r="R14" s="7" t="s">
+      <c r="N14" s="6">
+        <v>1</v>
+      </c>
+      <c r="S14" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="S14" s="7" t="s">
+      <c r="T14" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="T14" s="2" t="s">
+      <c r="U14" s="2" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="15" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="16" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="7" t="s">
+    <row r="15" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="16" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B16" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="G16" s="7">
-        <v>1</v>
-      </c>
-      <c r="H16" s="2">
+      <c r="G16" s="6">
+        <v>1</v>
+      </c>
+      <c r="H16" s="6">
+        <v>1</v>
+      </c>
+      <c r="I16" s="2">
         <v>5</v>
       </c>
-      <c r="I16" s="8">
+      <c r="J16" s="7">
         <v>5</v>
       </c>
-      <c r="J16" s="7" t="s">
+      <c r="K16" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="K16" t="s">
+      <c r="L16" t="s">
         <v>92</v>
       </c>
-      <c r="V16" s="7" t="s">
+      <c r="W16" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="W16" s="2" t="s">
+      <c r="X16" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="X16" s="7">
-        <v>1</v>
-      </c>
-      <c r="AA16" s="4" t="s">
+      <c r="Y16" s="6">
+        <v>1</v>
+      </c>
+      <c r="AB16" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="AB16" s="7" t="s">
+      <c r="AC16" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="AC16" s="7" t="s">
+      <c r="AD16" s="6" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="17" spans="2:31" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="X17" s="7">
+    <row r="17" spans="2:32" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="Y17" s="6">
         <v>2</v>
       </c>
-      <c r="AA17" s="2" t="s">
+      <c r="AB17" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AB17" s="7" t="s">
+      <c r="AC17" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="AC17" s="7" t="s">
+      <c r="AD17" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="AD17" s="7" t="s">
+      <c r="AE17" s="6" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="18" spans="2:31" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="7" t="s">
+    <row r="18" spans="2:32" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B18" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="6" t="s">
         <v>82</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="G18" s="7">
+      <c r="G18" s="6">
         <v>2</v>
       </c>
-      <c r="H18" s="2">
+      <c r="H18" s="6">
+        <v>1</v>
+      </c>
+      <c r="I18" s="2">
         <v>5</v>
       </c>
-      <c r="I18" s="8">
+      <c r="J18" s="7">
         <v>5</v>
       </c>
-      <c r="J18" s="7" t="s">
+      <c r="K18" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="K18" s="7" t="s">
+      <c r="L18" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="L18" s="2" t="s">
+      <c r="M18" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="M18" s="7">
-        <v>1</v>
-      </c>
-      <c r="R18" s="7" t="s">
+      <c r="N18" s="6">
+        <v>1</v>
+      </c>
+      <c r="S18" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="S18" s="4" t="s">
+      <c r="T18" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="T18" s="2" t="s">
+      <c r="U18" s="2" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="20" spans="2:31" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B20" t="s">
         <v>97</v>
       </c>
@@ -1566,41 +1613,44 @@
       <c r="E20" t="s">
         <v>94</v>
       </c>
-      <c r="G20">
-        <v>1</v>
-      </c>
-      <c r="H20">
+      <c r="G20" s="6">
+        <v>1</v>
+      </c>
+      <c r="H20" s="6">
+        <v>1</v>
+      </c>
+      <c r="I20" s="6">
         <v>5</v>
       </c>
-      <c r="I20">
+      <c r="J20" s="6">
         <v>5</v>
       </c>
-      <c r="J20" t="s">
+      <c r="K20" t="s">
         <v>100</v>
       </c>
-      <c r="L20" t="s">
+      <c r="M20" t="s">
         <v>101</v>
       </c>
-      <c r="M20" s="6">
-        <v>1</v>
-      </c>
-      <c r="N20" s="6" t="s">
+      <c r="N20" s="5">
+        <v>1</v>
+      </c>
+      <c r="O20" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="O20" s="6">
+      <c r="P20" s="5">
         <v>0</v>
       </c>
-      <c r="R20" s="2" t="s">
+      <c r="S20" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="S20" s="7" t="s">
+      <c r="T20" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="T20" s="7" t="s">
+      <c r="U20" s="6" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="22" spans="2:31" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B22" t="s">
         <v>104</v>
       </c>
@@ -1613,38 +1663,41 @@
       <c r="E22" t="s">
         <v>94</v>
       </c>
-      <c r="G22">
+      <c r="G22" s="6">
         <v>2</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="6">
+        <v>1</v>
+      </c>
+      <c r="I22" s="6">
         <v>4</v>
       </c>
-      <c r="I22">
+      <c r="J22" s="6">
         <v>4</v>
       </c>
-      <c r="J22" t="s">
+      <c r="K22" t="s">
         <v>110</v>
       </c>
-      <c r="K22" t="s">
+      <c r="L22" t="s">
         <v>107</v>
       </c>
-      <c r="L22" s="7" t="s">
+      <c r="M22" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="M22" s="6">
-        <v>1</v>
-      </c>
-      <c r="R22" s="6" t="s">
+      <c r="N22" s="5">
+        <v>1</v>
+      </c>
+      <c r="S22" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="S22" s="6" t="s">
+      <c r="T22" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="T22" s="6" t="s">
+      <c r="U22" s="5" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="24" spans="2:31" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B24" t="s">
         <v>111</v>
       </c>
@@ -1654,72 +1707,75 @@
       <c r="E24" t="s">
         <v>94</v>
       </c>
-      <c r="G24">
-        <v>1</v>
-      </c>
-      <c r="H24">
+      <c r="G24" s="6">
+        <v>1</v>
+      </c>
+      <c r="H24" s="6">
+        <v>1</v>
+      </c>
+      <c r="I24" s="6">
         <v>5</v>
       </c>
-      <c r="I24">
+      <c r="J24" s="6">
         <v>5</v>
       </c>
-      <c r="J24" t="s">
+      <c r="K24" t="s">
         <v>113</v>
       </c>
-      <c r="V24" s="7" t="s">
+      <c r="W24" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="W24" s="2" t="s">
+      <c r="X24" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="X24" s="7">
-        <v>1</v>
-      </c>
-      <c r="Y24" s="7"/>
-      <c r="Z24" s="7"/>
-      <c r="AA24" s="4" t="s">
+      <c r="Y24" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z24" s="6"/>
+      <c r="AA24" s="6"/>
+      <c r="AB24" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="AB24" s="7" t="s">
+      <c r="AC24" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="AC24" s="7" t="s">
+      <c r="AD24" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="AD24" s="4" t="s">
+      <c r="AE24" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="AE24" s="7"/>
-    </row>
-    <row r="25" spans="2:31" x14ac:dyDescent="0.3">
-      <c r="V25" s="7"/>
-      <c r="W25" s="7"/>
-      <c r="X25" s="7"/>
-      <c r="Y25" s="7"/>
-      <c r="Z25" s="7"/>
-      <c r="AA25" s="2"/>
-      <c r="AB25" s="7"/>
-      <c r="AC25" s="7"/>
-      <c r="AD25" s="7"/>
-      <c r="AE25" s="7"/>
+      <c r="AF24" s="6"/>
+    </row>
+    <row r="25" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="W25" s="6"/>
+      <c r="X25" s="6"/>
+      <c r="Y25" s="6"/>
+      <c r="Z25" s="6"/>
+      <c r="AA25" s="6"/>
+      <c r="AB25" s="2"/>
+      <c r="AC25" s="6"/>
+      <c r="AD25" s="6"/>
+      <c r="AE25" s="6"/>
+      <c r="AF25" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="L2:U2"/>
-    <mergeCell ref="L1:U1"/>
-    <mergeCell ref="N6:Q6"/>
-    <mergeCell ref="N5:Q5"/>
-    <mergeCell ref="O7:Q7"/>
-    <mergeCell ref="S7:U7"/>
-    <mergeCell ref="R6:U6"/>
-    <mergeCell ref="R5:U5"/>
-    <mergeCell ref="M4:U4"/>
-    <mergeCell ref="Y5:Z5"/>
-    <mergeCell ref="AA5:AD5"/>
-    <mergeCell ref="V1:AG1"/>
-    <mergeCell ref="V2:AG2"/>
-    <mergeCell ref="X4:AD4"/>
-    <mergeCell ref="AE4:AG4"/>
+    <mergeCell ref="Z5:AA5"/>
+    <mergeCell ref="AB5:AE5"/>
+    <mergeCell ref="W1:AH1"/>
+    <mergeCell ref="W2:AH2"/>
+    <mergeCell ref="Y4:AE4"/>
+    <mergeCell ref="AF4:AH4"/>
+    <mergeCell ref="M2:V2"/>
+    <mergeCell ref="M1:V1"/>
+    <mergeCell ref="O6:R6"/>
+    <mergeCell ref="O5:R5"/>
+    <mergeCell ref="P7:R7"/>
+    <mergeCell ref="T7:V7"/>
+    <mergeCell ref="S6:V6"/>
+    <mergeCell ref="S5:V5"/>
+    <mergeCell ref="N4:V4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/Datas/FoodDatas/FoodData.xlsx
+++ b/Config/Datas/FoodDatas/FoodData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\FoodDatas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F9EBCD7-99CA-446A-9F2B-7B97D4EFDD0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BE4F15A-FABF-4FBF-B759-C05CAC1615E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Config/Datas/FoodDatas/FoodData.xlsx
+++ b/Config/Datas/FoodDatas/FoodData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\FoodDatas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BE4F15A-FABF-4FBF-B759-C05CAC1615E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69704819-A75F-4551-BB64-C892C722044A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Config/Datas/FoodDatas/FoodData.xlsx
+++ b/Config/Datas/FoodDatas/FoodData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\FoodDatas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69704819-A75F-4551-BB64-C892C722044A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0509ECC-FCC2-42A3-8978-FFB1CA01BE01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Config/Datas/FoodDatas/FoodData.xlsx
+++ b/Config/Datas/FoodDatas/FoodData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\FoodDatas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0509ECC-FCC2-42A3-8978-FFB1CA01BE01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BEDE71F-DA04-45D9-A45D-8ED970636C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="124">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -496,6 +496,30 @@
   </si>
   <si>
     <t>时间消耗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cherry_bomb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>樱桃炸弹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>脾气不太好</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>被串取时\n将周围实体弹开1格</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GA_定点爆破</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自己,false</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -882,7 +906,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AH25"/>
+  <dimension ref="A1:AH26"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="9" customWidth="1"/>
@@ -901,7 +925,7 @@
     <col min="16" max="16" width="9.375" style="5" customWidth="1"/>
     <col min="17" max="17" width="13.125" style="5" customWidth="1"/>
     <col min="18" max="18" width="9.375" style="5" customWidth="1"/>
-    <col min="19" max="19" width="21.75" style="5" customWidth="1"/>
+    <col min="19" max="19" width="16.375" style="5" customWidth="1"/>
     <col min="20" max="20" width="21" style="5" customWidth="1"/>
     <col min="21" max="21" width="23" style="5" customWidth="1"/>
     <col min="22" max="22" width="24.25" customWidth="1"/>
@@ -1758,6 +1782,50 @@
       <c r="AD25" s="6"/>
       <c r="AE25" s="6"/>
       <c r="AF25" s="6"/>
+    </row>
+    <row r="26" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="B26" t="s">
+        <v>118</v>
+      </c>
+      <c r="C26" t="s">
+        <v>119</v>
+      </c>
+      <c r="D26" t="s">
+        <v>120</v>
+      </c>
+      <c r="E26" t="s">
+        <v>21</v>
+      </c>
+      <c r="G26" s="6">
+        <v>2</v>
+      </c>
+      <c r="H26" s="6">
+        <v>1</v>
+      </c>
+      <c r="I26" s="6">
+        <v>2</v>
+      </c>
+      <c r="J26" s="6">
+        <v>4</v>
+      </c>
+      <c r="K26" t="s">
+        <v>81</v>
+      </c>
+      <c r="L26" t="s">
+        <v>121</v>
+      </c>
+      <c r="M26" t="s">
+        <v>59</v>
+      </c>
+      <c r="N26" s="5">
+        <v>1</v>
+      </c>
+      <c r="S26" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="T26" s="5" t="s">
+        <v>123</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="15">

--- a/Config/Datas/FoodDatas/FoodData.xlsx
+++ b/Config/Datas/FoodDatas/FoodData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\FoodDatas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BEDE71F-DA04-45D9-A45D-8ED970636C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84C92F9D-6924-437E-B0C8-569A460383C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="131">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -520,6 +520,34 @@
   </si>
   <si>
     <t>自己,false</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QQ糖</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QQ_suger</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QQ弹弹~</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Jam</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>被撞击时，珍稀度+2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>被碰撞时</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DV_值,0</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -906,7 +934,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AH26"/>
+  <dimension ref="A1:AH28"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="9" customWidth="1"/>
@@ -927,8 +955,8 @@
     <col min="18" max="18" width="9.375" style="5" customWidth="1"/>
     <col min="19" max="19" width="16.375" style="5" customWidth="1"/>
     <col min="20" max="20" width="21" style="5" customWidth="1"/>
-    <col min="21" max="21" width="23" style="5" customWidth="1"/>
-    <col min="22" max="22" width="24.25" customWidth="1"/>
+    <col min="21" max="21" width="13.5" style="5" customWidth="1"/>
+    <col min="22" max="22" width="15.375" customWidth="1"/>
     <col min="23" max="23" width="11.5" customWidth="1"/>
     <col min="24" max="24" width="11.75" customWidth="1"/>
     <col min="28" max="28" width="15.375" customWidth="1"/>
@@ -1825,6 +1853,56 @@
       </c>
       <c r="T26" s="5" t="s">
         <v>123</v>
+      </c>
+    </row>
+    <row r="28" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="B28" t="s">
+        <v>125</v>
+      </c>
+      <c r="C28" t="s">
+        <v>124</v>
+      </c>
+      <c r="D28" t="s">
+        <v>126</v>
+      </c>
+      <c r="E28" t="s">
+        <v>94</v>
+      </c>
+      <c r="G28" s="6">
+        <v>1</v>
+      </c>
+      <c r="H28" s="6">
+        <v>1</v>
+      </c>
+      <c r="I28" s="6">
+        <v>2</v>
+      </c>
+      <c r="J28" s="6">
+        <v>5</v>
+      </c>
+      <c r="K28" t="s">
+        <v>127</v>
+      </c>
+      <c r="L28" t="s">
+        <v>128</v>
+      </c>
+      <c r="M28" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="N28" s="5">
+        <v>1</v>
+      </c>
+      <c r="S28" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="T28" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="U28" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="V28" s="6" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Datas/FoodDatas/FoodData.xlsx
+++ b/Config/Datas/FoodDatas/FoodData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\FoodDatas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84C92F9D-6924-437E-B0C8-569A460383C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B543E01-3166-4D64-B933-43C2067493E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="131">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -135,10 +135,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Chicken</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>苹果</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -339,10 +335,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>GA_食材位移</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>自己,DV_值~1,棋盘上</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -395,14 +387,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>完成烤串后\n小虾会选择一个方向移动\n并增加属性+1/+1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>周围空位,TRUE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>零食</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -548,6 +532,22 @@
   </si>
   <si>
     <t>DV_值,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GA_方向位移</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>随机</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>完成烤串后\n往随机一个方向移动\n并增加属性+1/+1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cookie</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -979,13 +979,13 @@
         <v>6</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="I1" s="13" t="s">
         <v>7</v>
@@ -997,10 +997,10 @@
         <v>22</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M1" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N1" s="10"/>
       <c r="O1" s="10"/>
@@ -1012,7 +1012,7 @@
       <c r="U1" s="10"/>
       <c r="V1" s="10"/>
       <c r="W1" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="X1" s="9"/>
       <c r="Y1" s="9"/>
@@ -1043,13 +1043,13 @@
         <v>9</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>10</v>
@@ -1064,7 +1064,7 @@
         <v>1</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N2" s="9"/>
       <c r="O2" s="9"/>
@@ -1076,7 +1076,7 @@
       <c r="U2" s="9"/>
       <c r="V2" s="9"/>
       <c r="W2" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="X2" s="10"/>
       <c r="Y2" s="10"/>
@@ -1107,11 +1107,11 @@
         <v>14</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>15</v>
@@ -1123,7 +1123,7 @@
         <v>23</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M3" s="1"/>
       <c r="N3" s="4"/>
@@ -1157,7 +1157,7 @@
         <v>6</v>
       </c>
       <c r="N4" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="O4" s="9"/>
       <c r="P4" s="9"/>
@@ -1168,13 +1168,13 @@
       <c r="U4" s="9"/>
       <c r="V4" s="9"/>
       <c r="W4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="X4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Y4" s="12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="Z4" s="12"/>
       <c r="AA4" s="12"/>
@@ -1183,7 +1183,7 @@
       <c r="AD4" s="12"/>
       <c r="AE4" s="12"/>
       <c r="AF4" s="10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AG4" s="10"/>
       <c r="AH4" s="10"/>
@@ -1208,13 +1208,13 @@
         <v>0</v>
       </c>
       <c r="O5" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P5" s="9"/>
       <c r="Q5" s="9"/>
       <c r="R5" s="9"/>
       <c r="S5" s="12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="T5" s="12"/>
       <c r="U5" s="12"/>
@@ -1223,11 +1223,11 @@
         <v>0</v>
       </c>
       <c r="Z5" s="12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AA5" s="12"/>
       <c r="AB5" s="12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AC5" s="12"/>
       <c r="AD5" s="12"/>
@@ -1253,13 +1253,13 @@
         <v>1</v>
       </c>
       <c r="O6" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P6" s="9"/>
       <c r="Q6" s="9"/>
       <c r="R6" s="9"/>
       <c r="S6" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="T6" s="12"/>
       <c r="U6" s="12"/>
@@ -1272,25 +1272,25 @@
       <c r="L7" s="7"/>
       <c r="M7" s="7"/>
       <c r="O7" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="P7" s="11" t="s">
         <v>33</v>
-      </c>
-      <c r="P7" s="11" t="s">
-        <v>34</v>
       </c>
       <c r="Q7" s="11"/>
       <c r="R7" s="11"/>
       <c r="S7" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="T7" s="11" t="s">
         <v>33</v>
-      </c>
-      <c r="T7" s="11" t="s">
-        <v>34</v>
       </c>
       <c r="U7" s="11"/>
       <c r="V7" s="11"/>
     </row>
     <row r="8" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B8" s="6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>18</v>
@@ -1309,7 +1309,7 @@
         <v>1</v>
       </c>
       <c r="I8" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J8" s="7">
         <v>5</v>
@@ -1318,19 +1318,19 @@
         <v>24</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M8" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="N8" s="6">
+        <v>1</v>
+      </c>
+      <c r="S8" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="T8" s="6" t="s">
         <v>59</v>
-      </c>
-      <c r="N8" s="6">
-        <v>1</v>
-      </c>
-      <c r="S8" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="T8" s="6" t="s">
-        <v>60</v>
       </c>
       <c r="X8" s="2"/>
       <c r="AB8" s="2"/>
@@ -1344,33 +1344,33 @@
       <c r="J9" s="7"/>
       <c r="K9" s="2"/>
       <c r="M9" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="N9" s="6">
+        <v>1</v>
+      </c>
+      <c r="S9" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="N9" s="6">
-        <v>1</v>
-      </c>
-      <c r="S9" s="2" t="s">
+      <c r="T9" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="U9" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="V9" s="6" t="s">
         <v>62</v>
-      </c>
-      <c r="T9" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="U9" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="V9" s="6" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B10" s="6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>21</v>
@@ -1383,7 +1383,7 @@
         <v>1</v>
       </c>
       <c r="I10" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J10" s="7">
         <v>5</v>
@@ -1392,34 +1392,34 @@
         <v>25</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="N10" s="6">
         <v>1</v>
       </c>
       <c r="O10" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="P10" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="P10" s="8" t="s">
+      <c r="Q10" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="R10" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="Q10" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="R10" s="6" t="s">
-        <v>49</v>
-      </c>
       <c r="S10" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="T10" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="U10" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2">
@@ -1431,13 +1431,13 @@
     </row>
     <row r="12" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B12" s="6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>21</v>
@@ -1450,7 +1450,7 @@
         <v>1</v>
       </c>
       <c r="I12" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J12" s="7">
         <v>5</v>
@@ -1459,49 +1459,49 @@
         <v>26</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="N12" s="6">
         <v>1</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q12" s="6">
         <v>2</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="T12" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="U12" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="14" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B14" s="6" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G14" s="2">
         <v>1</v>
@@ -1510,82 +1510,85 @@
         <v>1</v>
       </c>
       <c r="I14" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J14" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>27</v>
+        <v>130</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="M14" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N14" s="6">
         <v>1</v>
       </c>
       <c r="S14" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="T14" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="T14" s="6" t="s">
-        <v>55</v>
-      </c>
       <c r="U14" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="16" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B16" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D16" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="E16" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="G16" s="6">
+        <v>1</v>
+      </c>
+      <c r="H16" s="6">
+        <v>1</v>
+      </c>
+      <c r="I16" s="2">
+        <v>2</v>
+      </c>
+      <c r="J16" s="7">
+        <v>2</v>
+      </c>
+      <c r="K16" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="G16" s="6">
-        <v>1</v>
-      </c>
-      <c r="H16" s="6">
-        <v>1</v>
-      </c>
-      <c r="I16" s="2">
-        <v>5</v>
-      </c>
-      <c r="J16" s="7">
-        <v>5</v>
-      </c>
-      <c r="K16" s="6" t="s">
+      <c r="L16" t="s">
+        <v>129</v>
+      </c>
+      <c r="W16" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="X16" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y16" s="6">
+        <v>1</v>
+      </c>
+      <c r="AB16" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="AC16" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="L16" t="s">
-        <v>92</v>
-      </c>
-      <c r="W16" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="X16" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="Y16" s="6">
-        <v>1</v>
-      </c>
-      <c r="AB16" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="AC16" s="6" t="s">
-        <v>79</v>
-      </c>
       <c r="AD16" s="6" t="s">
-        <v>93</v>
+        <v>128</v>
+      </c>
+      <c r="AE16" s="6" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="17" spans="2:32" s="6" customFormat="1" x14ac:dyDescent="0.2">
@@ -1593,27 +1596,27 @@
         <v>2</v>
       </c>
       <c r="AB17" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AC17" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AD17" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AE17" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18" spans="2:32" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B18" s="6" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C18" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="D18" s="6" t="s">
         <v>80</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>82</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>21</v>
@@ -1625,45 +1628,45 @@
         <v>1</v>
       </c>
       <c r="I18" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J18" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K18" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="L18" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="N18" s="6">
+        <v>1</v>
+      </c>
+      <c r="S18" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="T18" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="U18" s="2" t="s">
         <v>81</v>
-      </c>
-      <c r="L18" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="M18" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="N18" s="6">
-        <v>1</v>
-      </c>
-      <c r="S18" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="T18" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="U18" s="2" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="20" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B20" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C20" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D20" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E20" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G20" s="6">
         <v>1</v>
@@ -1678,42 +1681,42 @@
         <v>5</v>
       </c>
       <c r="K20" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="M20" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="N20" s="5">
         <v>1</v>
       </c>
       <c r="O20" s="5" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="P20" s="5">
         <v>0</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="T20" s="6" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="U20" s="6" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="22" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B22" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C22" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D22" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E22" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G22" s="6">
         <v>2</v>
@@ -1728,36 +1731,36 @@
         <v>4</v>
       </c>
       <c r="K22" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="L22" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N22" s="5">
         <v>1</v>
       </c>
       <c r="S22" s="5" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="T22" s="5" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="U22" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="24" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B24" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C24" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E24" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G24" s="6">
         <v>1</v>
@@ -1772,13 +1775,13 @@
         <v>5</v>
       </c>
       <c r="K24" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="W24" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="X24" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Y24" s="6">
         <v>1</v>
@@ -1786,16 +1789,16 @@
       <c r="Z24" s="6"/>
       <c r="AA24" s="6"/>
       <c r="AB24" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AC24" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AD24" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AE24" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="AF24" s="6"/>
     </row>
@@ -1813,13 +1816,13 @@
     </row>
     <row r="26" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C26" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D26" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E26" t="s">
         <v>21</v>
@@ -1837,36 +1840,36 @@
         <v>4</v>
       </c>
       <c r="K26" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="L26" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="M26" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N26" s="5">
         <v>1</v>
       </c>
       <c r="S26" s="5" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="T26" s="5" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="28" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B28" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C28" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D28" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="E28" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G28" s="6">
         <v>1</v>
@@ -1881,28 +1884,28 @@
         <v>5</v>
       </c>
       <c r="K28" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L28" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="N28" s="5">
         <v>1</v>
       </c>
       <c r="S28" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="T28" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="U28" s="5" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="V28" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Datas/FoodDatas/FoodData.xlsx
+++ b/Config/Datas/FoodDatas/FoodData.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\FoodDatas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B543E01-3166-4D64-B933-43C2067493E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D5BD43C-972C-40E4-A94C-0C1970ED992F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="水果" sheetId="1" r:id="rId1"/>
+    <sheet name="蔬菜" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="133">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -339,26 +340,14 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>樱桃</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Cherry</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>成群结队的樱桃！</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>GA_直接修改当前烧烤值|DV_值,2|DV_值,2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>cherry</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>shrimp</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -375,18 +364,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>DV_周围食材数,cherry</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>被选中时</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>被选中时\n每与另一个樱桃相邻，则烧烤属性+2/+2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>零食</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -548,6 +529,34 @@
   </si>
   <si>
     <t>Cookie</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>稀有</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lemon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DV_周围食材数,lemon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>被选中时\n每与另一个柠檬相邻，则烧烤属性+2/+2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>柠檬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>挨在一起会发生化学反应！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lemon</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -934,7 +943,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AH28"/>
+  <dimension ref="A1:AH26"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="9" customWidth="1"/>
@@ -985,7 +994,7 @@
         <v>72</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="I1" s="13" t="s">
         <v>7</v>
@@ -1049,7 +1058,7 @@
         <v>73</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>10</v>
@@ -1111,7 +1120,7 @@
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>15</v>
@@ -1290,16 +1299,16 @@
     </row>
     <row r="8" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B8" s="6" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2">
@@ -1309,68 +1318,61 @@
         <v>1</v>
       </c>
       <c r="I8" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J8" s="7">
         <v>5</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="M8" s="6" t="s">
-        <v>58</v>
+        <v>50</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>84</v>
       </c>
       <c r="N8" s="6">
         <v>1</v>
       </c>
-      <c r="S8" s="8" t="s">
-        <v>51</v>
+      <c r="O8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="P8" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q8" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="R8" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="S8" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="T8" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="X8" s="2"/>
-      <c r="AB8" s="2"/>
+        <v>48</v>
+      </c>
+      <c r="U8" s="6" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="9" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="7"/>
       <c r="K9" s="2"/>
-      <c r="M9" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="N9" s="6">
-        <v>1</v>
-      </c>
-      <c r="S9" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="T9" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="U9" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="V9" s="6" t="s">
-        <v>62</v>
-      </c>
     </row>
     <row r="10" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B10" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>21</v>
@@ -1383,66 +1385,59 @@
         <v>1</v>
       </c>
       <c r="I10" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J10" s="7">
         <v>5</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="N10" s="6">
         <v>1</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="P10" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q10" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="P10" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="R10" s="6" t="s">
-        <v>48</v>
+      <c r="Q10" s="6">
+        <v>2</v>
       </c>
       <c r="S10" s="2" t="s">
         <v>34</v>
       </c>
       <c r="T10" s="6" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="U10" s="6" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="11" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="K11" s="2"/>
-    </row>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="12" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B12" s="6" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>28</v>
+        <v>86</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>39</v>
+        <v>86</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F12" s="2"/>
+        <v>85</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="G12" s="2">
         <v>1</v>
       </c>
@@ -1450,385 +1445,369 @@
         <v>1</v>
       </c>
       <c r="I12" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J12" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>26</v>
+        <v>125</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>88</v>
+        <v>64</v>
+      </c>
+      <c r="M12" s="6" t="s">
+        <v>58</v>
       </c>
       <c r="N12" s="6">
         <v>1</v>
       </c>
-      <c r="O12" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="P12" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q12" s="6">
-        <v>2</v>
-      </c>
-      <c r="S12" s="2" t="s">
-        <v>34</v>
+      <c r="S12" s="6" t="s">
+        <v>53</v>
       </c>
       <c r="T12" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="U12" s="6" t="s">
-        <v>54</v>
+      <c r="U12" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="13" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="14" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B14" s="6" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G14" s="2">
-        <v>1</v>
-      </c>
-      <c r="H14" s="2">
+        <v>74</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G14" s="6">
+        <v>1</v>
+      </c>
+      <c r="H14" s="6">
         <v>1</v>
       </c>
       <c r="I14" s="2">
         <v>2</v>
       </c>
       <c r="J14" s="7">
-        <v>3</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="L14" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="M14" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="N14" s="6">
-        <v>1</v>
-      </c>
-      <c r="S14" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="T14" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="U14" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="15" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2"/>
+        <v>2</v>
+      </c>
+      <c r="K14" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="L14" t="s">
+        <v>124</v>
+      </c>
+      <c r="W14" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="X14" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y14" s="6">
+        <v>1</v>
+      </c>
+      <c r="AB14" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="AC14" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD14" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="AE14" s="6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="Y15" s="6">
+        <v>2</v>
+      </c>
+      <c r="AB15" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC15" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="AD15" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE15" s="6" t="s">
+        <v>77</v>
+      </c>
+    </row>
     <row r="16" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B16" s="6" t="s">
-        <v>83</v>
+        <v>127</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>71</v>
+        <v>130</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>75</v>
+        <v>131</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="G16" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H16" s="6">
         <v>1</v>
       </c>
       <c r="I16" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J16" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="L16" t="s">
+        <v>132</v>
+      </c>
+      <c r="L16" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="W16" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="X16" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="Y16" s="6">
-        <v>1</v>
-      </c>
-      <c r="AB16" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="AC16" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="AD16" s="6" t="s">
+      <c r="M16" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="N16" s="6">
+        <v>1</v>
+      </c>
+      <c r="S16" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="T16" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="AE16" s="6" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="17" spans="2:32" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="Y17" s="6">
-        <v>2</v>
-      </c>
-      <c r="AB17" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AC17" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="AD17" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE17" s="6" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="18" spans="2:32" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>21</v>
+      <c r="U16" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="18" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="B18" t="s">
+        <v>88</v>
+      </c>
+      <c r="C18" t="s">
+        <v>89</v>
+      </c>
+      <c r="D18" t="s">
+        <v>90</v>
+      </c>
+      <c r="E18" t="s">
+        <v>85</v>
       </c>
       <c r="G18" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H18" s="6">
         <v>1</v>
       </c>
-      <c r="I18" s="2">
-        <v>4</v>
-      </c>
-      <c r="J18" s="7">
-        <v>4</v>
-      </c>
-      <c r="K18" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="L18" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="M18" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="N18" s="6">
-        <v>1</v>
-      </c>
-      <c r="S18" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="T18" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="U18" s="2" t="s">
-        <v>81</v>
+      <c r="I18" s="6">
+        <v>5</v>
+      </c>
+      <c r="J18" s="6">
+        <v>5</v>
+      </c>
+      <c r="K18" t="s">
+        <v>91</v>
+      </c>
+      <c r="M18" t="s">
+        <v>92</v>
+      </c>
+      <c r="N18" s="5">
+        <v>1</v>
+      </c>
+      <c r="O18" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="P18" s="5">
+        <v>0</v>
+      </c>
+      <c r="S18" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="T18" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="U18" s="6" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="20" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B20" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C20" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D20" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E20" t="s">
-        <v>90</v>
-      </c>
-      <c r="G20" s="6">
-        <v>1</v>
+        <v>85</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>126</v>
       </c>
       <c r="H20" s="6">
         <v>1</v>
       </c>
       <c r="I20" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J20" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K20" t="s">
-        <v>96</v>
-      </c>
-      <c r="M20" t="s">
-        <v>97</v>
+        <v>101</v>
+      </c>
+      <c r="L20" t="s">
+        <v>98</v>
+      </c>
+      <c r="M20" s="6" t="s">
+        <v>58</v>
       </c>
       <c r="N20" s="5">
         <v>1</v>
       </c>
-      <c r="O20" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="P20" s="5">
-        <v>0</v>
-      </c>
-      <c r="S20" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="T20" s="6" t="s">
+      <c r="S20" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="U20" s="6" t="s">
-        <v>99</v>
+      <c r="T20" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="U20" s="5" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="22" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B22" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C22" t="s">
-        <v>101</v>
-      </c>
-      <c r="D22" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E22" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="G22" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H22" s="6">
         <v>1</v>
       </c>
       <c r="I22" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J22" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K22" t="s">
-        <v>106</v>
-      </c>
-      <c r="L22" t="s">
-        <v>103</v>
-      </c>
-      <c r="M22" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="N22" s="5">
-        <v>1</v>
-      </c>
-      <c r="S22" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="T22" s="5" t="s">
+      <c r="W22" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="X22" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y22" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z22" s="6"/>
+      <c r="AA22" s="6"/>
+      <c r="AB22" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC22" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AD22" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AE22" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="U22" s="5" t="s">
-        <v>48</v>
-      </c>
+      <c r="AF22" s="6"/>
+    </row>
+    <row r="23" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="W23" s="6"/>
+      <c r="X23" s="6"/>
+      <c r="Y23" s="6"/>
+      <c r="Z23" s="6"/>
+      <c r="AA23" s="6"/>
+      <c r="AB23" s="2"/>
+      <c r="AC23" s="6"/>
+      <c r="AD23" s="6"/>
+      <c r="AE23" s="6"/>
+      <c r="AF23" s="6"/>
     </row>
     <row r="24" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B24" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C24" t="s">
-        <v>108</v>
+        <v>110</v>
+      </c>
+      <c r="D24" t="s">
+        <v>111</v>
       </c>
       <c r="E24" t="s">
-        <v>90</v>
-      </c>
-      <c r="G24" s="6">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>126</v>
       </c>
       <c r="H24" s="6">
         <v>1</v>
       </c>
       <c r="I24" s="6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J24" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K24" t="s">
-        <v>109</v>
-      </c>
-      <c r="W24" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="X24" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="Y24" s="6">
-        <v>1</v>
-      </c>
-      <c r="Z24" s="6"/>
-      <c r="AA24" s="6"/>
-      <c r="AB24" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="AC24" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="AD24" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="AE24" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="AF24" s="6"/>
-    </row>
-    <row r="25" spans="2:32" x14ac:dyDescent="0.2">
-      <c r="W25" s="6"/>
-      <c r="X25" s="6"/>
-      <c r="Y25" s="6"/>
-      <c r="Z25" s="6"/>
-      <c r="AA25" s="6"/>
-      <c r="AB25" s="2"/>
-      <c r="AC25" s="6"/>
-      <c r="AD25" s="6"/>
-      <c r="AE25" s="6"/>
-      <c r="AF25" s="6"/>
+        <v>78</v>
+      </c>
+      <c r="L24" t="s">
+        <v>112</v>
+      </c>
+      <c r="M24" t="s">
+        <v>58</v>
+      </c>
+      <c r="N24" s="5">
+        <v>1</v>
+      </c>
+      <c r="S24" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="T24" s="5" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="26" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C26" t="s">
         <v>115</v>
       </c>
       <c r="D26" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E26" t="s">
-        <v>21</v>
+        <v>85</v>
       </c>
       <c r="G26" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H26" s="6">
         <v>1</v>
@@ -1837,74 +1816,30 @@
         <v>2</v>
       </c>
       <c r="J26" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K26" t="s">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="L26" t="s">
-        <v>117</v>
-      </c>
-      <c r="M26" t="s">
-        <v>58</v>
+        <v>119</v>
+      </c>
+      <c r="M26" s="2" t="s">
+        <v>120</v>
       </c>
       <c r="N26" s="5">
         <v>1</v>
       </c>
       <c r="S26" s="5" t="s">
-        <v>118</v>
+        <v>61</v>
       </c>
       <c r="T26" s="5" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="28" spans="2:32" x14ac:dyDescent="0.2">
-      <c r="B28" t="s">
+        <v>54</v>
+      </c>
+      <c r="U26" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="C28" t="s">
-        <v>120</v>
-      </c>
-      <c r="D28" t="s">
-        <v>122</v>
-      </c>
-      <c r="E28" t="s">
-        <v>90</v>
-      </c>
-      <c r="G28" s="6">
-        <v>1</v>
-      </c>
-      <c r="H28" s="6">
-        <v>1</v>
-      </c>
-      <c r="I28" s="6">
-        <v>2</v>
-      </c>
-      <c r="J28" s="6">
-        <v>5</v>
-      </c>
-      <c r="K28" t="s">
-        <v>123</v>
-      </c>
-      <c r="L28" t="s">
-        <v>124</v>
-      </c>
-      <c r="M28" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="N28" s="5">
-        <v>1</v>
-      </c>
-      <c r="S28" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="T28" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="U28" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="V28" s="6" t="s">
+      <c r="V26" s="6" t="s">
         <v>77</v>
       </c>
     </row>
@@ -1929,4 +1864,456 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9BDF1B0-7733-4383-B476-4B5488719472}">
+  <dimension ref="A1:AH9"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="4" max="4" width="15.25" customWidth="1"/>
+    <col min="5" max="5" width="7.5" customWidth="1"/>
+    <col min="6" max="6" width="6.625" customWidth="1"/>
+    <col min="7" max="7" width="6" style="6" customWidth="1"/>
+    <col min="8" max="8" width="4.5" style="6" customWidth="1"/>
+    <col min="9" max="9" width="4.875" style="6" customWidth="1"/>
+    <col min="10" max="10" width="4.75" style="6" customWidth="1"/>
+    <col min="11" max="11" width="12.75" customWidth="1"/>
+    <col min="12" max="12" width="29.5" customWidth="1"/>
+    <col min="13" max="13" width="15.5" customWidth="1"/>
+    <col min="14" max="14" width="5.375" style="5" customWidth="1"/>
+    <col min="15" max="15" width="21.125" style="5" customWidth="1"/>
+    <col min="16" max="16" width="9.375" style="5" customWidth="1"/>
+    <col min="17" max="17" width="13.125" style="5" customWidth="1"/>
+    <col min="18" max="18" width="9.375" style="5" customWidth="1"/>
+    <col min="19" max="19" width="16.375" style="5" customWidth="1"/>
+    <col min="20" max="20" width="21" style="5" customWidth="1"/>
+    <col min="21" max="21" width="13.5" style="5" customWidth="1"/>
+    <col min="22" max="22" width="15.375" customWidth="1"/>
+    <col min="23" max="23" width="11.5" customWidth="1"/>
+    <col min="24" max="24" width="11.75" customWidth="1"/>
+    <col min="28" max="28" width="15.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="I1" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="N1" s="10"/>
+      <c r="O1" s="10"/>
+      <c r="P1" s="10"/>
+      <c r="Q1" s="10"/>
+      <c r="R1" s="10"/>
+      <c r="S1" s="10"/>
+      <c r="T1" s="10"/>
+      <c r="U1" s="10"/>
+      <c r="V1" s="10"/>
+      <c r="W1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="X1" s="9"/>
+      <c r="Y1" s="9"/>
+      <c r="Z1" s="9"/>
+      <c r="AA1" s="9"/>
+      <c r="AB1" s="9"/>
+      <c r="AC1" s="9"/>
+      <c r="AD1" s="9"/>
+      <c r="AE1" s="9"/>
+      <c r="AF1" s="9"/>
+      <c r="AG1" s="9"/>
+      <c r="AH1" s="9"/>
+    </row>
+    <row r="2" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="M2" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="N2" s="9"/>
+      <c r="O2" s="9"/>
+      <c r="P2" s="9"/>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="9"/>
+      <c r="S2" s="9"/>
+      <c r="T2" s="9"/>
+      <c r="U2" s="9"/>
+      <c r="V2" s="9"/>
+      <c r="W2" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="X2" s="10"/>
+      <c r="Y2" s="10"/>
+      <c r="Z2" s="10"/>
+      <c r="AA2" s="10"/>
+      <c r="AB2" s="10"/>
+      <c r="AC2" s="10"/>
+      <c r="AD2" s="10"/>
+      <c r="AE2" s="10"/>
+      <c r="AF2" s="10"/>
+      <c r="AG2" s="10"/>
+      <c r="AH2" s="10"/>
+    </row>
+    <row r="3" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M3" s="1"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4"/>
+      <c r="W3" s="1"/>
+      <c r="X3" s="1"/>
+      <c r="Y3" s="2"/>
+      <c r="Z3" s="1"/>
+      <c r="AA3" s="1"/>
+      <c r="AB3" s="1"/>
+      <c r="AC3" s="1"/>
+      <c r="AD3" s="1"/>
+      <c r="AE3" s="1"/>
+    </row>
+    <row r="4" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="N4" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="O4" s="9"/>
+      <c r="P4" s="9"/>
+      <c r="Q4" s="9"/>
+      <c r="R4" s="9"/>
+      <c r="S4" s="9"/>
+      <c r="T4" s="9"/>
+      <c r="U4" s="9"/>
+      <c r="V4" s="9"/>
+      <c r="W4" t="s">
+        <v>32</v>
+      </c>
+      <c r="X4" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y4" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z4" s="12"/>
+      <c r="AA4" s="12"/>
+      <c r="AB4" s="12"/>
+      <c r="AC4" s="12"/>
+      <c r="AD4" s="12"/>
+      <c r="AE4" s="12"/>
+      <c r="AF4" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="AG4" s="10"/>
+      <c r="AH4" s="10"/>
+    </row>
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="O5" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="P5" s="9"/>
+      <c r="Q5" s="9"/>
+      <c r="R5" s="9"/>
+      <c r="S5" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="T5" s="12"/>
+      <c r="U5" s="12"/>
+      <c r="V5" s="12"/>
+      <c r="Y5" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA5" s="12"/>
+      <c r="AB5" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC5" s="12"/>
+      <c r="AD5" s="12"/>
+      <c r="AE5" s="12"/>
+    </row>
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="O6" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="P6" s="9"/>
+      <c r="Q6" s="9"/>
+      <c r="R6" s="9"/>
+      <c r="S6" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="T6" s="12"/>
+      <c r="U6" s="12"/>
+      <c r="V6" s="12"/>
+    </row>
+    <row r="7" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+      <c r="O7" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="P7" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q7" s="11"/>
+      <c r="R7" s="11"/>
+      <c r="S7" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="T7" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="U7" s="11"/>
+      <c r="V7" s="11"/>
+    </row>
+    <row r="8" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2">
+        <v>1</v>
+      </c>
+      <c r="H8" s="2">
+        <v>1</v>
+      </c>
+      <c r="I8" s="2">
+        <v>1</v>
+      </c>
+      <c r="J8" s="7">
+        <v>5</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="M8" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="N8" s="6">
+        <v>1</v>
+      </c>
+      <c r="S8" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="T8" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="X8" s="2"/>
+      <c r="AB8" s="2"/>
+    </row>
+    <row r="9" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="2"/>
+      <c r="M9" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="N9" s="6">
+        <v>1</v>
+      </c>
+      <c r="S9" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="T9" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="U9" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="V9" s="6" t="s">
+        <v>62</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="P7:R7"/>
+    <mergeCell ref="T7:V7"/>
+    <mergeCell ref="O5:R5"/>
+    <mergeCell ref="S5:V5"/>
+    <mergeCell ref="Z5:AA5"/>
+    <mergeCell ref="AB5:AE5"/>
+    <mergeCell ref="O6:R6"/>
+    <mergeCell ref="S6:V6"/>
+    <mergeCell ref="M1:V1"/>
+    <mergeCell ref="W1:AH1"/>
+    <mergeCell ref="M2:V2"/>
+    <mergeCell ref="W2:AH2"/>
+    <mergeCell ref="N4:V4"/>
+    <mergeCell ref="Y4:AE4"/>
+    <mergeCell ref="AF4:AH4"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Config/Datas/FoodDatas/FoodData.xlsx
+++ b/Config/Datas/FoodDatas/FoodData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\FoodDatas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D5BD43C-972C-40E4-A94C-0C1970ED992F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AB277C0-BB0E-44F2-90C9-F155164AD618}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="水果" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="145">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -216,22 +216,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>DV_周围空位数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>DV_值,1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>如果食材周围有至少2个空位，则美味度+2、珍稀度+2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>如果食材周围有空位，则美味度+1、珍稀度+1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>GA_添加食材到烤串</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -280,14 +268,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>GA_为食材加属性|DV_值,1|DV_值,1|周围随机,DV_值~1,棋盘上+被选中</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>添加到烤串上时\n为周围随机1个未添加到烤串上的食材\n+2美味度 +2珍稀度</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>SE_监听事件</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -344,10 +324,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>GA_直接修改当前烧烤值|DV_值,2|DV_值,2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>shrimp</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -420,10 +396,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>添加到烤串上时，获得一层【丝滑】</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>GA_获得Buff</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -492,10 +464,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>QQ_suger</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>QQ弹弹~</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -504,10 +472,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>被撞击时，珍稀度+2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>被碰撞时</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -524,10 +488,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>完成烤串后\n往随机一个方向移动\n并增加属性+1/+1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Cookie</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -544,10 +504,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>被选中时\n每与另一个柠檬相邻，则烧烤属性+2/+2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>柠檬</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -557,6 +513,125 @@
   </si>
   <si>
     <t>Lemon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>碰撞时</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>被撞击时，珍稀度+5
+撞击时，美味度+5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GA_为食材加属性|DV_值,2|DV_值,3|周围随机,DV_值~1,棋盘上+被选中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GA_随机触发</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GA_直接修改当前烧烤值|DV_值,5|DV_值,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GA_直接修改当前烧烤值|DV_值,0|DV_值,5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GA_直接修改当前烧烤值|DV_值,3|DV_值,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>被选中时\n每与另一个柠檬相邻，则烧烤属性+3/+3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>如果食材周围有至少2个空位，则美味度+5、珍稀度+5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DV_值,7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>potato</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>土豆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Potato</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>被串取时，随机为串串+5珍稀度或+5美味度</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>完成串串后\n往随机一个方向移动\n并增加属性+2/+2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>串串构建完时
+若奥利奥是第一个食材
+则为串串美味度+7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>添加到串串上时，获得一层【丝滑】</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>串串构建完时
+若串上有且只有一个土豆
+则为串串属性值+6/+6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DV_值,6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>QQ_sug</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>a</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>r</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DV_串上某食材数量,potato</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>等于</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>添加到串串上时\n为周围随机2个未添加到串串上的食材\n+2美味度 +3珍稀度</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -564,7 +639,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -601,6 +676,13 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -622,7 +704,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -648,6 +730,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -658,10 +746,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -943,35 +1028,35 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AH26"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:AH28"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="4" max="4" width="15.25" customWidth="1"/>
     <col min="5" max="5" width="7.5" customWidth="1"/>
-    <col min="6" max="6" width="6.625" customWidth="1"/>
+    <col min="6" max="6" width="6.58203125" customWidth="1"/>
     <col min="7" max="7" width="6" style="6" customWidth="1"/>
     <col min="8" max="8" width="4.5" style="6" customWidth="1"/>
-    <col min="9" max="9" width="4.875" style="6" customWidth="1"/>
+    <col min="9" max="9" width="4.83203125" style="6" customWidth="1"/>
     <col min="10" max="10" width="4.75" style="6" customWidth="1"/>
     <col min="11" max="11" width="12.75" customWidth="1"/>
     <col min="12" max="12" width="29.5" customWidth="1"/>
     <col min="13" max="13" width="15.5" customWidth="1"/>
-    <col min="14" max="14" width="5.375" style="5" customWidth="1"/>
-    <col min="15" max="15" width="21.125" style="5" customWidth="1"/>
-    <col min="16" max="16" width="9.375" style="5" customWidth="1"/>
-    <col min="17" max="17" width="13.125" style="5" customWidth="1"/>
-    <col min="18" max="18" width="9.375" style="5" customWidth="1"/>
-    <col min="19" max="19" width="16.375" style="5" customWidth="1"/>
+    <col min="14" max="14" width="5.33203125" style="5" customWidth="1"/>
+    <col min="15" max="15" width="21.08203125" style="5" customWidth="1"/>
+    <col min="16" max="16" width="9.33203125" style="5" customWidth="1"/>
+    <col min="17" max="17" width="13.08203125" style="5" customWidth="1"/>
+    <col min="18" max="18" width="9.33203125" style="5" customWidth="1"/>
+    <col min="19" max="19" width="16.33203125" style="5" customWidth="1"/>
     <col min="20" max="20" width="21" style="5" customWidth="1"/>
     <col min="21" max="21" width="13.5" style="5" customWidth="1"/>
-    <col min="22" max="22" width="15.375" customWidth="1"/>
+    <col min="22" max="22" width="15.33203125" customWidth="1"/>
     <col min="23" max="23" width="11.5" customWidth="1"/>
     <col min="24" max="24" width="11.75" customWidth="1"/>
-    <col min="28" max="28" width="15.375" customWidth="1"/>
+    <col min="28" max="28" width="15.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -991,12 +1076,12 @@
         <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="I1" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="I1" s="9" t="s">
         <v>7</v>
       </c>
       <c r="J1" s="8" t="s">
@@ -1008,34 +1093,34 @@
       <c r="L1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="M1" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="N1" s="10"/>
-      <c r="O1" s="10"/>
-      <c r="P1" s="10"/>
-      <c r="Q1" s="10"/>
-      <c r="R1" s="10"/>
-      <c r="S1" s="10"/>
-      <c r="T1" s="10"/>
-      <c r="U1" s="10"/>
-      <c r="V1" s="10"/>
-      <c r="W1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="X1" s="9"/>
-      <c r="Y1" s="9"/>
-      <c r="Z1" s="9"/>
-      <c r="AA1" s="9"/>
-      <c r="AB1" s="9"/>
-      <c r="AC1" s="9"/>
-      <c r="AD1" s="9"/>
-      <c r="AE1" s="9"/>
-      <c r="AF1" s="9"/>
-      <c r="AG1" s="9"/>
-      <c r="AH1" s="9"/>
-    </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="M1" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="N1" s="12"/>
+      <c r="O1" s="12"/>
+      <c r="P1" s="12"/>
+      <c r="Q1" s="12"/>
+      <c r="R1" s="12"/>
+      <c r="S1" s="12"/>
+      <c r="T1" s="12"/>
+      <c r="U1" s="12"/>
+      <c r="V1" s="12"/>
+      <c r="W1" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="X1" s="11"/>
+      <c r="Y1" s="11"/>
+      <c r="Z1" s="11"/>
+      <c r="AA1" s="11"/>
+      <c r="AB1" s="11"/>
+      <c r="AC1" s="11"/>
+      <c r="AD1" s="11"/>
+      <c r="AE1" s="11"/>
+      <c r="AF1" s="11"/>
+      <c r="AG1" s="11"/>
+      <c r="AH1" s="11"/>
+    </row>
+    <row r="2" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1055,10 +1140,10 @@
         <v>36</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>10</v>
@@ -1072,34 +1157,34 @@
       <c r="L2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="M2" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="N2" s="9"/>
-      <c r="O2" s="9"/>
-      <c r="P2" s="9"/>
-      <c r="Q2" s="9"/>
-      <c r="R2" s="9"/>
-      <c r="S2" s="9"/>
-      <c r="T2" s="9"/>
-      <c r="U2" s="9"/>
-      <c r="V2" s="9"/>
-      <c r="W2" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="X2" s="10"/>
-      <c r="Y2" s="10"/>
-      <c r="Z2" s="10"/>
-      <c r="AA2" s="10"/>
-      <c r="AB2" s="10"/>
-      <c r="AC2" s="10"/>
-      <c r="AD2" s="10"/>
-      <c r="AE2" s="10"/>
-      <c r="AF2" s="10"/>
-      <c r="AG2" s="10"/>
-      <c r="AH2" s="10"/>
-    </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="M2" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="N2" s="11"/>
+      <c r="O2" s="11"/>
+      <c r="P2" s="11"/>
+      <c r="Q2" s="11"/>
+      <c r="R2" s="11"/>
+      <c r="S2" s="11"/>
+      <c r="T2" s="11"/>
+      <c r="U2" s="11"/>
+      <c r="V2" s="11"/>
+      <c r="W2" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="X2" s="12"/>
+      <c r="Y2" s="12"/>
+      <c r="Z2" s="12"/>
+      <c r="AA2" s="12"/>
+      <c r="AB2" s="12"/>
+      <c r="AC2" s="12"/>
+      <c r="AD2" s="12"/>
+      <c r="AE2" s="12"/>
+      <c r="AF2" s="12"/>
+      <c r="AG2" s="12"/>
+      <c r="AH2" s="12"/>
+    </row>
+    <row r="3" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -1120,7 +1205,7 @@
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>15</v>
@@ -1147,7 +1232,7 @@
       <c r="AD3" s="1"/>
       <c r="AE3" s="1"/>
     </row>
-    <row r="4" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1165,39 +1250,39 @@
       <c r="M4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="N4" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="O4" s="9"/>
-      <c r="P4" s="9"/>
-      <c r="Q4" s="9"/>
-      <c r="R4" s="9"/>
-      <c r="S4" s="9"/>
-      <c r="T4" s="9"/>
-      <c r="U4" s="9"/>
-      <c r="V4" s="9"/>
+      <c r="N4" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="O4" s="11"/>
+      <c r="P4" s="11"/>
+      <c r="Q4" s="11"/>
+      <c r="R4" s="11"/>
+      <c r="S4" s="11"/>
+      <c r="T4" s="11"/>
+      <c r="U4" s="11"/>
+      <c r="V4" s="11"/>
       <c r="W4" t="s">
         <v>32</v>
       </c>
       <c r="X4" t="s">
-        <v>66</v>
-      </c>
-      <c r="Y4" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y4" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="Z4" s="12"/>
-      <c r="AA4" s="12"/>
-      <c r="AB4" s="12"/>
-      <c r="AC4" s="12"/>
-      <c r="AD4" s="12"/>
-      <c r="AE4" s="12"/>
-      <c r="AF4" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="AG4" s="10"/>
-      <c r="AH4" s="10"/>
-    </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="Z4" s="10"/>
+      <c r="AA4" s="10"/>
+      <c r="AB4" s="10"/>
+      <c r="AC4" s="10"/>
+      <c r="AD4" s="10"/>
+      <c r="AE4" s="10"/>
+      <c r="AF4" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="AG4" s="12"/>
+      <c r="AH4" s="12"/>
+    </row>
+    <row r="5" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1216,33 +1301,33 @@
       <c r="N5" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="O5" s="9" t="s">
+      <c r="O5" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="P5" s="9"/>
-      <c r="Q5" s="9"/>
-      <c r="R5" s="9"/>
-      <c r="S5" s="12" t="s">
+      <c r="P5" s="11"/>
+      <c r="Q5" s="11"/>
+      <c r="R5" s="11"/>
+      <c r="S5" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="T5" s="12"/>
-      <c r="U5" s="12"/>
-      <c r="V5" s="12"/>
+      <c r="T5" s="10"/>
+      <c r="U5" s="10"/>
+      <c r="V5" s="10"/>
       <c r="Y5" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="Z5" s="12" t="s">
+      <c r="Z5" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="AA5" s="12"/>
-      <c r="AB5" s="12" t="s">
+      <c r="AA5" s="10"/>
+      <c r="AB5" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="AC5" s="12"/>
-      <c r="AD5" s="12"/>
-      <c r="AE5" s="12"/>
-    </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AC5" s="10"/>
+      <c r="AD5" s="10"/>
+      <c r="AE5" s="10"/>
+    </row>
+    <row r="6" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -1261,20 +1346,20 @@
       <c r="N6" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="O6" s="9" t="s">
+      <c r="O6" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="P6" s="9"/>
-      <c r="Q6" s="9"/>
-      <c r="R6" s="9"/>
-      <c r="S6" s="12" t="s">
+      <c r="P6" s="11"/>
+      <c r="Q6" s="11"/>
+      <c r="R6" s="11"/>
+      <c r="S6" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="T6" s="12"/>
-      <c r="U6" s="12"/>
-      <c r="V6" s="12"/>
-    </row>
-    <row r="7" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="T6" s="10"/>
+      <c r="U6" s="10"/>
+      <c r="V6" s="10"/>
+    </row>
+    <row r="7" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>3</v>
       </c>
@@ -1283,23 +1368,23 @@
       <c r="O7" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="P7" s="11" t="s">
+      <c r="P7" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="Q7" s="11"/>
-      <c r="R7" s="11"/>
+      <c r="Q7" s="13"/>
+      <c r="R7" s="13"/>
       <c r="S7" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="T7" s="11" t="s">
+      <c r="T7" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="U7" s="11"/>
-      <c r="V7" s="11"/>
-    </row>
-    <row r="8" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="U7" s="13"/>
+      <c r="V7" s="13"/>
+    </row>
+    <row r="8" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B8" s="6" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>27</v>
@@ -1318,7 +1403,7 @@
         <v>1</v>
       </c>
       <c r="I8" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J8" s="7">
         <v>5</v>
@@ -1327,46 +1412,37 @@
         <v>25</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>84</v>
+        <v>135</v>
+      </c>
+      <c r="M8" s="6" t="s">
+        <v>55</v>
       </c>
       <c r="N8" s="6">
         <v>1</v>
       </c>
-      <c r="O8" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="P8" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q8" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="R8" s="6" t="s">
-        <v>48</v>
-      </c>
+      <c r="O8" s="2"/>
+      <c r="P8" s="8"/>
       <c r="S8" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="T8" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="U8" s="6" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="9" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2">
+        <v>125</v>
+      </c>
+      <c r="T8" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="U8" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="K9" s="2"/>
-    </row>
-    <row r="10" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="T9" s="2"/>
+    </row>
+    <row r="10" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B10" s="6" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>28</v>
@@ -1385,19 +1461,19 @@
         <v>1</v>
       </c>
       <c r="I10" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J10" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>26</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>49</v>
+        <v>130</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="N10" s="6">
         <v>1</v>
@@ -1415,25 +1491,25 @@
         <v>34</v>
       </c>
       <c r="T10" s="6" t="s">
-        <v>54</v>
+        <v>88</v>
       </c>
       <c r="U10" s="6" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="11" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="12" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="12" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B12" s="6" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>38</v>
@@ -1445,113 +1521,113 @@
         <v>1</v>
       </c>
       <c r="I12" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J12" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>64</v>
+        <v>144</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="N12" s="6">
         <v>1</v>
       </c>
       <c r="S12" s="6" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="T12" s="6" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="U12" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="13" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="14" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B14" s="6" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C14" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="G14" s="6">
+        <v>1</v>
+      </c>
+      <c r="H14" s="6">
+        <v>1</v>
+      </c>
+      <c r="I14" s="2">
+        <v>4</v>
+      </c>
+      <c r="J14" s="7">
+        <v>4</v>
+      </c>
+      <c r="K14" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="D14" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="G14" s="6">
-        <v>1</v>
-      </c>
-      <c r="H14" s="6">
-        <v>1</v>
-      </c>
-      <c r="I14" s="2">
-        <v>2</v>
-      </c>
-      <c r="J14" s="7">
-        <v>2</v>
-      </c>
-      <c r="K14" s="6" t="s">
-        <v>76</v>
-      </c>
       <c r="L14" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="W14" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="X14" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="X14" s="2" t="s">
-        <v>70</v>
-      </c>
       <c r="Y14" s="6">
         <v>1</v>
       </c>
       <c r="AB14" s="3" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="AC14" s="6" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="AD14" s="6" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="AE14" s="6" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="15" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="Y15" s="6">
         <v>2</v>
       </c>
       <c r="AB15" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="AC15" s="6" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="AD15" s="6" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="AE15" s="6" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="16" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B16" s="6" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>21</v>
@@ -1569,63 +1645,66 @@
         <v>3</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="L16" s="6" t="s">
         <v>129</v>
       </c>
       <c r="M16" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="N16" s="6">
+        <v>1</v>
+      </c>
+      <c r="S16" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="T16" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="U16" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="18" spans="1:32" ht="42" x14ac:dyDescent="0.3">
+      <c r="B18" t="s">
+        <v>82</v>
+      </c>
+      <c r="C18" t="s">
+        <v>83</v>
+      </c>
+      <c r="D18" t="s">
         <v>84</v>
       </c>
-      <c r="N16" s="6">
-        <v>1</v>
-      </c>
-      <c r="S16" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="T16" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="U16" s="2" t="s">
+      <c r="E18" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="18" spans="2:32" x14ac:dyDescent="0.2">
-      <c r="B18" t="s">
-        <v>88</v>
-      </c>
-      <c r="C18" t="s">
-        <v>89</v>
-      </c>
-      <c r="D18" t="s">
-        <v>90</v>
-      </c>
-      <c r="E18" t="s">
+      <c r="G18" s="6">
+        <v>1</v>
+      </c>
+      <c r="H18" s="6">
+        <v>1</v>
+      </c>
+      <c r="I18" s="6">
+        <v>6</v>
+      </c>
+      <c r="J18" s="6">
+        <v>4</v>
+      </c>
+      <c r="K18" t="s">
         <v>85</v>
       </c>
-      <c r="G18" s="6">
-        <v>1</v>
-      </c>
-      <c r="H18" s="6">
-        <v>1</v>
-      </c>
-      <c r="I18" s="6">
-        <v>5</v>
-      </c>
-      <c r="J18" s="6">
-        <v>5</v>
-      </c>
-      <c r="K18" t="s">
-        <v>91</v>
+      <c r="L18" s="14" t="s">
+        <v>137</v>
       </c>
       <c r="M18" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="N18" s="5">
         <v>1</v>
       </c>
       <c r="O18" s="5" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="P18" s="5">
         <v>0</v>
@@ -1634,68 +1713,71 @@
         <v>34</v>
       </c>
       <c r="T18" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="U18" s="6" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="20" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B20" t="s">
+        <v>89</v>
+      </c>
+      <c r="C20" t="s">
+        <v>90</v>
+      </c>
+      <c r="D20" t="s">
+        <v>91</v>
+      </c>
+      <c r="E20" t="s">
+        <v>79</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="H20" s="6">
+        <v>1</v>
+      </c>
+      <c r="I20" s="6">
+        <v>2</v>
+      </c>
+      <c r="J20" s="6">
+        <v>20</v>
+      </c>
+      <c r="K20" t="s">
         <v>94</v>
       </c>
-      <c r="U18" s="6" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="20" spans="2:32" x14ac:dyDescent="0.2">
-      <c r="B20" t="s">
+      <c r="L20" t="s">
+        <v>138</v>
+      </c>
+      <c r="M20" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="N20" s="5">
+        <v>1</v>
+      </c>
+      <c r="S20" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="T20" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="U20" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="22" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>17</v>
+      </c>
+      <c r="B22" t="s">
         <v>95</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C22" t="s">
         <v>96</v>
       </c>
-      <c r="D20" t="s">
-        <v>97</v>
-      </c>
-      <c r="E20" t="s">
-        <v>85</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="H20" s="6">
-        <v>1</v>
-      </c>
-      <c r="I20" s="6">
-        <v>4</v>
-      </c>
-      <c r="J20" s="6">
-        <v>4</v>
-      </c>
-      <c r="K20" t="s">
-        <v>101</v>
-      </c>
-      <c r="L20" t="s">
-        <v>98</v>
-      </c>
-      <c r="M20" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="N20" s="5">
-        <v>1</v>
-      </c>
-      <c r="S20" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="T20" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="U20" s="5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="22" spans="2:32" x14ac:dyDescent="0.2">
-      <c r="B22" t="s">
-        <v>102</v>
-      </c>
-      <c r="C22" t="s">
-        <v>103</v>
-      </c>
       <c r="E22" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="G22" s="6">
         <v>1</v>
@@ -1710,13 +1792,13 @@
         <v>5</v>
       </c>
       <c r="K22" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="W22" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="X22" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="X22" s="2" t="s">
-        <v>70</v>
       </c>
       <c r="Y22" s="6">
         <v>1</v>
@@ -1724,20 +1806,20 @@
       <c r="Z22" s="6"/>
       <c r="AA22" s="6"/>
       <c r="AB22" s="3" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="AC22" s="6" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="AD22" s="6" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="AE22" s="3" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="AF22" s="6"/>
     </row>
-    <row r="23" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:32" x14ac:dyDescent="0.3">
       <c r="W23" s="6"/>
       <c r="X23" s="6"/>
       <c r="Y23" s="6"/>
@@ -1749,108 +1831,178 @@
       <c r="AE23" s="6"/>
       <c r="AF23" s="6"/>
     </row>
-    <row r="24" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="C24" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="D24" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="E24" t="s">
         <v>21</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="H24" s="6">
         <v>1</v>
       </c>
       <c r="I24" s="6">
+        <v>5</v>
+      </c>
+      <c r="J24" s="6">
+        <v>5</v>
+      </c>
+      <c r="K24" t="s">
+        <v>73</v>
+      </c>
+      <c r="L24" t="s">
+        <v>105</v>
+      </c>
+      <c r="M24" t="s">
+        <v>55</v>
+      </c>
+      <c r="N24" s="5">
+        <v>1</v>
+      </c>
+      <c r="S24" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="T24" s="5" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="26" spans="1:32" ht="30.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B26" t="s">
+        <v>141</v>
+      </c>
+      <c r="C26" t="s">
+        <v>108</v>
+      </c>
+      <c r="D26" t="s">
+        <v>109</v>
+      </c>
+      <c r="E26" t="s">
+        <v>79</v>
+      </c>
+      <c r="G26" s="6">
+        <v>1</v>
+      </c>
+      <c r="H26" s="6">
+        <v>1</v>
+      </c>
+      <c r="I26" s="6">
+        <v>5</v>
+      </c>
+      <c r="J26" s="6">
+        <v>10</v>
+      </c>
+      <c r="K26" t="s">
+        <v>110</v>
+      </c>
+      <c r="L26" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="M26" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="N26" s="5">
+        <v>1</v>
+      </c>
+      <c r="S26" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="T26" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="U26" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="V26" s="6" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="27" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="M27" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="N27" s="5">
         <v>2</v>
       </c>
-      <c r="J24" s="6">
+      <c r="S27" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="T27" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="U27" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="V27" s="6" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="28" spans="1:32" ht="42" x14ac:dyDescent="0.3">
+      <c r="B28" t="s">
+        <v>132</v>
+      </c>
+      <c r="C28" t="s">
+        <v>133</v>
+      </c>
+      <c r="E28" t="s">
+        <v>19</v>
+      </c>
+      <c r="G28" s="6">
+        <v>1</v>
+      </c>
+      <c r="H28" s="6">
+        <v>1</v>
+      </c>
+      <c r="I28" s="6">
         <v>4</v>
       </c>
-      <c r="K24" t="s">
-        <v>78</v>
-      </c>
-      <c r="L24" t="s">
-        <v>112</v>
-      </c>
-      <c r="M24" t="s">
-        <v>58</v>
-      </c>
-      <c r="N24" s="5">
-        <v>1</v>
-      </c>
-      <c r="S24" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="T24" s="5" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="26" spans="2:32" x14ac:dyDescent="0.2">
-      <c r="B26" t="s">
-        <v>116</v>
-      </c>
-      <c r="C26" t="s">
-        <v>115</v>
-      </c>
-      <c r="D26" t="s">
-        <v>117</v>
-      </c>
-      <c r="E26" t="s">
-        <v>85</v>
-      </c>
-      <c r="G26" s="6">
-        <v>1</v>
-      </c>
-      <c r="H26" s="6">
-        <v>1</v>
-      </c>
-      <c r="I26" s="6">
-        <v>2</v>
-      </c>
-      <c r="J26" s="6">
-        <v>5</v>
-      </c>
-      <c r="K26" t="s">
-        <v>118</v>
-      </c>
-      <c r="L26" t="s">
-        <v>119</v>
-      </c>
-      <c r="M26" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="N26" s="5">
-        <v>1</v>
-      </c>
-      <c r="S26" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="T26" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="U26" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="V26" s="6" t="s">
-        <v>77</v>
+      <c r="J28" s="6">
+        <v>4</v>
+      </c>
+      <c r="K28" t="s">
+        <v>134</v>
+      </c>
+      <c r="L28" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="M28" t="s">
+        <v>86</v>
+      </c>
+      <c r="N28" s="5">
+        <v>1</v>
+      </c>
+      <c r="O28" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="P28" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q28" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="R28" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="S28" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="T28" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="U28" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="Z5:AA5"/>
-    <mergeCell ref="AB5:AE5"/>
-    <mergeCell ref="W1:AH1"/>
-    <mergeCell ref="W2:AH2"/>
-    <mergeCell ref="Y4:AE4"/>
-    <mergeCell ref="AF4:AH4"/>
     <mergeCell ref="M2:V2"/>
     <mergeCell ref="M1:V1"/>
     <mergeCell ref="O6:R6"/>
@@ -1860,6 +2012,12 @@
     <mergeCell ref="S6:V6"/>
     <mergeCell ref="S5:V5"/>
     <mergeCell ref="N4:V4"/>
+    <mergeCell ref="Z5:AA5"/>
+    <mergeCell ref="AB5:AE5"/>
+    <mergeCell ref="W1:AH1"/>
+    <mergeCell ref="W2:AH2"/>
+    <mergeCell ref="Y4:AE4"/>
+    <mergeCell ref="AF4:AH4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1869,33 +2027,33 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9BDF1B0-7733-4383-B476-4B5488719472}">
   <dimension ref="A1:AH9"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="15.25" customWidth="1"/>
     <col min="5" max="5" width="7.5" customWidth="1"/>
-    <col min="6" max="6" width="6.625" customWidth="1"/>
+    <col min="6" max="6" width="6.58203125" customWidth="1"/>
     <col min="7" max="7" width="6" style="6" customWidth="1"/>
     <col min="8" max="8" width="4.5" style="6" customWidth="1"/>
-    <col min="9" max="9" width="4.875" style="6" customWidth="1"/>
+    <col min="9" max="9" width="4.83203125" style="6" customWidth="1"/>
     <col min="10" max="10" width="4.75" style="6" customWidth="1"/>
     <col min="11" max="11" width="12.75" customWidth="1"/>
     <col min="12" max="12" width="29.5" customWidth="1"/>
     <col min="13" max="13" width="15.5" customWidth="1"/>
-    <col min="14" max="14" width="5.375" style="5" customWidth="1"/>
-    <col min="15" max="15" width="21.125" style="5" customWidth="1"/>
-    <col min="16" max="16" width="9.375" style="5" customWidth="1"/>
-    <col min="17" max="17" width="13.125" style="5" customWidth="1"/>
-    <col min="18" max="18" width="9.375" style="5" customWidth="1"/>
-    <col min="19" max="19" width="16.375" style="5" customWidth="1"/>
+    <col min="14" max="14" width="5.33203125" style="5" customWidth="1"/>
+    <col min="15" max="15" width="21.08203125" style="5" customWidth="1"/>
+    <col min="16" max="16" width="9.33203125" style="5" customWidth="1"/>
+    <col min="17" max="17" width="13.08203125" style="5" customWidth="1"/>
+    <col min="18" max="18" width="9.33203125" style="5" customWidth="1"/>
+    <col min="19" max="19" width="16.33203125" style="5" customWidth="1"/>
     <col min="20" max="20" width="21" style="5" customWidth="1"/>
     <col min="21" max="21" width="13.5" style="5" customWidth="1"/>
-    <col min="22" max="22" width="15.375" customWidth="1"/>
+    <col min="22" max="22" width="15.33203125" customWidth="1"/>
     <col min="23" max="23" width="11.5" customWidth="1"/>
     <col min="24" max="24" width="11.75" customWidth="1"/>
-    <col min="28" max="28" width="15.375" customWidth="1"/>
+    <col min="28" max="28" width="15.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -1915,12 +2073,12 @@
         <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="I1" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="I1" s="9" t="s">
         <v>7</v>
       </c>
       <c r="J1" s="8" t="s">
@@ -1932,34 +2090,34 @@
       <c r="L1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="M1" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="N1" s="10"/>
-      <c r="O1" s="10"/>
-      <c r="P1" s="10"/>
-      <c r="Q1" s="10"/>
-      <c r="R1" s="10"/>
-      <c r="S1" s="10"/>
-      <c r="T1" s="10"/>
-      <c r="U1" s="10"/>
-      <c r="V1" s="10"/>
-      <c r="W1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="X1" s="9"/>
-      <c r="Y1" s="9"/>
-      <c r="Z1" s="9"/>
-      <c r="AA1" s="9"/>
-      <c r="AB1" s="9"/>
-      <c r="AC1" s="9"/>
-      <c r="AD1" s="9"/>
-      <c r="AE1" s="9"/>
-      <c r="AF1" s="9"/>
-      <c r="AG1" s="9"/>
-      <c r="AH1" s="9"/>
-    </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="M1" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="N1" s="12"/>
+      <c r="O1" s="12"/>
+      <c r="P1" s="12"/>
+      <c r="Q1" s="12"/>
+      <c r="R1" s="12"/>
+      <c r="S1" s="12"/>
+      <c r="T1" s="12"/>
+      <c r="U1" s="12"/>
+      <c r="V1" s="12"/>
+      <c r="W1" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="X1" s="11"/>
+      <c r="Y1" s="11"/>
+      <c r="Z1" s="11"/>
+      <c r="AA1" s="11"/>
+      <c r="AB1" s="11"/>
+      <c r="AC1" s="11"/>
+      <c r="AD1" s="11"/>
+      <c r="AE1" s="11"/>
+      <c r="AF1" s="11"/>
+      <c r="AG1" s="11"/>
+      <c r="AH1" s="11"/>
+    </row>
+    <row r="2" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1979,10 +2137,10 @@
         <v>36</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>10</v>
@@ -1996,34 +2154,34 @@
       <c r="L2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="M2" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="N2" s="9"/>
-      <c r="O2" s="9"/>
-      <c r="P2" s="9"/>
-      <c r="Q2" s="9"/>
-      <c r="R2" s="9"/>
-      <c r="S2" s="9"/>
-      <c r="T2" s="9"/>
-      <c r="U2" s="9"/>
-      <c r="V2" s="9"/>
-      <c r="W2" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="X2" s="10"/>
-      <c r="Y2" s="10"/>
-      <c r="Z2" s="10"/>
-      <c r="AA2" s="10"/>
-      <c r="AB2" s="10"/>
-      <c r="AC2" s="10"/>
-      <c r="AD2" s="10"/>
-      <c r="AE2" s="10"/>
-      <c r="AF2" s="10"/>
-      <c r="AG2" s="10"/>
-      <c r="AH2" s="10"/>
-    </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="M2" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="N2" s="11"/>
+      <c r="O2" s="11"/>
+      <c r="P2" s="11"/>
+      <c r="Q2" s="11"/>
+      <c r="R2" s="11"/>
+      <c r="S2" s="11"/>
+      <c r="T2" s="11"/>
+      <c r="U2" s="11"/>
+      <c r="V2" s="11"/>
+      <c r="W2" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="X2" s="12"/>
+      <c r="Y2" s="12"/>
+      <c r="Z2" s="12"/>
+      <c r="AA2" s="12"/>
+      <c r="AB2" s="12"/>
+      <c r="AC2" s="12"/>
+      <c r="AD2" s="12"/>
+      <c r="AE2" s="12"/>
+      <c r="AF2" s="12"/>
+      <c r="AG2" s="12"/>
+      <c r="AH2" s="12"/>
+    </row>
+    <row r="3" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -2044,7 +2202,7 @@
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>15</v>
@@ -2071,7 +2229,7 @@
       <c r="AD3" s="1"/>
       <c r="AE3" s="1"/>
     </row>
-    <row r="4" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2089,39 +2247,39 @@
       <c r="M4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="N4" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="O4" s="9"/>
-      <c r="P4" s="9"/>
-      <c r="Q4" s="9"/>
-      <c r="R4" s="9"/>
-      <c r="S4" s="9"/>
-      <c r="T4" s="9"/>
-      <c r="U4" s="9"/>
-      <c r="V4" s="9"/>
+      <c r="N4" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="O4" s="11"/>
+      <c r="P4" s="11"/>
+      <c r="Q4" s="11"/>
+      <c r="R4" s="11"/>
+      <c r="S4" s="11"/>
+      <c r="T4" s="11"/>
+      <c r="U4" s="11"/>
+      <c r="V4" s="11"/>
       <c r="W4" t="s">
         <v>32</v>
       </c>
       <c r="X4" t="s">
-        <v>66</v>
-      </c>
-      <c r="Y4" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y4" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="Z4" s="12"/>
-      <c r="AA4" s="12"/>
-      <c r="AB4" s="12"/>
-      <c r="AC4" s="12"/>
-      <c r="AD4" s="12"/>
-      <c r="AE4" s="12"/>
-      <c r="AF4" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="AG4" s="10"/>
-      <c r="AH4" s="10"/>
-    </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="Z4" s="10"/>
+      <c r="AA4" s="10"/>
+      <c r="AB4" s="10"/>
+      <c r="AC4" s="10"/>
+      <c r="AD4" s="10"/>
+      <c r="AE4" s="10"/>
+      <c r="AF4" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="AG4" s="12"/>
+      <c r="AH4" s="12"/>
+    </row>
+    <row r="5" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2140,33 +2298,33 @@
       <c r="N5" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="O5" s="9" t="s">
+      <c r="O5" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="P5" s="9"/>
-      <c r="Q5" s="9"/>
-      <c r="R5" s="9"/>
-      <c r="S5" s="12" t="s">
+      <c r="P5" s="11"/>
+      <c r="Q5" s="11"/>
+      <c r="R5" s="11"/>
+      <c r="S5" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="T5" s="12"/>
-      <c r="U5" s="12"/>
-      <c r="V5" s="12"/>
+      <c r="T5" s="10"/>
+      <c r="U5" s="10"/>
+      <c r="V5" s="10"/>
       <c r="Y5" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="Z5" s="12" t="s">
+      <c r="Z5" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="AA5" s="12"/>
-      <c r="AB5" s="12" t="s">
+      <c r="AA5" s="10"/>
+      <c r="AB5" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="AC5" s="12"/>
-      <c r="AD5" s="12"/>
-      <c r="AE5" s="12"/>
-    </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AC5" s="10"/>
+      <c r="AD5" s="10"/>
+      <c r="AE5" s="10"/>
+    </row>
+    <row r="6" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -2185,20 +2343,20 @@
       <c r="N6" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="O6" s="9" t="s">
+      <c r="O6" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="P6" s="9"/>
-      <c r="Q6" s="9"/>
-      <c r="R6" s="9"/>
-      <c r="S6" s="12" t="s">
+      <c r="P6" s="11"/>
+      <c r="Q6" s="11"/>
+      <c r="R6" s="11"/>
+      <c r="S6" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="T6" s="12"/>
-      <c r="U6" s="12"/>
-      <c r="V6" s="12"/>
-    </row>
-    <row r="7" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="T6" s="10"/>
+      <c r="U6" s="10"/>
+      <c r="V6" s="10"/>
+    </row>
+    <row r="7" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>3</v>
       </c>
@@ -2207,23 +2365,26 @@
       <c r="O7" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="P7" s="11" t="s">
+      <c r="P7" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="Q7" s="11"/>
-      <c r="R7" s="11"/>
+      <c r="Q7" s="13"/>
+      <c r="R7" s="13"/>
       <c r="S7" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="T7" s="11" t="s">
+      <c r="T7" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="U7" s="11"/>
-      <c r="V7" s="11"/>
-    </row>
-    <row r="8" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="U7" s="13"/>
+      <c r="V7" s="13"/>
+    </row>
+    <row r="8" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="6" t="s">
+        <v>17</v>
+      </c>
       <c r="B8" s="6" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>18</v>
@@ -2251,24 +2412,27 @@
         <v>24</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="M8" s="6" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="N8" s="6">
         <v>1</v>
       </c>
       <c r="S8" s="8" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="T8" s="6" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="X8" s="2"/>
       <c r="AB8" s="2"/>
     </row>
-    <row r="9" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="6" t="s">
+        <v>17</v>
+      </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
@@ -2277,31 +2441,26 @@
       <c r="J9" s="7"/>
       <c r="K9" s="2"/>
       <c r="M9" s="6" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="N9" s="6">
         <v>1</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="T9" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="U9" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V9" s="6" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="P7:R7"/>
-    <mergeCell ref="T7:V7"/>
-    <mergeCell ref="O5:R5"/>
-    <mergeCell ref="S5:V5"/>
-    <mergeCell ref="Z5:AA5"/>
     <mergeCell ref="AB5:AE5"/>
     <mergeCell ref="O6:R6"/>
     <mergeCell ref="S6:V6"/>
@@ -2312,6 +2471,11 @@
     <mergeCell ref="N4:V4"/>
     <mergeCell ref="Y4:AE4"/>
     <mergeCell ref="AF4:AH4"/>
+    <mergeCell ref="P7:R7"/>
+    <mergeCell ref="T7:V7"/>
+    <mergeCell ref="O5:R5"/>
+    <mergeCell ref="S5:V5"/>
+    <mergeCell ref="Z5:AA5"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/Datas/FoodDatas/FoodData.xlsx
+++ b/Config/Datas/FoodDatas/FoodData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\FoodDatas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AB277C0-BB0E-44F2-90C9-F155164AD618}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA516040-32D5-4355-9CD8-58698A9A14E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="14290" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="水果" sheetId="1" r:id="rId1"/>
@@ -734,7 +734,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -746,7 +746,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1029,34 +1029,34 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AH28"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="4" max="4" width="15.25" customWidth="1"/>
     <col min="5" max="5" width="7.5" customWidth="1"/>
-    <col min="6" max="6" width="6.58203125" customWidth="1"/>
+    <col min="6" max="6" width="6.625" customWidth="1"/>
     <col min="7" max="7" width="6" style="6" customWidth="1"/>
     <col min="8" max="8" width="4.5" style="6" customWidth="1"/>
-    <col min="9" max="9" width="4.83203125" style="6" customWidth="1"/>
+    <col min="9" max="9" width="4.875" style="6" customWidth="1"/>
     <col min="10" max="10" width="4.75" style="6" customWidth="1"/>
     <col min="11" max="11" width="12.75" customWidth="1"/>
     <col min="12" max="12" width="29.5" customWidth="1"/>
     <col min="13" max="13" width="15.5" customWidth="1"/>
-    <col min="14" max="14" width="5.33203125" style="5" customWidth="1"/>
-    <col min="15" max="15" width="21.08203125" style="5" customWidth="1"/>
-    <col min="16" max="16" width="9.33203125" style="5" customWidth="1"/>
-    <col min="17" max="17" width="13.08203125" style="5" customWidth="1"/>
-    <col min="18" max="18" width="9.33203125" style="5" customWidth="1"/>
-    <col min="19" max="19" width="16.33203125" style="5" customWidth="1"/>
+    <col min="14" max="14" width="5.375" style="5" customWidth="1"/>
+    <col min="15" max="15" width="21.125" style="5" customWidth="1"/>
+    <col min="16" max="16" width="9.375" style="5" customWidth="1"/>
+    <col min="17" max="17" width="13.125" style="5" customWidth="1"/>
+    <col min="18" max="18" width="9.375" style="5" customWidth="1"/>
+    <col min="19" max="19" width="16.375" style="5" customWidth="1"/>
     <col min="20" max="20" width="21" style="5" customWidth="1"/>
     <col min="21" max="21" width="13.5" style="5" customWidth="1"/>
-    <col min="22" max="22" width="15.33203125" customWidth="1"/>
+    <col min="22" max="22" width="15.375" customWidth="1"/>
     <col min="23" max="23" width="11.5" customWidth="1"/>
     <col min="24" max="24" width="11.75" customWidth="1"/>
-    <col min="28" max="28" width="15.33203125" customWidth="1"/>
+    <col min="28" max="28" width="15.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -1120,7 +1120,7 @@
       <c r="AG1" s="11"/>
       <c r="AH1" s="11"/>
     </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1184,7 +1184,7 @@
       <c r="AG2" s="12"/>
       <c r="AH2" s="12"/>
     </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -1232,7 +1232,7 @@
       <c r="AD3" s="1"/>
       <c r="AE3" s="1"/>
     </row>
-    <row r="4" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1267,22 +1267,22 @@
       <c r="X4" t="s">
         <v>61</v>
       </c>
-      <c r="Y4" s="10" t="s">
+      <c r="Y4" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="Z4" s="10"/>
-      <c r="AA4" s="10"/>
-      <c r="AB4" s="10"/>
-      <c r="AC4" s="10"/>
-      <c r="AD4" s="10"/>
-      <c r="AE4" s="10"/>
+      <c r="Z4" s="14"/>
+      <c r="AA4" s="14"/>
+      <c r="AB4" s="14"/>
+      <c r="AC4" s="14"/>
+      <c r="AD4" s="14"/>
+      <c r="AE4" s="14"/>
       <c r="AF4" s="12" t="s">
         <v>64</v>
       </c>
       <c r="AG4" s="12"/>
       <c r="AH4" s="12"/>
     </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1307,27 +1307,27 @@
       <c r="P5" s="11"/>
       <c r="Q5" s="11"/>
       <c r="R5" s="11"/>
-      <c r="S5" s="10" t="s">
+      <c r="S5" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="T5" s="10"/>
-      <c r="U5" s="10"/>
-      <c r="V5" s="10"/>
+      <c r="T5" s="14"/>
+      <c r="U5" s="14"/>
+      <c r="V5" s="14"/>
       <c r="Y5" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="Z5" s="10" t="s">
+      <c r="Z5" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="AA5" s="10"/>
-      <c r="AB5" s="10" t="s">
+      <c r="AA5" s="14"/>
+      <c r="AB5" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="AC5" s="10"/>
-      <c r="AD5" s="10"/>
-      <c r="AE5" s="10"/>
-    </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AC5" s="14"/>
+      <c r="AD5" s="14"/>
+      <c r="AE5" s="14"/>
+    </row>
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -1352,14 +1352,14 @@
       <c r="P6" s="11"/>
       <c r="Q6" s="11"/>
       <c r="R6" s="11"/>
-      <c r="S6" s="10" t="s">
+      <c r="S6" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="T6" s="10"/>
-      <c r="U6" s="10"/>
-      <c r="V6" s="10"/>
-    </row>
-    <row r="7" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="T6" s="14"/>
+      <c r="U6" s="14"/>
+      <c r="V6" s="14"/>
+    </row>
+    <row r="7" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
         <v>3</v>
       </c>
@@ -1382,7 +1382,7 @@
       <c r="U7" s="13"/>
       <c r="V7" s="13"/>
     </row>
-    <row r="8" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B8" s="6" t="s">
         <v>76</v>
       </c>
@@ -1432,7 +1432,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="9" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
@@ -1440,7 +1440,7 @@
       <c r="K9" s="2"/>
       <c r="T9" s="2"/>
     </row>
-    <row r="10" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B10" s="6" t="s">
         <v>75</v>
       </c>
@@ -1497,8 +1497,8 @@
         <v>88</v>
       </c>
     </row>
-    <row r="11" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="12" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="12" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B12" s="6" t="s">
         <v>81</v>
       </c>
@@ -1548,8 +1548,8 @@
         <v>124</v>
       </c>
     </row>
-    <row r="13" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="14" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B14" s="6" t="s">
         <v>74</v>
       </c>
@@ -1602,7 +1602,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="15" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="Y15" s="6">
         <v>2</v>
       </c>
@@ -1619,7 +1619,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="16" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B16" s="6" t="s">
         <v>117</v>
       </c>
@@ -1666,7 +1666,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="18" spans="1:32" ht="42" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:32" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B18" t="s">
         <v>82</v>
       </c>
@@ -1694,7 +1694,7 @@
       <c r="K18" t="s">
         <v>85</v>
       </c>
-      <c r="L18" s="14" t="s">
+      <c r="L18" s="10" t="s">
         <v>137</v>
       </c>
       <c r="M18" t="s">
@@ -1719,7 +1719,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="20" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B20" t="s">
         <v>89</v>
       </c>
@@ -1766,7 +1766,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>17</v>
       </c>
@@ -1819,7 +1819,7 @@
       </c>
       <c r="AF22" s="6"/>
     </row>
-    <row r="23" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:32" x14ac:dyDescent="0.2">
       <c r="W23" s="6"/>
       <c r="X23" s="6"/>
       <c r="Y23" s="6"/>
@@ -1831,7 +1831,7 @@
       <c r="AE23" s="6"/>
       <c r="AF23" s="6"/>
     </row>
-    <row r="24" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B24" t="s">
         <v>102</v>
       </c>
@@ -1875,7 +1875,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="26" spans="1:32" ht="30.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:32" ht="31.5" x14ac:dyDescent="0.4">
       <c r="B26" t="s">
         <v>141</v>
       </c>
@@ -1903,7 +1903,7 @@
       <c r="K26" t="s">
         <v>110</v>
       </c>
-      <c r="L26" s="14" t="s">
+      <c r="L26" s="10" t="s">
         <v>123</v>
       </c>
       <c r="M26" s="2" t="s">
@@ -1925,7 +1925,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="27" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:32" x14ac:dyDescent="0.2">
       <c r="M27" s="2" t="s">
         <v>122</v>
       </c>
@@ -1945,7 +1945,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="28" spans="1:32" ht="42" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:32" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B28" t="s">
         <v>132</v>
       </c>
@@ -1970,7 +1970,7 @@
       <c r="K28" t="s">
         <v>134</v>
       </c>
-      <c r="L28" s="14" t="s">
+      <c r="L28" s="10" t="s">
         <v>139</v>
       </c>
       <c r="M28" t="s">
@@ -2003,6 +2003,12 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="Z5:AA5"/>
+    <mergeCell ref="AB5:AE5"/>
+    <mergeCell ref="W1:AH1"/>
+    <mergeCell ref="W2:AH2"/>
+    <mergeCell ref="Y4:AE4"/>
+    <mergeCell ref="AF4:AH4"/>
     <mergeCell ref="M2:V2"/>
     <mergeCell ref="M1:V1"/>
     <mergeCell ref="O6:R6"/>
@@ -2012,12 +2018,6 @@
     <mergeCell ref="S6:V6"/>
     <mergeCell ref="S5:V5"/>
     <mergeCell ref="N4:V4"/>
-    <mergeCell ref="Z5:AA5"/>
-    <mergeCell ref="AB5:AE5"/>
-    <mergeCell ref="W1:AH1"/>
-    <mergeCell ref="W2:AH2"/>
-    <mergeCell ref="Y4:AE4"/>
-    <mergeCell ref="AF4:AH4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2027,33 +2027,33 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9BDF1B0-7733-4383-B476-4B5488719472}">
   <dimension ref="A1:AH9"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="15.25" customWidth="1"/>
     <col min="5" max="5" width="7.5" customWidth="1"/>
-    <col min="6" max="6" width="6.58203125" customWidth="1"/>
+    <col min="6" max="6" width="6.625" customWidth="1"/>
     <col min="7" max="7" width="6" style="6" customWidth="1"/>
     <col min="8" max="8" width="4.5" style="6" customWidth="1"/>
-    <col min="9" max="9" width="4.83203125" style="6" customWidth="1"/>
+    <col min="9" max="9" width="4.875" style="6" customWidth="1"/>
     <col min="10" max="10" width="4.75" style="6" customWidth="1"/>
     <col min="11" max="11" width="12.75" customWidth="1"/>
     <col min="12" max="12" width="29.5" customWidth="1"/>
     <col min="13" max="13" width="15.5" customWidth="1"/>
-    <col min="14" max="14" width="5.33203125" style="5" customWidth="1"/>
-    <col min="15" max="15" width="21.08203125" style="5" customWidth="1"/>
-    <col min="16" max="16" width="9.33203125" style="5" customWidth="1"/>
-    <col min="17" max="17" width="13.08203125" style="5" customWidth="1"/>
-    <col min="18" max="18" width="9.33203125" style="5" customWidth="1"/>
-    <col min="19" max="19" width="16.33203125" style="5" customWidth="1"/>
+    <col min="14" max="14" width="5.375" style="5" customWidth="1"/>
+    <col min="15" max="15" width="21.125" style="5" customWidth="1"/>
+    <col min="16" max="16" width="9.375" style="5" customWidth="1"/>
+    <col min="17" max="17" width="13.125" style="5" customWidth="1"/>
+    <col min="18" max="18" width="9.375" style="5" customWidth="1"/>
+    <col min="19" max="19" width="16.375" style="5" customWidth="1"/>
     <col min="20" max="20" width="21" style="5" customWidth="1"/>
     <col min="21" max="21" width="13.5" style="5" customWidth="1"/>
-    <col min="22" max="22" width="15.33203125" customWidth="1"/>
+    <col min="22" max="22" width="15.375" customWidth="1"/>
     <col min="23" max="23" width="11.5" customWidth="1"/>
     <col min="24" max="24" width="11.75" customWidth="1"/>
-    <col min="28" max="28" width="15.33203125" customWidth="1"/>
+    <col min="28" max="28" width="15.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -2117,7 +2117,7 @@
       <c r="AG1" s="11"/>
       <c r="AH1" s="11"/>
     </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -2181,7 +2181,7 @@
       <c r="AG2" s="12"/>
       <c r="AH2" s="12"/>
     </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -2229,7 +2229,7 @@
       <c r="AD3" s="1"/>
       <c r="AE3" s="1"/>
     </row>
-    <row r="4" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2264,22 +2264,22 @@
       <c r="X4" t="s">
         <v>61</v>
       </c>
-      <c r="Y4" s="10" t="s">
+      <c r="Y4" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="Z4" s="10"/>
-      <c r="AA4" s="10"/>
-      <c r="AB4" s="10"/>
-      <c r="AC4" s="10"/>
-      <c r="AD4" s="10"/>
-      <c r="AE4" s="10"/>
+      <c r="Z4" s="14"/>
+      <c r="AA4" s="14"/>
+      <c r="AB4" s="14"/>
+      <c r="AC4" s="14"/>
+      <c r="AD4" s="14"/>
+      <c r="AE4" s="14"/>
       <c r="AF4" s="12" t="s">
         <v>64</v>
       </c>
       <c r="AG4" s="12"/>
       <c r="AH4" s="12"/>
     </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2304,27 +2304,27 @@
       <c r="P5" s="11"/>
       <c r="Q5" s="11"/>
       <c r="R5" s="11"/>
-      <c r="S5" s="10" t="s">
+      <c r="S5" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="T5" s="10"/>
-      <c r="U5" s="10"/>
-      <c r="V5" s="10"/>
+      <c r="T5" s="14"/>
+      <c r="U5" s="14"/>
+      <c r="V5" s="14"/>
       <c r="Y5" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="Z5" s="10" t="s">
+      <c r="Z5" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="AA5" s="10"/>
-      <c r="AB5" s="10" t="s">
+      <c r="AA5" s="14"/>
+      <c r="AB5" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="AC5" s="10"/>
-      <c r="AD5" s="10"/>
-      <c r="AE5" s="10"/>
-    </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AC5" s="14"/>
+      <c r="AD5" s="14"/>
+      <c r="AE5" s="14"/>
+    </row>
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -2349,14 +2349,14 @@
       <c r="P6" s="11"/>
       <c r="Q6" s="11"/>
       <c r="R6" s="11"/>
-      <c r="S6" s="10" t="s">
+      <c r="S6" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="T6" s="10"/>
-      <c r="U6" s="10"/>
-      <c r="V6" s="10"/>
-    </row>
-    <row r="7" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="T6" s="14"/>
+      <c r="U6" s="14"/>
+      <c r="V6" s="14"/>
+    </row>
+    <row r="7" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
         <v>3</v>
       </c>
@@ -2379,7 +2379,7 @@
       <c r="U7" s="13"/>
       <c r="V7" s="13"/>
     </row>
-    <row r="8" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
         <v>17</v>
       </c>
@@ -2429,7 +2429,7 @@
       <c r="X8" s="2"/>
       <c r="AB8" s="2"/>
     </row>
-    <row r="9" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>17</v>
       </c>
@@ -2461,6 +2461,11 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="P7:R7"/>
+    <mergeCell ref="T7:V7"/>
+    <mergeCell ref="O5:R5"/>
+    <mergeCell ref="S5:V5"/>
+    <mergeCell ref="Z5:AA5"/>
     <mergeCell ref="AB5:AE5"/>
     <mergeCell ref="O6:R6"/>
     <mergeCell ref="S6:V6"/>
@@ -2471,11 +2476,6 @@
     <mergeCell ref="N4:V4"/>
     <mergeCell ref="Y4:AE4"/>
     <mergeCell ref="AF4:AH4"/>
-    <mergeCell ref="P7:R7"/>
-    <mergeCell ref="T7:V7"/>
-    <mergeCell ref="O5:R5"/>
-    <mergeCell ref="S5:V5"/>
-    <mergeCell ref="Z5:AA5"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/Datas/FoodDatas/FoodData.xlsx
+++ b/Config/Datas/FoodDatas/FoodData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\FoodDatas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA516040-32D5-4355-9CD8-58698A9A14E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E830BD69-3827-4B45-9C2F-5551A2847A6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="14290" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Config/Datas/FoodDatas/FoodData.xlsx
+++ b/Config/Datas/FoodDatas/FoodData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\FoodDatas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E830BD69-3827-4B45-9C2F-5551A2847A6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF3D7E1C-DEBD-4BF4-B62B-442F33AED97C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="14290" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="水果" sheetId="1" r:id="rId1"/>
@@ -704,7 +704,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -747,6 +747,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1032,7 +1035,7 @@
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="9" customWidth="1"/>
-    <col min="4" max="4" width="15.25" customWidth="1"/>
+    <col min="4" max="4" width="26.75" customWidth="1"/>
     <col min="5" max="5" width="7.5" customWidth="1"/>
     <col min="6" max="6" width="6.625" customWidth="1"/>
     <col min="7" max="7" width="6" style="6" customWidth="1"/>
@@ -1043,7 +1046,7 @@
     <col min="12" max="12" width="29.5" customWidth="1"/>
     <col min="13" max="13" width="15.5" customWidth="1"/>
     <col min="14" max="14" width="5.375" style="5" customWidth="1"/>
-    <col min="15" max="15" width="21.125" style="5" customWidth="1"/>
+    <col min="15" max="15" width="14.375" style="7" customWidth="1"/>
     <col min="16" max="16" width="9.375" style="5" customWidth="1"/>
     <col min="17" max="17" width="13.125" style="5" customWidth="1"/>
     <col min="18" max="18" width="9.375" style="5" customWidth="1"/>
@@ -1221,7 +1224,7 @@
       </c>
       <c r="M3" s="1"/>
       <c r="N3" s="4"/>
-      <c r="O3" s="4"/>
+      <c r="O3" s="2"/>
       <c r="W3" s="1"/>
       <c r="X3" s="1"/>
       <c r="Y3" s="2"/>
@@ -1438,6 +1441,7 @@
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="K9" s="2"/>
+      <c r="O9" s="7"/>
       <c r="T9" s="2"/>
     </row>
     <row r="10" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2">
@@ -1497,7 +1501,9 @@
         <v>88</v>
       </c>
     </row>
-    <row r="11" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="11" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O11" s="7"/>
+    </row>
     <row r="12" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B12" s="6" t="s">
         <v>81</v>
@@ -1538,6 +1544,7 @@
       <c r="N12" s="6">
         <v>1</v>
       </c>
+      <c r="O12" s="7"/>
       <c r="S12" s="6" t="s">
         <v>50</v>
       </c>
@@ -1548,7 +1555,9 @@
         <v>124</v>
       </c>
     </row>
-    <row r="13" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="13" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O13" s="7"/>
+    </row>
     <row r="14" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B14" s="6" t="s">
         <v>74</v>
@@ -1580,6 +1589,7 @@
       <c r="L14" t="s">
         <v>136</v>
       </c>
+      <c r="O14" s="7"/>
       <c r="W14" s="6" t="s">
         <v>60</v>
       </c>
@@ -1603,6 +1613,7 @@
       </c>
     </row>
     <row r="15" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O15" s="7"/>
       <c r="Y15" s="6">
         <v>2</v>
       </c>
@@ -1656,6 +1667,7 @@
       <c r="N16" s="6">
         <v>1</v>
       </c>
+      <c r="O16" s="7"/>
       <c r="S16" s="6" t="s">
         <v>50</v>
       </c>
@@ -1703,7 +1715,7 @@
       <c r="N18" s="5">
         <v>1</v>
       </c>
-      <c r="O18" s="5" t="s">
+      <c r="O18" s="7" t="s">
         <v>87</v>
       </c>
       <c r="P18" s="5">
@@ -1973,7 +1985,7 @@
       <c r="L28" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="M28" t="s">
+      <c r="M28" s="15" t="s">
         <v>86</v>
       </c>
       <c r="N28" s="5">

--- a/Config/Datas/FoodDatas/FoodData.xlsx
+++ b/Config/Datas/FoodDatas/FoodData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\FoodDatas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF3D7E1C-DEBD-4BF4-B62B-442F33AED97C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6EE6F06-A95B-4E62-91C1-CA9EA88310E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="水果" sheetId="1" r:id="rId1"/>
@@ -453,10 +453,6 @@
   </si>
   <si>
     <t>GA_定点爆破</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自己,false</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -632,6 +628,10 @@
   </si>
   <si>
     <t>添加到串串上时\n为周围随机2个未添加到串串上的食材\n+2美味度 +3珍稀度</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自己,任意,false,GS_1x1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -736,6 +736,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -744,12 +750,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1032,34 +1032,34 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AH28"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="4" max="4" width="26.75" customWidth="1"/>
     <col min="5" max="5" width="7.5" customWidth="1"/>
-    <col min="6" max="6" width="6.625" customWidth="1"/>
+    <col min="6" max="6" width="6.58203125" customWidth="1"/>
     <col min="7" max="7" width="6" style="6" customWidth="1"/>
     <col min="8" max="8" width="4.5" style="6" customWidth="1"/>
-    <col min="9" max="9" width="4.875" style="6" customWidth="1"/>
+    <col min="9" max="9" width="4.83203125" style="6" customWidth="1"/>
     <col min="10" max="10" width="4.75" style="6" customWidth="1"/>
     <col min="11" max="11" width="12.75" customWidth="1"/>
     <col min="12" max="12" width="29.5" customWidth="1"/>
     <col min="13" max="13" width="15.5" customWidth="1"/>
-    <col min="14" max="14" width="5.375" style="5" customWidth="1"/>
-    <col min="15" max="15" width="14.375" style="7" customWidth="1"/>
-    <col min="16" max="16" width="9.375" style="5" customWidth="1"/>
-    <col min="17" max="17" width="13.125" style="5" customWidth="1"/>
-    <col min="18" max="18" width="9.375" style="5" customWidth="1"/>
-    <col min="19" max="19" width="16.375" style="5" customWidth="1"/>
+    <col min="14" max="14" width="5.33203125" style="5" customWidth="1"/>
+    <col min="15" max="15" width="14.33203125" style="7" customWidth="1"/>
+    <col min="16" max="16" width="9.33203125" style="5" customWidth="1"/>
+    <col min="17" max="17" width="13.08203125" style="5" customWidth="1"/>
+    <col min="18" max="18" width="9.33203125" style="5" customWidth="1"/>
+    <col min="19" max="19" width="16.33203125" style="5" customWidth="1"/>
     <col min="20" max="20" width="21" style="5" customWidth="1"/>
     <col min="21" max="21" width="13.5" style="5" customWidth="1"/>
-    <col min="22" max="22" width="15.375" customWidth="1"/>
+    <col min="22" max="22" width="15.33203125" customWidth="1"/>
     <col min="23" max="23" width="11.5" customWidth="1"/>
     <col min="24" max="24" width="11.75" customWidth="1"/>
-    <col min="28" max="28" width="15.375" customWidth="1"/>
+    <col min="28" max="28" width="15.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -1096,34 +1096,34 @@
       <c r="L1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="M1" s="12" t="s">
+      <c r="M1" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="N1" s="12"/>
-      <c r="O1" s="12"/>
-      <c r="P1" s="12"/>
-      <c r="Q1" s="12"/>
-      <c r="R1" s="12"/>
-      <c r="S1" s="12"/>
-      <c r="T1" s="12"/>
-      <c r="U1" s="12"/>
-      <c r="V1" s="12"/>
-      <c r="W1" s="11" t="s">
+      <c r="N1" s="14"/>
+      <c r="O1" s="14"/>
+      <c r="P1" s="14"/>
+      <c r="Q1" s="14"/>
+      <c r="R1" s="14"/>
+      <c r="S1" s="14"/>
+      <c r="T1" s="14"/>
+      <c r="U1" s="14"/>
+      <c r="V1" s="14"/>
+      <c r="W1" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="X1" s="11"/>
-      <c r="Y1" s="11"/>
-      <c r="Z1" s="11"/>
-      <c r="AA1" s="11"/>
-      <c r="AB1" s="11"/>
-      <c r="AC1" s="11"/>
-      <c r="AD1" s="11"/>
-      <c r="AE1" s="11"/>
-      <c r="AF1" s="11"/>
-      <c r="AG1" s="11"/>
-      <c r="AH1" s="11"/>
-    </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="X1" s="13"/>
+      <c r="Y1" s="13"/>
+      <c r="Z1" s="13"/>
+      <c r="AA1" s="13"/>
+      <c r="AB1" s="13"/>
+      <c r="AC1" s="13"/>
+      <c r="AD1" s="13"/>
+      <c r="AE1" s="13"/>
+      <c r="AF1" s="13"/>
+      <c r="AG1" s="13"/>
+      <c r="AH1" s="13"/>
+    </row>
+    <row r="2" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1160,34 +1160,34 @@
       <c r="L2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="M2" s="11" t="s">
+      <c r="M2" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="N2" s="11"/>
-      <c r="O2" s="11"/>
-      <c r="P2" s="11"/>
-      <c r="Q2" s="11"/>
-      <c r="R2" s="11"/>
-      <c r="S2" s="11"/>
-      <c r="T2" s="11"/>
-      <c r="U2" s="11"/>
-      <c r="V2" s="11"/>
-      <c r="W2" s="12" t="s">
+      <c r="N2" s="13"/>
+      <c r="O2" s="13"/>
+      <c r="P2" s="13"/>
+      <c r="Q2" s="13"/>
+      <c r="R2" s="13"/>
+      <c r="S2" s="13"/>
+      <c r="T2" s="13"/>
+      <c r="U2" s="13"/>
+      <c r="V2" s="13"/>
+      <c r="W2" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="X2" s="12"/>
-      <c r="Y2" s="12"/>
-      <c r="Z2" s="12"/>
-      <c r="AA2" s="12"/>
-      <c r="AB2" s="12"/>
-      <c r="AC2" s="12"/>
-      <c r="AD2" s="12"/>
-      <c r="AE2" s="12"/>
-      <c r="AF2" s="12"/>
-      <c r="AG2" s="12"/>
-      <c r="AH2" s="12"/>
-    </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="X2" s="14"/>
+      <c r="Y2" s="14"/>
+      <c r="Z2" s="14"/>
+      <c r="AA2" s="14"/>
+      <c r="AB2" s="14"/>
+      <c r="AC2" s="14"/>
+      <c r="AD2" s="14"/>
+      <c r="AE2" s="14"/>
+      <c r="AF2" s="14"/>
+      <c r="AG2" s="14"/>
+      <c r="AH2" s="14"/>
+    </row>
+    <row r="3" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -1235,7 +1235,7 @@
       <c r="AD3" s="1"/>
       <c r="AE3" s="1"/>
     </row>
-    <row r="4" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1253,39 +1253,39 @@
       <c r="M4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="N4" s="11" t="s">
+      <c r="N4" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="O4" s="11"/>
-      <c r="P4" s="11"/>
-      <c r="Q4" s="11"/>
-      <c r="R4" s="11"/>
-      <c r="S4" s="11"/>
-      <c r="T4" s="11"/>
-      <c r="U4" s="11"/>
-      <c r="V4" s="11"/>
+      <c r="O4" s="13"/>
+      <c r="P4" s="13"/>
+      <c r="Q4" s="13"/>
+      <c r="R4" s="13"/>
+      <c r="S4" s="13"/>
+      <c r="T4" s="13"/>
+      <c r="U4" s="13"/>
+      <c r="V4" s="13"/>
       <c r="W4" t="s">
         <v>32</v>
       </c>
       <c r="X4" t="s">
         <v>61</v>
       </c>
-      <c r="Y4" s="14" t="s">
+      <c r="Y4" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="Z4" s="14"/>
-      <c r="AA4" s="14"/>
-      <c r="AB4" s="14"/>
-      <c r="AC4" s="14"/>
-      <c r="AD4" s="14"/>
-      <c r="AE4" s="14"/>
-      <c r="AF4" s="12" t="s">
+      <c r="Z4" s="12"/>
+      <c r="AA4" s="12"/>
+      <c r="AB4" s="12"/>
+      <c r="AC4" s="12"/>
+      <c r="AD4" s="12"/>
+      <c r="AE4" s="12"/>
+      <c r="AF4" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="AG4" s="12"/>
-      <c r="AH4" s="12"/>
-    </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AG4" s="14"/>
+      <c r="AH4" s="14"/>
+    </row>
+    <row r="5" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1304,33 +1304,33 @@
       <c r="N5" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="O5" s="11" t="s">
+      <c r="O5" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="P5" s="11"/>
-      <c r="Q5" s="11"/>
-      <c r="R5" s="11"/>
-      <c r="S5" s="14" t="s">
+      <c r="P5" s="13"/>
+      <c r="Q5" s="13"/>
+      <c r="R5" s="13"/>
+      <c r="S5" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="T5" s="14"/>
-      <c r="U5" s="14"/>
-      <c r="V5" s="14"/>
+      <c r="T5" s="12"/>
+      <c r="U5" s="12"/>
+      <c r="V5" s="12"/>
       <c r="Y5" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="Z5" s="14" t="s">
+      <c r="Z5" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="AA5" s="14"/>
-      <c r="AB5" s="14" t="s">
+      <c r="AA5" s="12"/>
+      <c r="AB5" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="AC5" s="14"/>
-      <c r="AD5" s="14"/>
-      <c r="AE5" s="14"/>
-    </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AC5" s="12"/>
+      <c r="AD5" s="12"/>
+      <c r="AE5" s="12"/>
+    </row>
+    <row r="6" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -1349,20 +1349,20 @@
       <c r="N6" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="O6" s="11" t="s">
+      <c r="O6" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="P6" s="11"/>
-      <c r="Q6" s="11"/>
-      <c r="R6" s="11"/>
-      <c r="S6" s="14" t="s">
+      <c r="P6" s="13"/>
+      <c r="Q6" s="13"/>
+      <c r="R6" s="13"/>
+      <c r="S6" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="T6" s="14"/>
-      <c r="U6" s="14"/>
-      <c r="V6" s="14"/>
-    </row>
-    <row r="7" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="T6" s="12"/>
+      <c r="U6" s="12"/>
+      <c r="V6" s="12"/>
+    </row>
+    <row r="7" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>3</v>
       </c>
@@ -1371,21 +1371,21 @@
       <c r="O7" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="P7" s="13" t="s">
+      <c r="P7" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="Q7" s="13"/>
-      <c r="R7" s="13"/>
+      <c r="Q7" s="15"/>
+      <c r="R7" s="15"/>
       <c r="S7" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="T7" s="13" t="s">
+      <c r="T7" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="U7" s="13"/>
-      <c r="V7" s="13"/>
-    </row>
-    <row r="8" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="U7" s="15"/>
+      <c r="V7" s="15"/>
+    </row>
+    <row r="8" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B8" s="6" t="s">
         <v>76</v>
       </c>
@@ -1415,7 +1415,7 @@
         <v>25</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M8" s="6" t="s">
         <v>55</v>
@@ -1426,16 +1426,16 @@
       <c r="O8" s="2"/>
       <c r="P8" s="8"/>
       <c r="S8" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="T8" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="T8" s="2" t="s">
+      <c r="U8" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="U8" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="9" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
@@ -1444,7 +1444,7 @@
       <c r="O9" s="7"/>
       <c r="T9" s="2"/>
     </row>
-    <row r="10" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B10" s="6" t="s">
         <v>75</v>
       </c>
@@ -1474,7 +1474,7 @@
         <v>26</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="M10" s="2" t="s">
         <v>78</v>
@@ -1501,10 +1501,10 @@
         <v>88</v>
       </c>
     </row>
-    <row r="11" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="O11" s="7"/>
     </row>
-    <row r="12" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B12" s="6" t="s">
         <v>81</v>
       </c>
@@ -1533,10 +1533,10 @@
         <v>4</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="M12" s="6" t="s">
         <v>55</v>
@@ -1552,13 +1552,13 @@
         <v>51</v>
       </c>
       <c r="U12" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="13" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="O13" s="7"/>
     </row>
-    <row r="14" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B14" s="6" t="s">
         <v>74</v>
       </c>
@@ -1587,7 +1587,7 @@
         <v>71</v>
       </c>
       <c r="L14" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O14" s="7"/>
       <c r="W14" s="6" t="s">
@@ -1600,19 +1600,19 @@
         <v>1</v>
       </c>
       <c r="AB14" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AC14" s="6" t="s">
         <v>72</v>
       </c>
       <c r="AD14" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AE14" s="6" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="15" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="O15" s="7"/>
       <c r="Y15" s="6">
         <v>2</v>
@@ -1630,15 +1630,15 @@
         <v>72</v>
       </c>
     </row>
-    <row r="16" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B16" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C16" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="D16" s="6" t="s">
         <v>119</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>120</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>21</v>
@@ -1656,10 +1656,10 @@
         <v>3</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="M16" s="2" t="s">
         <v>78</v>
@@ -1672,13 +1672,13 @@
         <v>50</v>
       </c>
       <c r="T16" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="U16" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="18" spans="1:32" ht="42.75" x14ac:dyDescent="0.2">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="18" spans="1:32" ht="42" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>82</v>
       </c>
@@ -1707,7 +1707,7 @@
         <v>85</v>
       </c>
       <c r="L18" s="10" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M18" t="s">
         <v>86</v>
@@ -1725,13 +1725,13 @@
         <v>34</v>
       </c>
       <c r="T18" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="U18" s="6" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="20" spans="1:32" x14ac:dyDescent="0.2">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="20" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>89</v>
       </c>
@@ -1745,7 +1745,7 @@
         <v>79</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H20" s="6">
         <v>1</v>
@@ -1760,7 +1760,7 @@
         <v>94</v>
       </c>
       <c r="L20" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="M20" s="6" t="s">
         <v>55</v>
@@ -1778,7 +1778,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>17</v>
       </c>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="AF22" s="6"/>
     </row>
-    <row r="23" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:32" x14ac:dyDescent="0.3">
       <c r="W23" s="6"/>
       <c r="X23" s="6"/>
       <c r="Y23" s="6"/>
@@ -1843,7 +1843,7 @@
       <c r="AE23" s="6"/>
       <c r="AF23" s="6"/>
     </row>
-    <row r="24" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>102</v>
       </c>
@@ -1857,7 +1857,7 @@
         <v>21</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H24" s="6">
         <v>1</v>
@@ -1884,18 +1884,18 @@
         <v>106</v>
       </c>
       <c r="T24" s="5" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="26" spans="1:32" ht="30.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B26" t="s">
+        <v>140</v>
+      </c>
+      <c r="C26" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="26" spans="1:32" ht="31.5" x14ac:dyDescent="0.4">
-      <c r="B26" t="s">
-        <v>141</v>
-      </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
         <v>108</v>
-      </c>
-      <c r="D26" t="s">
-        <v>109</v>
       </c>
       <c r="E26" t="s">
         <v>79</v>
@@ -1913,13 +1913,13 @@
         <v>10</v>
       </c>
       <c r="K26" t="s">
+        <v>109</v>
+      </c>
+      <c r="L26" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="M26" s="2" t="s">
         <v>110</v>
-      </c>
-      <c r="L26" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="M26" s="2" t="s">
-        <v>111</v>
       </c>
       <c r="N26" s="5">
         <v>1</v>
@@ -1931,15 +1931,15 @@
         <v>51</v>
       </c>
       <c r="U26" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="V26" s="6" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="27" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:32" x14ac:dyDescent="0.3">
       <c r="M27" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="N27" s="5">
         <v>2</v>
@@ -1948,7 +1948,7 @@
         <v>58</v>
       </c>
       <c r="T27" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="U27" s="5" t="s">
         <v>51</v>
@@ -1957,12 +1957,12 @@
         <v>72</v>
       </c>
     </row>
-    <row r="28" spans="1:32" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:32" ht="42" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
+        <v>131</v>
+      </c>
+      <c r="C28" t="s">
         <v>132</v>
-      </c>
-      <c r="C28" t="s">
-        <v>133</v>
       </c>
       <c r="E28" t="s">
         <v>19</v>
@@ -1980,12 +1980,12 @@
         <v>4</v>
       </c>
       <c r="K28" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="L28" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="M28" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="M28" s="11" t="s">
         <v>86</v>
       </c>
       <c r="N28" s="5">
@@ -1995,10 +1995,10 @@
         <v>46</v>
       </c>
       <c r="P28" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="Q28" s="5" t="s">
         <v>142</v>
-      </c>
-      <c r="Q28" s="5" t="s">
-        <v>143</v>
       </c>
       <c r="R28" s="5" t="s">
         <v>47</v>
@@ -2007,20 +2007,14 @@
         <v>34</v>
       </c>
       <c r="T28" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="U28" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="Z5:AA5"/>
-    <mergeCell ref="AB5:AE5"/>
-    <mergeCell ref="W1:AH1"/>
-    <mergeCell ref="W2:AH2"/>
-    <mergeCell ref="Y4:AE4"/>
-    <mergeCell ref="AF4:AH4"/>
     <mergeCell ref="M2:V2"/>
     <mergeCell ref="M1:V1"/>
     <mergeCell ref="O6:R6"/>
@@ -2030,6 +2024,12 @@
     <mergeCell ref="S6:V6"/>
     <mergeCell ref="S5:V5"/>
     <mergeCell ref="N4:V4"/>
+    <mergeCell ref="Z5:AA5"/>
+    <mergeCell ref="AB5:AE5"/>
+    <mergeCell ref="W1:AH1"/>
+    <mergeCell ref="W2:AH2"/>
+    <mergeCell ref="Y4:AE4"/>
+    <mergeCell ref="AF4:AH4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2039,33 +2039,33 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9BDF1B0-7733-4383-B476-4B5488719472}">
   <dimension ref="A1:AH9"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="15.25" customWidth="1"/>
     <col min="5" max="5" width="7.5" customWidth="1"/>
-    <col min="6" max="6" width="6.625" customWidth="1"/>
+    <col min="6" max="6" width="6.58203125" customWidth="1"/>
     <col min="7" max="7" width="6" style="6" customWidth="1"/>
     <col min="8" max="8" width="4.5" style="6" customWidth="1"/>
-    <col min="9" max="9" width="4.875" style="6" customWidth="1"/>
+    <col min="9" max="9" width="4.83203125" style="6" customWidth="1"/>
     <col min="10" max="10" width="4.75" style="6" customWidth="1"/>
     <col min="11" max="11" width="12.75" customWidth="1"/>
     <col min="12" max="12" width="29.5" customWidth="1"/>
     <col min="13" max="13" width="15.5" customWidth="1"/>
-    <col min="14" max="14" width="5.375" style="5" customWidth="1"/>
-    <col min="15" max="15" width="21.125" style="5" customWidth="1"/>
-    <col min="16" max="16" width="9.375" style="5" customWidth="1"/>
-    <col min="17" max="17" width="13.125" style="5" customWidth="1"/>
-    <col min="18" max="18" width="9.375" style="5" customWidth="1"/>
-    <col min="19" max="19" width="16.375" style="5" customWidth="1"/>
+    <col min="14" max="14" width="5.33203125" style="5" customWidth="1"/>
+    <col min="15" max="15" width="21.08203125" style="5" customWidth="1"/>
+    <col min="16" max="16" width="9.33203125" style="5" customWidth="1"/>
+    <col min="17" max="17" width="13.08203125" style="5" customWidth="1"/>
+    <col min="18" max="18" width="9.33203125" style="5" customWidth="1"/>
+    <col min="19" max="19" width="16.33203125" style="5" customWidth="1"/>
     <col min="20" max="20" width="21" style="5" customWidth="1"/>
     <col min="21" max="21" width="13.5" style="5" customWidth="1"/>
-    <col min="22" max="22" width="15.375" customWidth="1"/>
+    <col min="22" max="22" width="15.33203125" customWidth="1"/>
     <col min="23" max="23" width="11.5" customWidth="1"/>
     <col min="24" max="24" width="11.75" customWidth="1"/>
-    <col min="28" max="28" width="15.375" customWidth="1"/>
+    <col min="28" max="28" width="15.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -2102,34 +2102,34 @@
       <c r="L1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="M1" s="12" t="s">
+      <c r="M1" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="N1" s="12"/>
-      <c r="O1" s="12"/>
-      <c r="P1" s="12"/>
-      <c r="Q1" s="12"/>
-      <c r="R1" s="12"/>
-      <c r="S1" s="12"/>
-      <c r="T1" s="12"/>
-      <c r="U1" s="12"/>
-      <c r="V1" s="12"/>
-      <c r="W1" s="11" t="s">
+      <c r="N1" s="14"/>
+      <c r="O1" s="14"/>
+      <c r="P1" s="14"/>
+      <c r="Q1" s="14"/>
+      <c r="R1" s="14"/>
+      <c r="S1" s="14"/>
+      <c r="T1" s="14"/>
+      <c r="U1" s="14"/>
+      <c r="V1" s="14"/>
+      <c r="W1" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="X1" s="11"/>
-      <c r="Y1" s="11"/>
-      <c r="Z1" s="11"/>
-      <c r="AA1" s="11"/>
-      <c r="AB1" s="11"/>
-      <c r="AC1" s="11"/>
-      <c r="AD1" s="11"/>
-      <c r="AE1" s="11"/>
-      <c r="AF1" s="11"/>
-      <c r="AG1" s="11"/>
-      <c r="AH1" s="11"/>
-    </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="X1" s="13"/>
+      <c r="Y1" s="13"/>
+      <c r="Z1" s="13"/>
+      <c r="AA1" s="13"/>
+      <c r="AB1" s="13"/>
+      <c r="AC1" s="13"/>
+      <c r="AD1" s="13"/>
+      <c r="AE1" s="13"/>
+      <c r="AF1" s="13"/>
+      <c r="AG1" s="13"/>
+      <c r="AH1" s="13"/>
+    </row>
+    <row r="2" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -2166,34 +2166,34 @@
       <c r="L2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="M2" s="11" t="s">
+      <c r="M2" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="N2" s="11"/>
-      <c r="O2" s="11"/>
-      <c r="P2" s="11"/>
-      <c r="Q2" s="11"/>
-      <c r="R2" s="11"/>
-      <c r="S2" s="11"/>
-      <c r="T2" s="11"/>
-      <c r="U2" s="11"/>
-      <c r="V2" s="11"/>
-      <c r="W2" s="12" t="s">
+      <c r="N2" s="13"/>
+      <c r="O2" s="13"/>
+      <c r="P2" s="13"/>
+      <c r="Q2" s="13"/>
+      <c r="R2" s="13"/>
+      <c r="S2" s="13"/>
+      <c r="T2" s="13"/>
+      <c r="U2" s="13"/>
+      <c r="V2" s="13"/>
+      <c r="W2" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="X2" s="12"/>
-      <c r="Y2" s="12"/>
-      <c r="Z2" s="12"/>
-      <c r="AA2" s="12"/>
-      <c r="AB2" s="12"/>
-      <c r="AC2" s="12"/>
-      <c r="AD2" s="12"/>
-      <c r="AE2" s="12"/>
-      <c r="AF2" s="12"/>
-      <c r="AG2" s="12"/>
-      <c r="AH2" s="12"/>
-    </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="X2" s="14"/>
+      <c r="Y2" s="14"/>
+      <c r="Z2" s="14"/>
+      <c r="AA2" s="14"/>
+      <c r="AB2" s="14"/>
+      <c r="AC2" s="14"/>
+      <c r="AD2" s="14"/>
+      <c r="AE2" s="14"/>
+      <c r="AF2" s="14"/>
+      <c r="AG2" s="14"/>
+      <c r="AH2" s="14"/>
+    </row>
+    <row r="3" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -2241,7 +2241,7 @@
       <c r="AD3" s="1"/>
       <c r="AE3" s="1"/>
     </row>
-    <row r="4" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2259,39 +2259,39 @@
       <c r="M4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="N4" s="11" t="s">
+      <c r="N4" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="O4" s="11"/>
-      <c r="P4" s="11"/>
-      <c r="Q4" s="11"/>
-      <c r="R4" s="11"/>
-      <c r="S4" s="11"/>
-      <c r="T4" s="11"/>
-      <c r="U4" s="11"/>
-      <c r="V4" s="11"/>
+      <c r="O4" s="13"/>
+      <c r="P4" s="13"/>
+      <c r="Q4" s="13"/>
+      <c r="R4" s="13"/>
+      <c r="S4" s="13"/>
+      <c r="T4" s="13"/>
+      <c r="U4" s="13"/>
+      <c r="V4" s="13"/>
       <c r="W4" t="s">
         <v>32</v>
       </c>
       <c r="X4" t="s">
         <v>61</v>
       </c>
-      <c r="Y4" s="14" t="s">
+      <c r="Y4" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="Z4" s="14"/>
-      <c r="AA4" s="14"/>
-      <c r="AB4" s="14"/>
-      <c r="AC4" s="14"/>
-      <c r="AD4" s="14"/>
-      <c r="AE4" s="14"/>
-      <c r="AF4" s="12" t="s">
+      <c r="Z4" s="12"/>
+      <c r="AA4" s="12"/>
+      <c r="AB4" s="12"/>
+      <c r="AC4" s="12"/>
+      <c r="AD4" s="12"/>
+      <c r="AE4" s="12"/>
+      <c r="AF4" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="AG4" s="12"/>
-      <c r="AH4" s="12"/>
-    </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AG4" s="14"/>
+      <c r="AH4" s="14"/>
+    </row>
+    <row r="5" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2310,33 +2310,33 @@
       <c r="N5" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="O5" s="11" t="s">
+      <c r="O5" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="P5" s="11"/>
-      <c r="Q5" s="11"/>
-      <c r="R5" s="11"/>
-      <c r="S5" s="14" t="s">
+      <c r="P5" s="13"/>
+      <c r="Q5" s="13"/>
+      <c r="R5" s="13"/>
+      <c r="S5" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="T5" s="14"/>
-      <c r="U5" s="14"/>
-      <c r="V5" s="14"/>
+      <c r="T5" s="12"/>
+      <c r="U5" s="12"/>
+      <c r="V5" s="12"/>
       <c r="Y5" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="Z5" s="14" t="s">
+      <c r="Z5" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="AA5" s="14"/>
-      <c r="AB5" s="14" t="s">
+      <c r="AA5" s="12"/>
+      <c r="AB5" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="AC5" s="14"/>
-      <c r="AD5" s="14"/>
-      <c r="AE5" s="14"/>
-    </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AC5" s="12"/>
+      <c r="AD5" s="12"/>
+      <c r="AE5" s="12"/>
+    </row>
+    <row r="6" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -2355,20 +2355,20 @@
       <c r="N6" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="O6" s="11" t="s">
+      <c r="O6" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="P6" s="11"/>
-      <c r="Q6" s="11"/>
-      <c r="R6" s="11"/>
-      <c r="S6" s="14" t="s">
+      <c r="P6" s="13"/>
+      <c r="Q6" s="13"/>
+      <c r="R6" s="13"/>
+      <c r="S6" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="T6" s="14"/>
-      <c r="U6" s="14"/>
-      <c r="V6" s="14"/>
-    </row>
-    <row r="7" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="T6" s="12"/>
+      <c r="U6" s="12"/>
+      <c r="V6" s="12"/>
+    </row>
+    <row r="7" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>3</v>
       </c>
@@ -2377,21 +2377,21 @@
       <c r="O7" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="P7" s="13" t="s">
+      <c r="P7" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="Q7" s="13"/>
-      <c r="R7" s="13"/>
+      <c r="Q7" s="15"/>
+      <c r="R7" s="15"/>
       <c r="S7" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="T7" s="13" t="s">
+      <c r="T7" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="U7" s="13"/>
-      <c r="V7" s="13"/>
-    </row>
-    <row r="8" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="U7" s="15"/>
+      <c r="V7" s="15"/>
+    </row>
+    <row r="8" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>17</v>
       </c>
@@ -2441,7 +2441,7 @@
       <c r="X8" s="2"/>
       <c r="AB8" s="2"/>
     </row>
-    <row r="9" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
         <v>17</v>
       </c>
@@ -2473,11 +2473,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="P7:R7"/>
-    <mergeCell ref="T7:V7"/>
-    <mergeCell ref="O5:R5"/>
-    <mergeCell ref="S5:V5"/>
-    <mergeCell ref="Z5:AA5"/>
     <mergeCell ref="AB5:AE5"/>
     <mergeCell ref="O6:R6"/>
     <mergeCell ref="S6:V6"/>
@@ -2488,6 +2483,11 @@
     <mergeCell ref="N4:V4"/>
     <mergeCell ref="Y4:AE4"/>
     <mergeCell ref="AF4:AH4"/>
+    <mergeCell ref="P7:R7"/>
+    <mergeCell ref="T7:V7"/>
+    <mergeCell ref="O5:R5"/>
+    <mergeCell ref="S5:V5"/>
+    <mergeCell ref="Z5:AA5"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/Datas/FoodDatas/FoodData.xlsx
+++ b/Config/Datas/FoodDatas/FoodData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\FoodDatas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6EE6F06-A95B-4E62-91C1-CA9EA88310E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3221E2DF-FFB2-4CCF-BE18-F1CFC69F5361}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="148">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -632,6 +632,18 @@
   </si>
   <si>
     <t>自己,任意,false,GS_1x1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fish</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>金枪鱼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fish</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1031,7 +1043,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AH28"/>
+  <dimension ref="A1:AH30"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="9" customWidth="1"/>
@@ -2011,6 +2023,32 @@
       </c>
       <c r="U28" s="6" t="s">
         <v>139</v>
+      </c>
+    </row>
+    <row r="30" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B30" t="s">
+        <v>145</v>
+      </c>
+      <c r="C30" t="s">
+        <v>146</v>
+      </c>
+      <c r="E30" t="s">
+        <v>70</v>
+      </c>
+      <c r="G30" s="6">
+        <v>2</v>
+      </c>
+      <c r="H30" s="6">
+        <v>2</v>
+      </c>
+      <c r="I30" s="6">
+        <v>5</v>
+      </c>
+      <c r="J30" s="6">
+        <v>5</v>
+      </c>
+      <c r="K30" t="s">
+        <v>147</v>
       </c>
     </row>
   </sheetData>
